--- a/internal_doc/05.测试设计/story/mysql连接器/MySQL自动化用例修改-索引支持数值型及日期型.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/MySQL自动化用例修改-索引支持数值型及日期型.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" activeTab="7"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="待办事项" sheetId="7" r:id="rId1"/>
@@ -1664,11 +1664,6 @@
   </si>
   <si>
     <t>修改注释
-不支持触发器，待确认</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改注释
 time为索引
 datetime为索引</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1703,6 +1698,11 @@
   </si>
   <si>
     <t>在date上创建索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改注释
+在timestamp上创建索引</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2006,25 +2006,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">修改注释
-在timestamp上创建索引
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>主干上需修改54行、105行</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>是</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2166,6 +2147,11 @@
   </si>
   <si>
     <t>set</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改注释
+触发器代码去注释</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4990,7 +4976,7 @@
       <c r="E66" s="25"/>
       <c r="F66" s="25"/>
       <c r="G66" s="19" t="s">
-        <v>418</v>
+        <v>534</v>
       </c>
       <c r="H66" s="16" t="s">
         <v>363</v>
@@ -5010,7 +4996,7 @@
       <c r="E67" s="16"/>
       <c r="F67" s="16"/>
       <c r="G67" s="19" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H67" s="16" t="s">
         <v>363</v>
@@ -5354,7 +5340,7 @@
       <c r="E89" s="25"/>
       <c r="F89" s="25"/>
       <c r="G89" s="19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H89" s="16" t="s">
         <v>363</v>
@@ -5704,7 +5690,7 @@
       <c r="E109" s="25"/>
       <c r="F109" s="25"/>
       <c r="G109" s="19" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H109" s="16" t="s">
         <v>363</v>
@@ -5774,7 +5760,7 @@
       <c r="E113" s="17"/>
       <c r="F113" s="25"/>
       <c r="G113" s="19" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H113" s="16" t="s">
         <v>363</v>
@@ -5849,7 +5835,7 @@
       <c r="E117" s="16"/>
       <c r="F117" s="16"/>
       <c r="G117" s="19" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H117" s="16" t="s">
         <v>363</v>
@@ -5914,7 +5900,7 @@
       <c r="E121" s="25"/>
       <c r="F121" s="25"/>
       <c r="G121" s="19" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H121" s="16" t="s">
         <v>363</v>
@@ -6049,7 +6035,7 @@
       <c r="E128" s="25"/>
       <c r="F128" s="25"/>
       <c r="G128" s="19" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H128" s="16" t="s">
         <v>363</v>
@@ -6069,7 +6055,7 @@
       <c r="E129" s="17"/>
       <c r="F129" s="25"/>
       <c r="G129" s="19" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H129" s="16" t="s">
         <v>363</v>
@@ -6089,7 +6075,7 @@
       <c r="E130" s="25"/>
       <c r="F130" s="25"/>
       <c r="G130" s="19" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H130" s="16" t="s">
         <v>363</v>
@@ -6216,7 +6202,7 @@
       <c r="E137" s="25"/>
       <c r="F137" s="25"/>
       <c r="G137" s="19" t="s">
-        <v>498</v>
+        <v>426</v>
       </c>
       <c r="H137" s="16" t="s">
         <v>363</v>
@@ -6389,7 +6375,7 @@
         <v>357</v>
       </c>
       <c r="H148" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="30" customHeight="1">
@@ -6406,10 +6392,10 @@
       <c r="E149" s="25"/>
       <c r="F149" s="25"/>
       <c r="G149" s="19" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H149" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="30" hidden="1" customHeight="1">
@@ -6534,7 +6520,7 @@
         <v>458</v>
       </c>
       <c r="H157" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="30" customHeight="1">
@@ -6554,7 +6540,7 @@
         <v>458</v>
       </c>
       <c r="H158" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="30" customHeight="1">
@@ -6574,7 +6560,7 @@
         <v>458</v>
       </c>
       <c r="H159" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="30" customHeight="1">
@@ -6594,7 +6580,7 @@
         <v>458</v>
       </c>
       <c r="H160" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="30" customHeight="1">
@@ -6614,7 +6600,7 @@
         <v>458</v>
       </c>
       <c r="H161" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="30" customHeight="1">
@@ -6634,7 +6620,7 @@
         <v>458</v>
       </c>
       <c r="H162" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="163" spans="1:8" s="13" customFormat="1" ht="30" customHeight="1">
@@ -6779,7 +6765,7 @@
     </row>
     <row r="172" spans="1:8" ht="30" customHeight="1">
       <c r="A172" s="16" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B172" s="16" t="s">
         <v>363</v>
@@ -7184,7 +7170,7 @@
     </row>
     <row r="196" spans="1:8" ht="30" customHeight="1">
       <c r="A196" s="16" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B196" s="16" t="s">
         <v>363</v>
@@ -7204,7 +7190,7 @@
     </row>
     <row r="197" spans="1:8" ht="30" customHeight="1">
       <c r="A197" s="16" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B197" s="16" t="s">
         <v>363</v>
@@ -7281,7 +7267,7 @@
     </row>
     <row r="201" spans="1:8" ht="30" customHeight="1">
       <c r="A201" s="16" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B201" s="16" t="s">
         <v>363</v>
@@ -7461,7 +7447,7 @@
     </row>
     <row r="210" spans="1:8" ht="30" customHeight="1">
       <c r="A210" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B210" s="16" t="s">
         <v>363</v>
@@ -7641,7 +7627,7 @@
     </row>
     <row r="219" spans="1:8" ht="30" customHeight="1">
       <c r="A219" s="16" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B219" s="16" t="s">
         <v>363</v>
@@ -7961,7 +7947,7 @@
     </row>
     <row r="235" spans="1:8" ht="30" customHeight="1">
       <c r="A235" s="16" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B235" s="16" t="s">
         <v>363</v>
@@ -8161,7 +8147,7 @@
     </row>
     <row r="248" spans="1:8" ht="30" customHeight="1">
       <c r="A248" s="16" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B248" s="16" t="s">
         <v>363</v>
@@ -8226,7 +8212,7 @@
     </row>
     <row r="252" spans="1:8" ht="30" customHeight="1">
       <c r="A252" s="16" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B252" s="16" t="s">
         <v>363</v>
@@ -8246,7 +8232,7 @@
     </row>
     <row r="253" spans="1:8" ht="30" customHeight="1">
       <c r="A253" s="16" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B253" s="16" t="s">
         <v>363</v>
@@ -8266,7 +8252,7 @@
     </row>
     <row r="254" spans="1:8" ht="30" customHeight="1">
       <c r="A254" s="16" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B254" s="16" t="s">
         <v>363</v>
@@ -8286,7 +8272,7 @@
     </row>
     <row r="255" spans="1:8" ht="30" customHeight="1">
       <c r="A255" s="16" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B255" s="16" t="s">
         <v>363</v>
@@ -8318,7 +8304,7 @@
       <c r="E256" s="25"/>
       <c r="F256" s="25"/>
       <c r="G256" s="19" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H256" s="16" t="s">
         <v>363</v>
@@ -8426,7 +8412,7 @@
     </row>
     <row r="263" spans="1:8" ht="30" customHeight="1">
       <c r="A263" s="16" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B263" s="16" t="s">
         <v>363</v>
@@ -8476,7 +8462,7 @@
     </row>
     <row r="266" spans="1:8" ht="30" customHeight="1">
       <c r="A266" s="16" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B266" s="16" t="s">
         <v>363</v>
@@ -8496,7 +8482,7 @@
     </row>
     <row r="267" spans="1:8" ht="30" customHeight="1">
       <c r="A267" s="16" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B267" s="16" t="s">
         <v>363</v>
@@ -8643,7 +8629,7 @@
       <c r="E275" s="16"/>
       <c r="F275" s="16"/>
       <c r="G275" s="16" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H275" s="16"/>
     </row>
@@ -12813,29 +12799,29 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1">
       <c r="A1" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>515</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>516</v>
-      </c>
       <c r="C1" s="16" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" customHeight="1">
       <c r="A2" s="16" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" customHeight="1">
       <c r="A3" s="16" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>296</v>
@@ -12844,7 +12830,7 @@
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1">
       <c r="A4" s="16" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>296</v>
@@ -12853,7 +12839,7 @@
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>296</v>
@@ -12862,7 +12848,7 @@
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>296</v>
@@ -12871,7 +12857,7 @@
     </row>
     <row r="7" spans="1:3" s="13" customFormat="1" ht="30" customHeight="1">
       <c r="A7" s="16" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>296</v>
@@ -12880,38 +12866,38 @@
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1">
       <c r="A8" s="16" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C10" s="16"/>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>296</v>
@@ -12920,7 +12906,7 @@
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1">
       <c r="A12" s="16" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>296</v>
@@ -12929,25 +12915,25 @@
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1">
       <c r="A13" s="16" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C13" s="16"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1">
       <c r="A14" s="16" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C14" s="16"/>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1">
       <c r="A15" s="16" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>296</v>
@@ -12956,24 +12942,24 @@
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1">
       <c r="A16" s="16" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>296</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>296</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" customHeight="1"/>

--- a/internal_doc/05.测试设计/story/mysql连接器/MySQL自动化用例修改-索引支持数值型及日期型.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/MySQL自动化用例修改-索引支持数值型及日期型.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7860" firstSheet="5" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="待办事项" sheetId="7" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet3" sheetId="15" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">需调整用例!$B$1:$C$929</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">需调整用例!$G$1:$G$929</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -3847,7 +3847,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H929"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -3887,7 +3886,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>364</v>
       </c>
@@ -3902,7 +3901,7 @@
       <c r="F2" s="25"/>
       <c r="G2" s="16"/>
     </row>
-    <row r="3" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="3" spans="1:8" ht="30" customHeight="1">
       <c r="A3" s="16" t="s">
         <v>365</v>
       </c>
@@ -3917,7 +3916,7 @@
       <c r="F3" s="25"/>
       <c r="G3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="4" spans="1:8" ht="30" customHeight="1">
       <c r="A4" s="16" t="s">
         <v>73</v>
       </c>
@@ -3972,7 +3971,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="7" spans="1:8" ht="30" customHeight="1">
       <c r="A7" s="16" t="s">
         <v>332</v>
       </c>
@@ -3987,7 +3986,7 @@
       <c r="F7" s="25"/>
       <c r="G7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="8" spans="1:8" ht="30" customHeight="1">
       <c r="A8" s="16" t="s">
         <v>74</v>
       </c>
@@ -4002,7 +4001,7 @@
       <c r="F8" s="25"/>
       <c r="G8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="16" t="s">
         <v>366</v>
       </c>
@@ -4017,7 +4016,7 @@
       <c r="F9" s="25"/>
       <c r="G9" s="19"/>
     </row>
-    <row r="10" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="10" spans="1:8" ht="30" customHeight="1">
       <c r="A10" s="16" t="s">
         <v>75</v>
       </c>
@@ -4032,7 +4031,7 @@
       <c r="F10" s="25"/>
       <c r="G10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="11" spans="1:8" ht="30" customHeight="1">
       <c r="A11" s="16" t="s">
         <v>76</v>
       </c>
@@ -4047,7 +4046,7 @@
       <c r="F11" s="25"/>
       <c r="G11" s="16"/>
     </row>
-    <row r="12" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="12" spans="1:8" ht="30" customHeight="1">
       <c r="A12" s="16" t="s">
         <v>367</v>
       </c>
@@ -4062,7 +4061,7 @@
       <c r="F12" s="25"/>
       <c r="G12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="13" spans="1:8" ht="30" customHeight="1">
       <c r="A13" s="16" t="s">
         <v>368</v>
       </c>
@@ -4077,7 +4076,7 @@
       <c r="F13" s="25"/>
       <c r="G13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="14" spans="1:8" ht="30" customHeight="1">
       <c r="A14" s="16" t="s">
         <v>369</v>
       </c>
@@ -4092,7 +4091,7 @@
       <c r="F14" s="25"/>
       <c r="G14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="15" spans="1:8" ht="30" customHeight="1">
       <c r="A15" s="16" t="s">
         <v>77</v>
       </c>
@@ -4107,7 +4106,7 @@
       <c r="F15" s="25"/>
       <c r="G15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="16" spans="1:8" ht="30" customHeight="1">
       <c r="A16" s="16" t="s">
         <v>78</v>
       </c>
@@ -4122,7 +4121,7 @@
       <c r="F16" s="25"/>
       <c r="G16" s="16"/>
     </row>
-    <row r="17" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="17" spans="1:8" ht="30" customHeight="1">
       <c r="A17" s="16" t="s">
         <v>370</v>
       </c>
@@ -4137,7 +4136,7 @@
       <c r="F17" s="25"/>
       <c r="G17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="18" spans="1:8" ht="30" customHeight="1">
       <c r="A18" s="16" t="s">
         <v>371</v>
       </c>
@@ -4152,7 +4151,7 @@
       <c r="F18" s="25"/>
       <c r="G18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="19" spans="1:8" ht="30" customHeight="1">
       <c r="A19" s="16" t="s">
         <v>79</v>
       </c>
@@ -4167,7 +4166,7 @@
       <c r="F19" s="25"/>
       <c r="G19" s="16"/>
     </row>
-    <row r="20" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="20" spans="1:8" ht="30" customHeight="1">
       <c r="A20" s="16" t="s">
         <v>80</v>
       </c>
@@ -4182,7 +4181,7 @@
       <c r="F20" s="25"/>
       <c r="G20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="21" spans="1:8" ht="30" customHeight="1">
       <c r="A21" s="16" t="s">
         <v>81</v>
       </c>
@@ -4197,7 +4196,7 @@
       <c r="F21" s="25"/>
       <c r="G21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="22" spans="1:8" ht="30" customHeight="1">
       <c r="A22" s="16" t="s">
         <v>82</v>
       </c>
@@ -4232,7 +4231,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="24" spans="1:8" ht="30" customHeight="1">
       <c r="A24" s="16" t="s">
         <v>83</v>
       </c>
@@ -4267,7 +4266,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="26" spans="1:8" ht="30" customHeight="1">
       <c r="A26" s="16" t="s">
         <v>84</v>
       </c>
@@ -4282,7 +4281,7 @@
       <c r="F26" s="25"/>
       <c r="G26" s="16"/>
     </row>
-    <row r="27" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="27" spans="1:8" ht="30" customHeight="1">
       <c r="A27" s="16" t="s">
         <v>85</v>
       </c>
@@ -4317,7 +4316,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="29" spans="1:8" ht="30" customHeight="1">
       <c r="A29" s="16" t="s">
         <v>86</v>
       </c>
@@ -4332,7 +4331,7 @@
       <c r="F29" s="25"/>
       <c r="G29" s="16"/>
     </row>
-    <row r="30" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="30" spans="1:8" ht="30" customHeight="1">
       <c r="A30" s="16" t="s">
         <v>87</v>
       </c>
@@ -4347,7 +4346,7 @@
       <c r="F30" s="25"/>
       <c r="G30" s="16"/>
     </row>
-    <row r="31" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="31" spans="1:8" ht="30" customHeight="1">
       <c r="A31" s="16" t="s">
         <v>88</v>
       </c>
@@ -4362,7 +4361,7 @@
       <c r="F31" s="25"/>
       <c r="G31" s="16"/>
     </row>
-    <row r="32" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="32" spans="1:8" ht="30" customHeight="1">
       <c r="A32" s="16" t="s">
         <v>89</v>
       </c>
@@ -4437,7 +4436,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="36" spans="1:8" ht="30" customHeight="1">
       <c r="A36" s="16" t="s">
         <v>372</v>
       </c>
@@ -4452,7 +4451,7 @@
       <c r="F36" s="25"/>
       <c r="G36" s="19"/>
     </row>
-    <row r="37" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="37" spans="1:8" ht="30" customHeight="1">
       <c r="A37" s="16" t="s">
         <v>91</v>
       </c>
@@ -4467,7 +4466,7 @@
       <c r="F37" s="25"/>
       <c r="G37" s="19"/>
     </row>
-    <row r="38" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="38" spans="1:8" ht="30" customHeight="1">
       <c r="A38" s="16" t="s">
         <v>373</v>
       </c>
@@ -4562,7 +4561,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="43" spans="1:8" ht="30" customHeight="1">
       <c r="A43" s="16" t="s">
         <v>96</v>
       </c>
@@ -4597,7 +4596,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="45" spans="1:8" ht="30" customHeight="1">
       <c r="A45" s="16" t="s">
         <v>98</v>
       </c>
@@ -4612,7 +4611,7 @@
       <c r="F45" s="25"/>
       <c r="G45" s="16"/>
     </row>
-    <row r="46" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="46" spans="1:8" ht="30" customHeight="1">
       <c r="A46" s="16" t="s">
         <v>99</v>
       </c>
@@ -4627,7 +4626,7 @@
       <c r="F46" s="25"/>
       <c r="G46" s="19"/>
     </row>
-    <row r="47" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="47" spans="1:8" ht="30" customHeight="1">
       <c r="A47" s="16" t="s">
         <v>100</v>
       </c>
@@ -4642,7 +4641,7 @@
       <c r="F47" s="25"/>
       <c r="G47" s="16"/>
     </row>
-    <row r="48" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="48" spans="1:8" ht="30" customHeight="1">
       <c r="A48" s="16" t="s">
         <v>101</v>
       </c>
@@ -4677,7 +4676,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="50" spans="1:8" ht="30" customHeight="1">
       <c r="A50" s="16" t="s">
         <v>103</v>
       </c>
@@ -4712,7 +4711,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="52" spans="1:8" ht="30" customHeight="1">
       <c r="A52" s="16" t="s">
         <v>105</v>
       </c>
@@ -4787,7 +4786,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="56" spans="1:8" ht="30" customHeight="1">
       <c r="A56" s="16" t="s">
         <v>108</v>
       </c>
@@ -4802,7 +4801,7 @@
       <c r="F56" s="25"/>
       <c r="G56" s="19"/>
     </row>
-    <row r="57" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="57" spans="1:8" ht="30" customHeight="1">
       <c r="A57" s="16" t="s">
         <v>109</v>
       </c>
@@ -4817,7 +4816,7 @@
       <c r="F57" s="25"/>
       <c r="G57" s="19"/>
     </row>
-    <row r="58" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="58" spans="1:8" ht="30" customHeight="1">
       <c r="A58" s="16" t="s">
         <v>375</v>
       </c>
@@ -4832,7 +4831,7 @@
       <c r="F58" s="16"/>
       <c r="G58" s="16"/>
     </row>
-    <row r="59" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="59" spans="1:8" ht="30" customHeight="1">
       <c r="A59" s="16" t="s">
         <v>110</v>
       </c>
@@ -4847,7 +4846,7 @@
       <c r="F59" s="16"/>
       <c r="G59" s="16"/>
     </row>
-    <row r="60" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="60" spans="1:8" ht="30" customHeight="1">
       <c r="A60" s="16" t="s">
         <v>376</v>
       </c>
@@ -5022,7 +5021,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="69" spans="1:8" ht="30" customHeight="1">
       <c r="A69" s="16" t="s">
         <v>116</v>
       </c>
@@ -5057,7 +5056,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="71" spans="1:8" ht="30" customHeight="1">
       <c r="A71" s="16" t="s">
         <v>117</v>
       </c>
@@ -5072,7 +5071,7 @@
       <c r="F71" s="16"/>
       <c r="G71" s="19"/>
     </row>
-    <row r="72" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="72" spans="1:8" ht="30" customHeight="1">
       <c r="A72" s="16" t="s">
         <v>118</v>
       </c>
@@ -5087,7 +5086,7 @@
       <c r="F72" s="25"/>
       <c r="G72" s="19"/>
     </row>
-    <row r="73" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="73" spans="1:8" ht="30" customHeight="1">
       <c r="A73" s="16" t="s">
         <v>379</v>
       </c>
@@ -5102,7 +5101,7 @@
       <c r="F73" s="16"/>
       <c r="G73" s="16"/>
     </row>
-    <row r="74" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="74" spans="1:8" ht="30" customHeight="1">
       <c r="A74" s="16" t="s">
         <v>119</v>
       </c>
@@ -5117,7 +5116,7 @@
       <c r="F74" s="25"/>
       <c r="G74" s="16"/>
     </row>
-    <row r="75" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="75" spans="1:8" ht="30" customHeight="1">
       <c r="A75" s="16" t="s">
         <v>120</v>
       </c>
@@ -5132,7 +5131,7 @@
       <c r="F75" s="25"/>
       <c r="G75" s="16"/>
     </row>
-    <row r="76" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="76" spans="1:8" ht="30" customHeight="1">
       <c r="A76" s="16" t="s">
         <v>121</v>
       </c>
@@ -5147,7 +5146,7 @@
       <c r="F76" s="25"/>
       <c r="G76" s="16"/>
     </row>
-    <row r="77" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="77" spans="1:8" ht="30" customHeight="1">
       <c r="A77" s="16" t="s">
         <v>122</v>
       </c>
@@ -5162,7 +5161,7 @@
       <c r="F77" s="25"/>
       <c r="G77" s="19"/>
     </row>
-    <row r="78" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="78" spans="1:8" ht="30" customHeight="1">
       <c r="A78" s="16" t="s">
         <v>123</v>
       </c>
@@ -5177,7 +5176,7 @@
       <c r="F78" s="25"/>
       <c r="G78" s="19"/>
     </row>
-    <row r="79" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="79" spans="1:8" ht="30" customHeight="1">
       <c r="A79" s="16" t="s">
         <v>124</v>
       </c>
@@ -5192,7 +5191,7 @@
       <c r="F79" s="16"/>
       <c r="G79" s="19"/>
     </row>
-    <row r="80" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="80" spans="1:8" ht="30" customHeight="1">
       <c r="A80" s="16" t="s">
         <v>125</v>
       </c>
@@ -5207,7 +5206,7 @@
       <c r="F80" s="25"/>
       <c r="G80" s="19"/>
     </row>
-    <row r="81" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="81" spans="1:8" ht="30" customHeight="1">
       <c r="A81" s="16" t="s">
         <v>126</v>
       </c>
@@ -5222,7 +5221,7 @@
       <c r="F81" s="25"/>
       <c r="G81" s="19"/>
     </row>
-    <row r="82" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="82" spans="1:8" ht="30" customHeight="1">
       <c r="A82" s="16" t="s">
         <v>127</v>
       </c>
@@ -5237,7 +5236,7 @@
       <c r="F82" s="25"/>
       <c r="G82" s="19"/>
     </row>
-    <row r="83" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="83" spans="1:8" ht="30" customHeight="1">
       <c r="A83" s="16" t="s">
         <v>335</v>
       </c>
@@ -5252,7 +5251,7 @@
       <c r="F83" s="16"/>
       <c r="G83" s="16"/>
     </row>
-    <row r="84" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="84" spans="1:8" ht="30" customHeight="1">
       <c r="A84" s="16" t="s">
         <v>128</v>
       </c>
@@ -5267,7 +5266,7 @@
       <c r="F84" s="16"/>
       <c r="G84" s="16"/>
     </row>
-    <row r="85" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="85" spans="1:8" ht="30" customHeight="1">
       <c r="A85" s="16" t="s">
         <v>129</v>
       </c>
@@ -5282,7 +5281,7 @@
       <c r="F85" s="25"/>
       <c r="G85" s="19"/>
     </row>
-    <row r="86" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="86" spans="1:8" ht="30" customHeight="1">
       <c r="A86" s="16" t="s">
         <v>130</v>
       </c>
@@ -5297,7 +5296,7 @@
       <c r="F86" s="25"/>
       <c r="G86" s="19"/>
     </row>
-    <row r="87" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="87" spans="1:8" ht="30" customHeight="1">
       <c r="A87" s="16" t="s">
         <v>131</v>
       </c>
@@ -5312,7 +5311,7 @@
       <c r="F87" s="25"/>
       <c r="G87" s="19"/>
     </row>
-    <row r="88" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="88" spans="1:8" ht="30" customHeight="1">
       <c r="A88" s="16" t="s">
         <v>341</v>
       </c>
@@ -5346,7 +5345,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="90" spans="1:8" ht="30" customHeight="1">
       <c r="A90" s="16" t="s">
         <v>132</v>
       </c>
@@ -5481,7 +5480,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="97" spans="1:8" ht="30" customHeight="1">
       <c r="A97" s="16" t="s">
         <v>139</v>
       </c>
@@ -5536,7 +5535,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="100" spans="1:8" ht="30" customHeight="1">
       <c r="A100" s="16" t="s">
         <v>141</v>
       </c>
@@ -5551,7 +5550,7 @@
       <c r="F100" s="25"/>
       <c r="G100" s="19"/>
     </row>
-    <row r="101" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="101" spans="1:8" ht="30" customHeight="1">
       <c r="A101" s="16" t="s">
         <v>142</v>
       </c>
@@ -5566,7 +5565,7 @@
       <c r="F101" s="25"/>
       <c r="G101" s="19"/>
     </row>
-    <row r="102" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="102" spans="1:8" ht="30" customHeight="1">
       <c r="A102" s="16" t="s">
         <v>143</v>
       </c>
@@ -5581,7 +5580,7 @@
       <c r="F102" s="16"/>
       <c r="G102" s="19"/>
     </row>
-    <row r="103" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="103" spans="1:8" ht="30" customHeight="1">
       <c r="A103" s="16" t="s">
         <v>144</v>
       </c>
@@ -5596,7 +5595,7 @@
       <c r="F103" s="25"/>
       <c r="G103" s="19"/>
     </row>
-    <row r="104" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="104" spans="1:8" ht="30" customHeight="1">
       <c r="A104" s="16" t="s">
         <v>145</v>
       </c>
@@ -5631,7 +5630,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="106" spans="1:8" ht="30" customHeight="1">
       <c r="A106" s="16" t="s">
         <v>146</v>
       </c>
@@ -5646,7 +5645,7 @@
       <c r="F106" s="16"/>
       <c r="G106" s="19"/>
     </row>
-    <row r="107" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="107" spans="1:8" ht="30" customHeight="1">
       <c r="A107" s="16" t="s">
         <v>147</v>
       </c>
@@ -5661,7 +5660,7 @@
       <c r="F107" s="25"/>
       <c r="G107" s="19"/>
     </row>
-    <row r="108" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="108" spans="1:8" ht="30" customHeight="1">
       <c r="A108" s="16" t="s">
         <v>148</v>
       </c>
@@ -5716,7 +5715,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="111" spans="1:8" ht="30" customHeight="1">
       <c r="A111" s="16" t="s">
         <v>149</v>
       </c>
@@ -5731,7 +5730,7 @@
       <c r="F111" s="25"/>
       <c r="G111" s="19"/>
     </row>
-    <row r="112" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="112" spans="1:8" ht="30" customHeight="1">
       <c r="A112" s="16" t="s">
         <v>150</v>
       </c>
@@ -5766,7 +5765,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="114" spans="1:8" ht="30" customHeight="1">
       <c r="A114" s="16" t="s">
         <v>380</v>
       </c>
@@ -5841,7 +5840,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="118" spans="1:8" ht="30" customHeight="1">
       <c r="A118" s="16" t="s">
         <v>151</v>
       </c>
@@ -5856,7 +5855,7 @@
       <c r="F118" s="25"/>
       <c r="G118" s="19"/>
     </row>
-    <row r="119" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="119" spans="1:8" ht="30" customHeight="1">
       <c r="A119" s="16" t="s">
         <v>152</v>
       </c>
@@ -5871,7 +5870,7 @@
       <c r="F119" s="25"/>
       <c r="G119" s="19"/>
     </row>
-    <row r="120" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="120" spans="1:8" ht="30" customHeight="1">
       <c r="A120" s="16" t="s">
         <v>153</v>
       </c>
@@ -6006,7 +6005,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="127" spans="1:8" ht="30" customHeight="1">
       <c r="A127" s="16" t="s">
         <v>158</v>
       </c>
@@ -6081,7 +6080,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="131" spans="1:8" ht="30" customHeight="1">
       <c r="A131" s="16" t="s">
         <v>495</v>
       </c>
@@ -6097,7 +6096,7 @@
       <c r="G131" s="19"/>
       <c r="H131" s="16"/>
     </row>
-    <row r="132" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="132" spans="1:8" ht="30" customHeight="1">
       <c r="A132" s="16" t="s">
         <v>161</v>
       </c>
@@ -6113,7 +6112,7 @@
       <c r="G132" s="19"/>
       <c r="H132" s="16"/>
     </row>
-    <row r="133" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="133" spans="1:8" ht="30" customHeight="1">
       <c r="A133" s="16" t="s">
         <v>381</v>
       </c>
@@ -6208,7 +6207,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="138" spans="1:8" ht="30" customHeight="1">
       <c r="A138" s="16" t="s">
         <v>164</v>
       </c>
@@ -6223,7 +6222,7 @@
       <c r="F138" s="25"/>
       <c r="G138" s="19"/>
     </row>
-    <row r="139" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="139" spans="1:8" ht="30" customHeight="1">
       <c r="A139" s="16" t="s">
         <v>165</v>
       </c>
@@ -6238,7 +6237,7 @@
       <c r="F139" s="16"/>
       <c r="G139" s="19"/>
     </row>
-    <row r="140" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="140" spans="1:8" ht="30" customHeight="1">
       <c r="A140" s="16" t="s">
         <v>166</v>
       </c>
@@ -6253,7 +6252,7 @@
       <c r="F140" s="25"/>
       <c r="G140" s="19"/>
     </row>
-    <row r="141" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="141" spans="1:8" ht="30" customHeight="1">
       <c r="A141" s="16" t="s">
         <v>382</v>
       </c>
@@ -6268,7 +6267,7 @@
       <c r="F141" s="25"/>
       <c r="G141" s="19"/>
     </row>
-    <row r="142" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="142" spans="1:8" ht="30" customHeight="1">
       <c r="A142" s="16" t="s">
         <v>383</v>
       </c>
@@ -6283,7 +6282,7 @@
       <c r="F142" s="25"/>
       <c r="G142" s="19"/>
     </row>
-    <row r="143" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="143" spans="1:8" ht="30" customHeight="1">
       <c r="A143" s="16" t="s">
         <v>167</v>
       </c>
@@ -6298,7 +6297,7 @@
       <c r="F143" s="16"/>
       <c r="G143" s="16"/>
     </row>
-    <row r="144" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="144" spans="1:8" ht="30" customHeight="1">
       <c r="A144" s="16" t="s">
         <v>384</v>
       </c>
@@ -6313,7 +6312,7 @@
       <c r="F144" s="25"/>
       <c r="G144" s="19"/>
     </row>
-    <row r="145" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="145" spans="1:8" ht="30" customHeight="1">
       <c r="A145" s="16" t="s">
         <v>385</v>
       </c>
@@ -6328,7 +6327,7 @@
       <c r="F145" s="25"/>
       <c r="G145" s="19"/>
     </row>
-    <row r="146" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="146" spans="1:8" ht="30" customHeight="1">
       <c r="A146" s="16" t="s">
         <v>168</v>
       </c>
@@ -6343,7 +6342,7 @@
       <c r="F146" s="25"/>
       <c r="G146" s="19"/>
     </row>
-    <row r="147" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="147" spans="1:8" ht="30" customHeight="1">
       <c r="A147" s="16" t="s">
         <v>169</v>
       </c>
@@ -6398,7 +6397,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="150" spans="1:8" ht="30" customHeight="1">
       <c r="A150" s="16" t="s">
         <v>333</v>
       </c>
@@ -6413,7 +6412,7 @@
       <c r="F150" s="16"/>
       <c r="G150" s="16"/>
     </row>
-    <row r="151" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="151" spans="1:8" ht="30" customHeight="1">
       <c r="A151" s="16" t="s">
         <v>386</v>
       </c>
@@ -6428,7 +6427,7 @@
       <c r="F151" s="25"/>
       <c r="G151" s="19"/>
     </row>
-    <row r="152" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="152" spans="1:8" ht="30" customHeight="1">
       <c r="A152" s="16" t="s">
         <v>387</v>
       </c>
@@ -6443,7 +6442,7 @@
       <c r="F152" s="16"/>
       <c r="G152" s="16"/>
     </row>
-    <row r="153" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="153" spans="1:8" ht="30" customHeight="1">
       <c r="A153" s="16" t="s">
         <v>388</v>
       </c>
@@ -6458,7 +6457,7 @@
       <c r="F153" s="25"/>
       <c r="G153" s="16"/>
     </row>
-    <row r="154" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="154" spans="1:8" ht="30" customHeight="1">
       <c r="A154" s="16" t="s">
         <v>172</v>
       </c>
@@ -6473,7 +6472,7 @@
       <c r="F154" s="25"/>
       <c r="G154" s="19"/>
     </row>
-    <row r="155" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="155" spans="1:8" ht="30" customHeight="1">
       <c r="A155" s="16" t="s">
         <v>173</v>
       </c>
@@ -6488,7 +6487,7 @@
       <c r="F155" s="25"/>
       <c r="G155" s="16"/>
     </row>
-    <row r="156" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="156" spans="1:8" ht="30" customHeight="1">
       <c r="A156" s="16" t="s">
         <v>174</v>
       </c>
@@ -6643,7 +6642,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="164" spans="1:8" ht="30" customHeight="1">
       <c r="A164" s="16" t="s">
         <v>175</v>
       </c>
@@ -6658,7 +6657,7 @@
       <c r="F164" s="25"/>
       <c r="G164" s="16"/>
     </row>
-    <row r="165" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="165" spans="1:8" ht="30" customHeight="1">
       <c r="A165" s="16" t="s">
         <v>394</v>
       </c>
@@ -6673,7 +6672,7 @@
       <c r="F165" s="25"/>
       <c r="G165" s="16"/>
     </row>
-    <row r="166" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="166" spans="1:8" ht="30" customHeight="1">
       <c r="A166" s="16" t="s">
         <v>176</v>
       </c>
@@ -6688,7 +6687,7 @@
       <c r="F166" s="25"/>
       <c r="G166" s="16"/>
     </row>
-    <row r="167" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="167" spans="1:8" ht="30" customHeight="1">
       <c r="A167" s="16" t="s">
         <v>395</v>
       </c>
@@ -6703,7 +6702,7 @@
       <c r="F167" s="25"/>
       <c r="G167" s="16"/>
     </row>
-    <row r="168" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="168" spans="1:8" ht="30" customHeight="1">
       <c r="A168" s="16" t="s">
         <v>177</v>
       </c>
@@ -6718,7 +6717,7 @@
       <c r="F168" s="25"/>
       <c r="G168" s="16"/>
     </row>
-    <row r="169" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="169" spans="1:8" ht="30" customHeight="1">
       <c r="A169" s="16" t="s">
         <v>396</v>
       </c>
@@ -6733,7 +6732,7 @@
       <c r="F169" s="25"/>
       <c r="G169" s="16"/>
     </row>
-    <row r="170" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="170" spans="1:8" ht="30" customHeight="1">
       <c r="A170" s="16" t="s">
         <v>178</v>
       </c>
@@ -6748,7 +6747,7 @@
       <c r="F170" s="25"/>
       <c r="G170" s="16"/>
     </row>
-    <row r="171" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="171" spans="1:8" ht="30" customHeight="1">
       <c r="A171" s="16" t="s">
         <v>179</v>
       </c>
@@ -6823,7 +6822,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="175" spans="1:8" ht="30" customHeight="1">
       <c r="A175" s="16" t="s">
         <v>398</v>
       </c>
@@ -6838,7 +6837,7 @@
       <c r="F175" s="16"/>
       <c r="G175" s="19"/>
     </row>
-    <row r="176" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="176" spans="1:8" ht="30" customHeight="1">
       <c r="A176" s="16" t="s">
         <v>399</v>
       </c>
@@ -6973,7 +6972,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="183" spans="1:8" ht="30" customHeight="1">
       <c r="A183" s="16" t="s">
         <v>406</v>
       </c>
@@ -6988,7 +6987,7 @@
       <c r="F183" s="25"/>
       <c r="G183" s="16"/>
     </row>
-    <row r="184" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="184" spans="1:8" ht="30" customHeight="1">
       <c r="A184" s="16" t="s">
         <v>180</v>
       </c>
@@ -7003,7 +7002,7 @@
       <c r="F184" s="25"/>
       <c r="G184" s="16"/>
     </row>
-    <row r="185" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="185" spans="1:8" ht="30" customHeight="1">
       <c r="A185" s="16" t="s">
         <v>181</v>
       </c>
@@ -7018,7 +7017,7 @@
       <c r="F185" s="25"/>
       <c r="G185" s="16"/>
     </row>
-    <row r="186" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="186" spans="1:8" ht="30" customHeight="1">
       <c r="A186" s="16" t="s">
         <v>182</v>
       </c>
@@ -7033,7 +7032,7 @@
       <c r="F186" s="25"/>
       <c r="G186" s="16"/>
     </row>
-    <row r="187" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="187" spans="1:8" ht="30" customHeight="1">
       <c r="A187" s="16" t="s">
         <v>183</v>
       </c>
@@ -7048,7 +7047,7 @@
       <c r="F187" s="16"/>
       <c r="G187" s="16"/>
     </row>
-    <row r="188" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="188" spans="1:8" ht="30" customHeight="1">
       <c r="A188" s="16" t="s">
         <v>184</v>
       </c>
@@ -7063,7 +7062,7 @@
       <c r="F188" s="16"/>
       <c r="G188" s="16"/>
     </row>
-    <row r="189" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="189" spans="1:8" ht="30" customHeight="1">
       <c r="A189" s="16" t="s">
         <v>185</v>
       </c>
@@ -7078,7 +7077,7 @@
       <c r="F189" s="16"/>
       <c r="G189" s="16"/>
     </row>
-    <row r="190" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="190" spans="1:8" ht="30" customHeight="1">
       <c r="A190" s="16" t="s">
         <v>407</v>
       </c>
@@ -7093,7 +7092,7 @@
       <c r="F190" s="16"/>
       <c r="G190" s="16"/>
     </row>
-    <row r="191" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="191" spans="1:8" ht="30" customHeight="1">
       <c r="A191" s="16" t="s">
         <v>186</v>
       </c>
@@ -7108,7 +7107,7 @@
       <c r="F191" s="25"/>
       <c r="G191" s="16"/>
     </row>
-    <row r="192" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="192" spans="1:8" ht="30" customHeight="1">
       <c r="A192" s="16" t="s">
         <v>187</v>
       </c>
@@ -7123,7 +7122,7 @@
       <c r="F192" s="25"/>
       <c r="G192" s="16"/>
     </row>
-    <row r="193" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="193" spans="1:8" ht="30" customHeight="1">
       <c r="A193" s="16" t="s">
         <v>188</v>
       </c>
@@ -7138,7 +7137,7 @@
       <c r="F193" s="25"/>
       <c r="G193" s="16"/>
     </row>
-    <row r="194" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="194" spans="1:8" ht="30" customHeight="1">
       <c r="A194" s="16" t="s">
         <v>189</v>
       </c>
@@ -7153,7 +7152,7 @@
       <c r="F194" s="25"/>
       <c r="G194" s="19"/>
     </row>
-    <row r="195" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="195" spans="1:8" ht="30" customHeight="1">
       <c r="A195" s="16" t="s">
         <v>190</v>
       </c>
@@ -7248,7 +7247,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="200" spans="1:8" s="13" customFormat="1" ht="30" hidden="1" customHeight="1">
+    <row r="200" spans="1:8" s="13" customFormat="1" ht="30" customHeight="1">
       <c r="A200" s="16" t="s">
         <v>359</v>
       </c>
@@ -7965,7 +7964,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="236" spans="1:8" ht="30" customHeight="1">
       <c r="A236" s="16" t="s">
         <v>216</v>
       </c>
@@ -7980,7 +7979,7 @@
       <c r="F236" s="25"/>
       <c r="G236" s="19"/>
     </row>
-    <row r="237" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="237" spans="1:8" ht="30" customHeight="1">
       <c r="A237" s="16" t="s">
         <v>471</v>
       </c>
@@ -7995,7 +7994,7 @@
       <c r="F237" s="25"/>
       <c r="G237" s="19"/>
     </row>
-    <row r="238" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="238" spans="1:8" ht="30" customHeight="1">
       <c r="A238" s="16" t="s">
         <v>217</v>
       </c>
@@ -8010,7 +8009,7 @@
       <c r="F238" s="25"/>
       <c r="G238" s="19"/>
     </row>
-    <row r="239" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="239" spans="1:8" ht="30" customHeight="1">
       <c r="A239" s="16" t="s">
         <v>218</v>
       </c>
@@ -8025,7 +8024,7 @@
       <c r="F239" s="25"/>
       <c r="G239" s="19"/>
     </row>
-    <row r="240" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="240" spans="1:8" ht="30" customHeight="1">
       <c r="A240" s="16" t="s">
         <v>219</v>
       </c>
@@ -8040,7 +8039,7 @@
       <c r="F240" s="25"/>
       <c r="G240" s="19"/>
     </row>
-    <row r="241" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="241" spans="1:8" ht="30" customHeight="1">
       <c r="A241" s="16" t="s">
         <v>220</v>
       </c>
@@ -8055,7 +8054,7 @@
       <c r="F241" s="25"/>
       <c r="G241" s="19"/>
     </row>
-    <row r="242" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="242" spans="1:8" ht="30" customHeight="1">
       <c r="A242" s="16" t="s">
         <v>221</v>
       </c>
@@ -8070,7 +8069,7 @@
       <c r="F242" s="25"/>
       <c r="G242" s="19"/>
     </row>
-    <row r="243" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="243" spans="1:8" ht="30" customHeight="1">
       <c r="A243" s="16" t="s">
         <v>222</v>
       </c>
@@ -8085,7 +8084,7 @@
       <c r="F243" s="25"/>
       <c r="G243" s="19"/>
     </row>
-    <row r="244" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="244" spans="1:8" ht="30" customHeight="1">
       <c r="A244" s="16" t="s">
         <v>223</v>
       </c>
@@ -8100,7 +8099,7 @@
       <c r="F244" s="16"/>
       <c r="G244" s="19"/>
     </row>
-    <row r="245" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="245" spans="1:8" ht="30" customHeight="1">
       <c r="A245" s="16" t="s">
         <v>224</v>
       </c>
@@ -8115,7 +8114,7 @@
       <c r="F245" s="25"/>
       <c r="G245" s="19"/>
     </row>
-    <row r="246" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="246" spans="1:8" ht="30" customHeight="1">
       <c r="A246" s="16" t="s">
         <v>225</v>
       </c>
@@ -8130,7 +8129,7 @@
       <c r="F246" s="25"/>
       <c r="G246" s="19"/>
     </row>
-    <row r="247" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="247" spans="1:8" ht="30" customHeight="1">
       <c r="A247" s="16" t="s">
         <v>226</v>
       </c>
@@ -8165,7 +8164,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="249" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="249" spans="1:8" ht="30" customHeight="1">
       <c r="A249" s="16" t="s">
         <v>227</v>
       </c>
@@ -8180,7 +8179,7 @@
       <c r="F249" s="16"/>
       <c r="G249" s="16"/>
     </row>
-    <row r="250" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="250" spans="1:8" ht="30" customHeight="1">
       <c r="A250" s="16" t="s">
         <v>228</v>
       </c>
@@ -8195,7 +8194,7 @@
       <c r="F250" s="25"/>
       <c r="G250" s="19"/>
     </row>
-    <row r="251" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="251" spans="1:8" ht="30" customHeight="1">
       <c r="A251" s="16" t="s">
         <v>229</v>
       </c>
@@ -8310,7 +8309,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="257" spans="1:8" ht="30" customHeight="1">
       <c r="A257" s="16" t="s">
         <v>337</v>
       </c>
@@ -8345,7 +8344,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="259" spans="1:8" ht="30" customHeight="1">
       <c r="A259" s="16" t="s">
         <v>231</v>
       </c>
@@ -8380,7 +8379,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="261" spans="1:8" ht="30" customHeight="1">
       <c r="A261" s="16" t="s">
         <v>232</v>
       </c>
@@ -8395,7 +8394,7 @@
       <c r="F261" s="16"/>
       <c r="G261" s="16"/>
     </row>
-    <row r="262" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="262" spans="1:8" ht="30" customHeight="1">
       <c r="A262" s="16" t="s">
         <v>233</v>
       </c>
@@ -8430,7 +8429,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="264" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="264" spans="1:8" ht="30" customHeight="1">
       <c r="A264" s="16" t="s">
         <v>342</v>
       </c>
@@ -8445,7 +8444,7 @@
       <c r="F264" s="16"/>
       <c r="G264" s="16"/>
     </row>
-    <row r="265" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="265" spans="1:8" ht="30" customHeight="1">
       <c r="A265" s="16" t="s">
         <v>234</v>
       </c>
@@ -8520,7 +8519,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="269" spans="1:8" ht="30" customHeight="1">
       <c r="A269" s="16" t="s">
         <v>236</v>
       </c>
@@ -8535,7 +8534,7 @@
       <c r="F269" s="16"/>
       <c r="G269" s="16"/>
     </row>
-    <row r="270" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="270" spans="1:8" ht="30" customHeight="1">
       <c r="A270" s="16" t="s">
         <v>237</v>
       </c>
@@ -8550,7 +8549,7 @@
       <c r="F270" s="16"/>
       <c r="G270" s="16"/>
     </row>
-    <row r="271" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="271" spans="1:8" ht="30" customHeight="1">
       <c r="A271" s="16" t="s">
         <v>238</v>
       </c>
@@ -8585,7 +8584,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="273" spans="1:8" ht="30" customHeight="1">
       <c r="A273" s="16" t="s">
         <v>240</v>
       </c>
@@ -8600,7 +8599,7 @@
       <c r="F273" s="16"/>
       <c r="G273" s="16"/>
     </row>
-    <row r="274" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="274" spans="1:8" ht="30" customHeight="1">
       <c r="A274" s="16" t="s">
         <v>241</v>
       </c>
@@ -8633,7 +8632,7 @@
       </c>
       <c r="H275" s="16"/>
     </row>
-    <row r="276" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="276" spans="1:8" ht="30" customHeight="1">
       <c r="A276" s="16" t="s">
         <v>442</v>
       </c>
@@ -8648,1462 +8647,1462 @@
       <c r="F276" s="16"/>
       <c r="G276" s="16"/>
     </row>
-    <row r="277" spans="1:8" hidden="1">
+    <row r="277" spans="1:8">
       <c r="C277" s="5"/>
       <c r="G277"/>
     </row>
-    <row r="278" spans="1:8" hidden="1">
+    <row r="278" spans="1:8">
       <c r="C278" s="5"/>
       <c r="G278"/>
     </row>
-    <row r="279" spans="1:8" hidden="1">
+    <row r="279" spans="1:8">
       <c r="C279" s="5"/>
       <c r="G279"/>
     </row>
-    <row r="280" spans="1:8" hidden="1">
+    <row r="280" spans="1:8">
       <c r="B280" s="13"/>
       <c r="C280" s="15"/>
       <c r="G280" s="13"/>
     </row>
-    <row r="281" spans="1:8" hidden="1">
+    <row r="281" spans="1:8">
       <c r="B281" s="13"/>
       <c r="C281" s="15"/>
       <c r="G281" s="13"/>
     </row>
-    <row r="282" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="282" spans="1:8" ht="30" customHeight="1">
       <c r="B282" s="13"/>
       <c r="C282" s="15"/>
       <c r="G282" s="14"/>
     </row>
-    <row r="283" spans="1:8" hidden="1">
+    <row r="283" spans="1:8">
       <c r="B283" s="13"/>
       <c r="C283" s="15"/>
       <c r="G283" s="14"/>
     </row>
-    <row r="284" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="284" spans="1:8" ht="30" customHeight="1">
       <c r="C284" s="5"/>
       <c r="D284" s="5"/>
       <c r="E284" s="12"/>
       <c r="F284" s="5"/>
       <c r="G284" s="14"/>
     </row>
-    <row r="285" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="285" spans="1:8" ht="30" customHeight="1">
       <c r="A285" s="13"/>
       <c r="B285" s="13"/>
       <c r="C285" s="15"/>
       <c r="G285" s="14"/>
     </row>
-    <row r="286" spans="1:8" ht="30" hidden="1" customHeight="1">
+    <row r="286" spans="1:8" ht="30" customHeight="1">
       <c r="B286" s="13"/>
       <c r="C286" s="15"/>
       <c r="G286" s="14"/>
     </row>
-    <row r="287" spans="1:8" hidden="1">
+    <row r="287" spans="1:8">
       <c r="B287" s="13"/>
       <c r="C287" s="15"/>
       <c r="G287" s="13"/>
     </row>
-    <row r="288" spans="1:8" hidden="1">
+    <row r="288" spans="1:8">
       <c r="B288" s="13"/>
       <c r="C288" s="15"/>
       <c r="G288" s="13"/>
     </row>
-    <row r="289" spans="1:7" hidden="1">
+    <row r="289" spans="1:7">
       <c r="C289" s="5"/>
       <c r="G289"/>
     </row>
-    <row r="290" spans="1:7" hidden="1">
+    <row r="290" spans="1:7">
       <c r="C290" s="5"/>
       <c r="G290"/>
     </row>
-    <row r="291" spans="1:7" hidden="1">
+    <row r="291" spans="1:7">
       <c r="C291" s="5"/>
       <c r="G291"/>
     </row>
-    <row r="292" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="292" spans="1:7" ht="30" customHeight="1">
       <c r="B292" s="13"/>
       <c r="C292" s="15"/>
       <c r="E292" s="14"/>
       <c r="G292" s="14"/>
     </row>
-    <row r="293" spans="1:7" hidden="1">
+    <row r="293" spans="1:7">
       <c r="C293" s="5"/>
       <c r="G293"/>
     </row>
-    <row r="294" spans="1:7" hidden="1">
+    <row r="294" spans="1:7">
       <c r="C294" s="5"/>
       <c r="G294"/>
     </row>
-    <row r="295" spans="1:7" hidden="1">
+    <row r="295" spans="1:7">
       <c r="C295" s="5"/>
       <c r="G295"/>
     </row>
-    <row r="296" spans="1:7" hidden="1">
+    <row r="296" spans="1:7">
       <c r="C296" s="5"/>
       <c r="G296"/>
     </row>
-    <row r="297" spans="1:7" hidden="1">
+    <row r="297" spans="1:7">
       <c r="B297" s="13"/>
       <c r="C297" s="15"/>
       <c r="G297" s="14"/>
     </row>
-    <row r="298" spans="1:7" hidden="1">
+    <row r="298" spans="1:7">
       <c r="B298" s="13"/>
       <c r="C298" s="15"/>
       <c r="G298" s="13"/>
     </row>
-    <row r="299" spans="1:7" hidden="1">
+    <row r="299" spans="1:7">
       <c r="B299" s="13"/>
       <c r="C299" s="15"/>
       <c r="G299" s="13"/>
     </row>
-    <row r="300" spans="1:7" hidden="1">
+    <row r="300" spans="1:7">
       <c r="B300" s="13"/>
       <c r="C300" s="15"/>
       <c r="G300" s="13"/>
     </row>
-    <row r="301" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="301" spans="1:7" ht="30" customHeight="1">
       <c r="B301" s="13"/>
       <c r="C301" s="15"/>
       <c r="G301" s="14"/>
     </row>
-    <row r="302" spans="1:7" hidden="1">
+    <row r="302" spans="1:7">
       <c r="A302" s="13"/>
       <c r="B302" s="13"/>
       <c r="C302" s="15"/>
       <c r="G302" s="14"/>
     </row>
-    <row r="303" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="303" spans="1:7" ht="30" customHeight="1">
       <c r="B303" s="13"/>
       <c r="C303" s="15"/>
       <c r="G303" s="14"/>
     </row>
-    <row r="304" spans="1:7" hidden="1">
+    <row r="304" spans="1:7">
       <c r="B304" s="13"/>
       <c r="C304" s="15"/>
       <c r="G304" s="14"/>
     </row>
-    <row r="305" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="305" spans="1:7" ht="30" customHeight="1">
       <c r="B305" s="13"/>
       <c r="C305" s="15"/>
       <c r="G305" s="14"/>
     </row>
-    <row r="306" spans="1:7" hidden="1">
+    <row r="306" spans="1:7">
       <c r="B306" s="13"/>
       <c r="C306" s="15"/>
       <c r="G306" s="14"/>
     </row>
-    <row r="307" spans="1:7" hidden="1">
+    <row r="307" spans="1:7">
       <c r="B307" s="13"/>
       <c r="C307" s="15"/>
       <c r="G307" s="14"/>
     </row>
-    <row r="308" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="308" spans="1:7" ht="30" customHeight="1">
       <c r="B308" s="13"/>
       <c r="C308" s="15"/>
       <c r="G308" s="14"/>
     </row>
-    <row r="309" spans="1:7" hidden="1">
+    <row r="309" spans="1:7">
       <c r="A309" s="13"/>
       <c r="B309" s="13"/>
       <c r="C309" s="15"/>
       <c r="G309" s="13"/>
     </row>
-    <row r="310" spans="1:7" hidden="1">
+    <row r="310" spans="1:7">
       <c r="B310" s="13"/>
       <c r="C310" s="15"/>
       <c r="G310" s="13"/>
     </row>
-    <row r="311" spans="1:7" hidden="1">
+    <row r="311" spans="1:7">
       <c r="B311" s="13"/>
       <c r="C311" s="15"/>
       <c r="G311" s="13"/>
     </row>
-    <row r="312" spans="1:7" hidden="1">
+    <row r="312" spans="1:7">
       <c r="B312" s="13"/>
       <c r="C312" s="15"/>
       <c r="G312" s="13"/>
     </row>
-    <row r="313" spans="1:7" hidden="1">
+    <row r="313" spans="1:7">
       <c r="B313" s="13"/>
       <c r="C313" s="15"/>
       <c r="G313" s="13"/>
     </row>
-    <row r="314" spans="1:7" hidden="1">
+    <row r="314" spans="1:7">
       <c r="B314" s="13"/>
       <c r="C314" s="15"/>
       <c r="G314" s="13"/>
     </row>
-    <row r="315" spans="1:7" hidden="1">
+    <row r="315" spans="1:7">
       <c r="B315" s="13"/>
       <c r="C315" s="15"/>
       <c r="G315" s="13"/>
     </row>
-    <row r="316" spans="1:7" hidden="1">
+    <row r="316" spans="1:7">
       <c r="B316" s="13"/>
       <c r="C316" s="15"/>
       <c r="G316" s="13"/>
     </row>
-    <row r="317" spans="1:7" hidden="1">
+    <row r="317" spans="1:7">
       <c r="B317" s="13"/>
       <c r="C317" s="15"/>
       <c r="G317" s="14"/>
     </row>
-    <row r="318" spans="1:7" hidden="1">
+    <row r="318" spans="1:7">
       <c r="B318" s="13"/>
       <c r="C318" s="15"/>
       <c r="G318" s="14"/>
     </row>
-    <row r="319" spans="1:7" hidden="1">
+    <row r="319" spans="1:7">
       <c r="B319" s="13"/>
       <c r="C319" s="15"/>
       <c r="G319" s="13"/>
     </row>
-    <row r="320" spans="1:7" hidden="1">
+    <row r="320" spans="1:7">
       <c r="B320" s="13"/>
       <c r="C320" s="15"/>
       <c r="G320" s="13"/>
     </row>
-    <row r="321" spans="2:7" hidden="1">
+    <row r="321" spans="2:7">
       <c r="B321" s="13"/>
       <c r="C321" s="15"/>
       <c r="G321"/>
     </row>
-    <row r="322" spans="2:7" hidden="1">
+    <row r="322" spans="2:7">
       <c r="B322" s="13"/>
       <c r="C322" s="15"/>
       <c r="G322" s="13"/>
     </row>
-    <row r="323" spans="2:7" hidden="1">
+    <row r="323" spans="2:7">
       <c r="B323" s="13"/>
       <c r="C323" s="15"/>
       <c r="G323" s="13"/>
     </row>
-    <row r="324" spans="2:7" hidden="1">
+    <row r="324" spans="2:7">
       <c r="B324" s="13"/>
       <c r="C324" s="15"/>
       <c r="G324" s="13"/>
     </row>
-    <row r="325" spans="2:7" hidden="1">
+    <row r="325" spans="2:7">
       <c r="B325" s="13"/>
       <c r="C325" s="15"/>
       <c r="G325" s="13"/>
     </row>
-    <row r="326" spans="2:7" hidden="1">
+    <row r="326" spans="2:7">
       <c r="B326" s="13"/>
       <c r="C326" s="15"/>
       <c r="G326" s="13"/>
     </row>
-    <row r="327" spans="2:7" hidden="1">
+    <row r="327" spans="2:7">
       <c r="B327" s="13"/>
       <c r="C327" s="15"/>
       <c r="G327" s="13"/>
     </row>
-    <row r="328" spans="2:7" hidden="1">
+    <row r="328" spans="2:7">
       <c r="B328" s="13"/>
       <c r="C328" s="15"/>
       <c r="G328" s="13"/>
     </row>
-    <row r="329" spans="2:7" hidden="1">
+    <row r="329" spans="2:7">
       <c r="C329" s="5"/>
       <c r="G329"/>
     </row>
-    <row r="330" spans="2:7" hidden="1">
+    <row r="330" spans="2:7">
       <c r="C330" s="5"/>
       <c r="G330"/>
     </row>
-    <row r="331" spans="2:7" hidden="1">
+    <row r="331" spans="2:7">
       <c r="C331" s="5"/>
       <c r="G331"/>
     </row>
-    <row r="332" spans="2:7" hidden="1">
+    <row r="332" spans="2:7">
       <c r="C332" s="5"/>
       <c r="G332"/>
     </row>
-    <row r="333" spans="2:7" hidden="1">
+    <row r="333" spans="2:7">
       <c r="C333" s="5"/>
       <c r="G333"/>
     </row>
-    <row r="334" spans="2:7" hidden="1">
+    <row r="334" spans="2:7">
       <c r="C334" s="5"/>
       <c r="G334"/>
     </row>
-    <row r="335" spans="2:7" hidden="1">
+    <row r="335" spans="2:7">
       <c r="C335" s="5"/>
       <c r="G335"/>
     </row>
-    <row r="336" spans="2:7" hidden="1">
+    <row r="336" spans="2:7">
       <c r="C336" s="5"/>
       <c r="G336"/>
     </row>
-    <row r="337" spans="3:7" ht="12.75" hidden="1" customHeight="1">
+    <row r="337" spans="3:7" ht="12.75" customHeight="1">
       <c r="C337" s="5"/>
       <c r="G337"/>
     </row>
-    <row r="338" spans="3:7" hidden="1">
+    <row r="338" spans="3:7">
       <c r="C338" s="5"/>
       <c r="G338"/>
     </row>
-    <row r="339" spans="3:7" hidden="1">
+    <row r="339" spans="3:7">
       <c r="C339" s="5"/>
       <c r="G339"/>
     </row>
-    <row r="340" spans="3:7" hidden="1">
+    <row r="340" spans="3:7">
       <c r="C340" s="5"/>
       <c r="G340"/>
     </row>
-    <row r="341" spans="3:7" hidden="1">
+    <row r="341" spans="3:7">
       <c r="C341" s="5"/>
       <c r="G341"/>
     </row>
-    <row r="342" spans="3:7" hidden="1">
+    <row r="342" spans="3:7">
       <c r="C342" s="5"/>
       <c r="G342"/>
     </row>
-    <row r="343" spans="3:7" hidden="1">
+    <row r="343" spans="3:7">
       <c r="C343" s="5"/>
       <c r="G343"/>
     </row>
-    <row r="344" spans="3:7" hidden="1">
+    <row r="344" spans="3:7">
       <c r="C344" s="5"/>
       <c r="G344"/>
     </row>
-    <row r="345" spans="3:7" hidden="1">
+    <row r="345" spans="3:7">
       <c r="C345" s="5"/>
       <c r="G345"/>
     </row>
-    <row r="346" spans="3:7" hidden="1">
+    <row r="346" spans="3:7">
       <c r="C346" s="5"/>
       <c r="G346"/>
     </row>
-    <row r="347" spans="3:7" hidden="1">
+    <row r="347" spans="3:7">
       <c r="C347" s="5"/>
       <c r="G347"/>
     </row>
-    <row r="348" spans="3:7" hidden="1">
+    <row r="348" spans="3:7">
       <c r="C348" s="5"/>
       <c r="G348"/>
     </row>
-    <row r="349" spans="3:7" hidden="1">
+    <row r="349" spans="3:7">
       <c r="C349" s="5"/>
       <c r="G349"/>
     </row>
-    <row r="350" spans="3:7" hidden="1">
+    <row r="350" spans="3:7">
       <c r="C350" s="5"/>
       <c r="G350"/>
     </row>
-    <row r="351" spans="3:7" hidden="1">
+    <row r="351" spans="3:7">
       <c r="C351" s="5"/>
       <c r="G351"/>
     </row>
-    <row r="352" spans="3:7" ht="12.75" hidden="1" customHeight="1">
+    <row r="352" spans="3:7" ht="12.75" customHeight="1">
       <c r="C352" s="5"/>
       <c r="G352"/>
     </row>
-    <row r="353" spans="2:7" hidden="1">
+    <row r="353" spans="2:7">
       <c r="B353" s="13"/>
       <c r="C353" s="15"/>
       <c r="G353" s="14"/>
     </row>
-    <row r="354" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="354" spans="2:7" ht="30" customHeight="1">
       <c r="B354" s="13"/>
       <c r="C354" s="15"/>
       <c r="G354" s="14"/>
     </row>
-    <row r="355" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="355" spans="2:7" ht="30" customHeight="1">
       <c r="B355" s="13"/>
       <c r="C355" s="15"/>
       <c r="E355" s="14"/>
       <c r="G355" s="14"/>
     </row>
-    <row r="356" spans="2:7" hidden="1">
+    <row r="356" spans="2:7">
       <c r="B356" s="13"/>
       <c r="C356" s="15"/>
       <c r="G356" s="13"/>
     </row>
-    <row r="357" spans="2:7" hidden="1">
+    <row r="357" spans="2:7">
       <c r="B357" s="13"/>
       <c r="C357" s="15"/>
       <c r="G357" s="13"/>
     </row>
-    <row r="358" spans="2:7" hidden="1">
+    <row r="358" spans="2:7">
       <c r="B358" s="13"/>
       <c r="C358" s="15"/>
       <c r="G358" s="13"/>
     </row>
-    <row r="359" spans="2:7" hidden="1">
+    <row r="359" spans="2:7">
       <c r="B359" s="13"/>
       <c r="C359" s="15"/>
       <c r="G359" s="13"/>
     </row>
-    <row r="360" spans="2:7" hidden="1">
+    <row r="360" spans="2:7">
       <c r="B360" s="13"/>
       <c r="C360" s="15"/>
       <c r="G360" s="13"/>
     </row>
-    <row r="361" spans="2:7" hidden="1">
+    <row r="361" spans="2:7">
       <c r="B361" s="13"/>
       <c r="C361" s="15"/>
       <c r="G361" s="13"/>
     </row>
-    <row r="362" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="362" spans="2:7" ht="30" customHeight="1">
       <c r="B362" s="13"/>
       <c r="C362" s="15"/>
       <c r="G362" s="14"/>
     </row>
-    <row r="363" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="363" spans="2:7" ht="30" customHeight="1">
       <c r="B363" s="13"/>
       <c r="C363" s="15"/>
       <c r="G363" s="14"/>
     </row>
-    <row r="364" spans="2:7" hidden="1">
+    <row r="364" spans="2:7">
       <c r="B364" s="13"/>
       <c r="C364" s="15"/>
       <c r="G364" s="13"/>
     </row>
-    <row r="365" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="365" spans="2:7" ht="30" customHeight="1">
       <c r="B365" s="13"/>
       <c r="C365" s="15"/>
       <c r="E365" s="14"/>
       <c r="G365" s="14"/>
     </row>
-    <row r="366" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="366" spans="2:7" ht="30" customHeight="1">
       <c r="C366" s="15"/>
       <c r="G366" s="14"/>
     </row>
-    <row r="367" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="367" spans="2:7" ht="30" customHeight="1">
       <c r="C367" s="15"/>
       <c r="G367" s="14"/>
     </row>
-    <row r="368" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="368" spans="2:7" ht="30" customHeight="1">
       <c r="C368" s="15"/>
       <c r="G368" s="14"/>
     </row>
-    <row r="369" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="369" spans="1:7" ht="30" customHeight="1">
       <c r="C369" s="15"/>
       <c r="G369" s="14"/>
     </row>
-    <row r="370" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="370" spans="1:7" ht="30" customHeight="1">
       <c r="B370" s="13"/>
       <c r="C370" s="15"/>
       <c r="G370" s="14"/>
     </row>
-    <row r="371" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="371" spans="1:7" ht="30" customHeight="1">
       <c r="B371" s="13"/>
       <c r="C371" s="15"/>
       <c r="G371" s="14"/>
     </row>
-    <row r="372" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="372" spans="1:7" ht="30" customHeight="1">
       <c r="B372" s="13"/>
       <c r="C372" s="15"/>
       <c r="G372" s="14"/>
     </row>
-    <row r="373" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="373" spans="1:7" ht="30" customHeight="1">
       <c r="A373" s="13"/>
       <c r="B373" s="13"/>
       <c r="C373" s="15"/>
       <c r="G373" s="14"/>
     </row>
-    <row r="374" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="374" spans="1:7" ht="30" customHeight="1">
       <c r="B374" s="13"/>
       <c r="C374" s="15"/>
       <c r="E374" s="14"/>
       <c r="G374" s="14"/>
     </row>
-    <row r="375" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="375" spans="1:7" ht="30" customHeight="1">
       <c r="C375" s="5"/>
       <c r="D375" s="5"/>
       <c r="E375" s="15"/>
       <c r="F375" s="5"/>
       <c r="G375" s="14"/>
     </row>
-    <row r="376" spans="1:7" hidden="1">
+    <row r="376" spans="1:7">
       <c r="B376" s="13"/>
       <c r="C376" s="15"/>
       <c r="G376" s="14"/>
     </row>
-    <row r="377" spans="1:7" hidden="1">
+    <row r="377" spans="1:7">
       <c r="C377" s="15"/>
       <c r="E377" s="14"/>
       <c r="G377" s="14"/>
     </row>
-    <row r="378" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="378" spans="1:7" ht="30" customHeight="1">
       <c r="C378" s="15"/>
       <c r="G378" s="14"/>
     </row>
-    <row r="379" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="379" spans="1:7" ht="30" customHeight="1">
       <c r="C379" s="5"/>
       <c r="D379" s="5"/>
       <c r="E379" s="12"/>
       <c r="F379" s="5"/>
       <c r="G379" s="14"/>
     </row>
-    <row r="380" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="380" spans="1:7" ht="30" customHeight="1">
       <c r="B380" s="13"/>
       <c r="C380" s="15"/>
       <c r="G380" s="14"/>
     </row>
-    <row r="381" spans="1:7" hidden="1">
+    <row r="381" spans="1:7">
       <c r="B381" s="13"/>
       <c r="C381" s="15"/>
       <c r="G381" s="14"/>
     </row>
-    <row r="382" spans="1:7" hidden="1">
+    <row r="382" spans="1:7">
       <c r="B382" s="13"/>
       <c r="C382" s="15"/>
       <c r="G382" s="14"/>
     </row>
-    <row r="383" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="383" spans="1:7" ht="30" customHeight="1">
       <c r="C383" s="5"/>
       <c r="D383" s="5"/>
       <c r="E383" s="15"/>
       <c r="F383" s="5"/>
       <c r="G383" s="14"/>
     </row>
-    <row r="384" spans="1:7" hidden="1">
+    <row r="384" spans="1:7">
       <c r="B384" s="13"/>
       <c r="C384" s="15"/>
       <c r="G384" s="14"/>
     </row>
-    <row r="385" spans="2:7" hidden="1">
+    <row r="385" spans="2:7">
       <c r="B385" s="13"/>
       <c r="C385" s="15"/>
       <c r="G385" s="14"/>
     </row>
-    <row r="386" spans="2:7" hidden="1">
+    <row r="386" spans="2:7">
       <c r="B386" s="13"/>
       <c r="C386" s="15"/>
       <c r="G386" s="14"/>
     </row>
-    <row r="387" spans="2:7" hidden="1">
+    <row r="387" spans="2:7">
       <c r="B387" s="13"/>
       <c r="C387" s="15"/>
       <c r="G387" s="14"/>
     </row>
-    <row r="388" spans="2:7" hidden="1">
+    <row r="388" spans="2:7">
       <c r="B388" s="13"/>
       <c r="C388" s="15"/>
       <c r="G388" s="14"/>
     </row>
-    <row r="389" spans="2:7" hidden="1">
+    <row r="389" spans="2:7">
       <c r="B389" s="13"/>
       <c r="C389" s="15"/>
       <c r="G389" s="14"/>
     </row>
-    <row r="390" spans="2:7" hidden="1">
+    <row r="390" spans="2:7">
       <c r="B390" s="13"/>
       <c r="C390" s="15"/>
       <c r="G390" s="14"/>
     </row>
-    <row r="391" spans="2:7" hidden="1">
+    <row r="391" spans="2:7">
       <c r="B391" s="13"/>
       <c r="C391" s="15"/>
       <c r="G391" s="14"/>
     </row>
-    <row r="392" spans="2:7" hidden="1">
+    <row r="392" spans="2:7">
       <c r="B392" s="13"/>
       <c r="C392" s="15"/>
       <c r="G392" s="14"/>
     </row>
-    <row r="393" spans="2:7" hidden="1">
+    <row r="393" spans="2:7">
       <c r="B393" s="13"/>
       <c r="C393" s="15"/>
       <c r="G393" s="14"/>
     </row>
-    <row r="394" spans="2:7" hidden="1">
+    <row r="394" spans="2:7">
       <c r="B394" s="13"/>
       <c r="C394" s="15"/>
       <c r="G394" s="14"/>
     </row>
-    <row r="395" spans="2:7" hidden="1">
+    <row r="395" spans="2:7">
       <c r="B395" s="13"/>
       <c r="C395" s="15"/>
       <c r="G395" s="13"/>
     </row>
-    <row r="396" spans="2:7" hidden="1">
+    <row r="396" spans="2:7">
       <c r="B396" s="13"/>
       <c r="C396" s="15"/>
       <c r="G396" s="13"/>
     </row>
-    <row r="397" spans="2:7" hidden="1">
+    <row r="397" spans="2:7">
       <c r="B397" s="13"/>
       <c r="C397" s="15"/>
       <c r="G397" s="13"/>
     </row>
-    <row r="398" spans="2:7" hidden="1">
+    <row r="398" spans="2:7">
       <c r="B398" s="13"/>
       <c r="C398" s="15"/>
       <c r="G398" s="13"/>
     </row>
-    <row r="399" spans="2:7" hidden="1">
+    <row r="399" spans="2:7">
       <c r="B399" s="13"/>
       <c r="C399" s="15"/>
       <c r="G399" s="13"/>
     </row>
-    <row r="400" spans="2:7" hidden="1">
+    <row r="400" spans="2:7">
       <c r="B400" s="13"/>
       <c r="C400" s="15"/>
       <c r="G400" s="13"/>
     </row>
-    <row r="401" spans="2:7" hidden="1">
+    <row r="401" spans="2:7">
       <c r="B401" s="13"/>
       <c r="C401" s="15"/>
       <c r="G401" s="13"/>
     </row>
-    <row r="402" spans="2:7" hidden="1">
+    <row r="402" spans="2:7">
       <c r="B402" s="13"/>
       <c r="C402" s="15"/>
       <c r="G402" s="13"/>
     </row>
-    <row r="403" spans="2:7" hidden="1">
+    <row r="403" spans="2:7">
       <c r="B403" s="13"/>
       <c r="C403" s="15"/>
       <c r="G403" s="14"/>
     </row>
-    <row r="404" spans="2:7" hidden="1">
+    <row r="404" spans="2:7">
       <c r="B404" s="13"/>
       <c r="C404" s="15"/>
       <c r="G404" s="14"/>
     </row>
-    <row r="405" spans="2:7" hidden="1">
+    <row r="405" spans="2:7">
       <c r="B405" s="13"/>
       <c r="C405" s="15"/>
       <c r="G405" s="14"/>
     </row>
-    <row r="406" spans="2:7" hidden="1">
+    <row r="406" spans="2:7">
       <c r="B406" s="13"/>
       <c r="C406" s="15"/>
       <c r="G406" s="14"/>
     </row>
-    <row r="407" spans="2:7" hidden="1">
+    <row r="407" spans="2:7">
       <c r="B407" s="13"/>
       <c r="C407" s="15"/>
       <c r="G407" s="14"/>
     </row>
-    <row r="408" spans="2:7" hidden="1">
+    <row r="408" spans="2:7">
       <c r="B408" s="13"/>
       <c r="C408" s="15"/>
       <c r="G408" s="14"/>
     </row>
-    <row r="409" spans="2:7" hidden="1">
+    <row r="409" spans="2:7">
       <c r="B409" s="13"/>
       <c r="C409" s="15"/>
       <c r="G409" s="14"/>
     </row>
-    <row r="410" spans="2:7" hidden="1">
+    <row r="410" spans="2:7">
       <c r="B410" s="13"/>
       <c r="C410" s="15"/>
       <c r="G410" s="14"/>
     </row>
-    <row r="411" spans="2:7" hidden="1">
+    <row r="411" spans="2:7">
       <c r="B411" s="13"/>
       <c r="C411" s="15"/>
       <c r="G411" s="14"/>
     </row>
-    <row r="412" spans="2:7" hidden="1">
+    <row r="412" spans="2:7">
       <c r="B412" s="13"/>
       <c r="C412" s="15"/>
       <c r="G412" s="14"/>
     </row>
-    <row r="413" spans="2:7" hidden="1">
+    <row r="413" spans="2:7">
       <c r="B413" s="13"/>
       <c r="C413" s="15"/>
       <c r="G413" s="14"/>
     </row>
-    <row r="414" spans="2:7" hidden="1">
+    <row r="414" spans="2:7">
       <c r="B414" s="13"/>
       <c r="C414" s="15"/>
       <c r="G414" s="14"/>
     </row>
-    <row r="415" spans="2:7" hidden="1">
+    <row r="415" spans="2:7">
       <c r="B415" s="13"/>
       <c r="C415" s="15"/>
       <c r="G415" s="14"/>
     </row>
-    <row r="416" spans="2:7" hidden="1">
+    <row r="416" spans="2:7">
       <c r="B416" s="13"/>
       <c r="C416" s="15"/>
       <c r="G416" s="14"/>
     </row>
-    <row r="417" spans="1:7" hidden="1">
+    <row r="417" spans="1:7">
       <c r="B417" s="13"/>
       <c r="C417" s="15"/>
       <c r="G417" s="14"/>
     </row>
-    <row r="418" spans="1:7" hidden="1">
+    <row r="418" spans="1:7">
       <c r="B418" s="13"/>
       <c r="C418" s="15"/>
       <c r="G418" s="14"/>
     </row>
-    <row r="419" spans="1:7" hidden="1">
+    <row r="419" spans="1:7">
       <c r="B419" s="13"/>
       <c r="C419" s="15"/>
       <c r="G419" s="13"/>
     </row>
-    <row r="420" spans="1:7" hidden="1">
+    <row r="420" spans="1:7">
       <c r="B420" s="13"/>
       <c r="C420" s="15"/>
       <c r="G420" s="13"/>
     </row>
-    <row r="421" spans="1:7" hidden="1">
+    <row r="421" spans="1:7">
       <c r="B421" s="13"/>
       <c r="C421" s="15"/>
       <c r="G421" s="13"/>
     </row>
-    <row r="422" spans="1:7" hidden="1">
+    <row r="422" spans="1:7">
       <c r="B422" s="13"/>
       <c r="C422" s="15"/>
       <c r="G422"/>
     </row>
-    <row r="423" spans="1:7" hidden="1">
+    <row r="423" spans="1:7">
       <c r="B423" s="13"/>
       <c r="C423" s="15"/>
       <c r="G423" s="14"/>
     </row>
-    <row r="424" spans="1:7" hidden="1">
+    <row r="424" spans="1:7">
       <c r="B424" s="13"/>
       <c r="C424" s="15"/>
       <c r="G424" s="14"/>
     </row>
-    <row r="425" spans="1:7" hidden="1">
+    <row r="425" spans="1:7">
       <c r="B425" s="13"/>
       <c r="C425" s="15"/>
       <c r="G425" s="13"/>
     </row>
-    <row r="426" spans="1:7" hidden="1">
+    <row r="426" spans="1:7">
       <c r="C426" s="15"/>
       <c r="G426" s="13"/>
     </row>
-    <row r="427" spans="1:7" hidden="1">
+    <row r="427" spans="1:7">
       <c r="B427" s="13"/>
       <c r="C427" s="15"/>
       <c r="G427" s="13"/>
     </row>
-    <row r="428" spans="1:7" hidden="1">
+    <row r="428" spans="1:7">
       <c r="B428" s="13"/>
       <c r="C428" s="15"/>
       <c r="G428" s="13"/>
     </row>
-    <row r="429" spans="1:7" hidden="1">
+    <row r="429" spans="1:7">
       <c r="B429" s="13"/>
       <c r="C429" s="15"/>
       <c r="G429" s="13"/>
     </row>
-    <row r="430" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="430" spans="1:7" ht="30" customHeight="1">
       <c r="B430" s="13"/>
       <c r="C430" s="15"/>
       <c r="G430" s="14"/>
     </row>
-    <row r="431" spans="1:7" hidden="1">
+    <row r="431" spans="1:7">
       <c r="A431" s="13"/>
       <c r="B431" s="13"/>
       <c r="C431" s="15"/>
       <c r="G431" s="14"/>
     </row>
-    <row r="432" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="432" spans="1:7" ht="30" customHeight="1">
       <c r="A432" s="13"/>
       <c r="B432" s="13"/>
       <c r="C432" s="15"/>
       <c r="G432" s="14"/>
     </row>
-    <row r="433" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="433" spans="2:7" ht="30" customHeight="1">
       <c r="C433" s="5"/>
       <c r="D433" s="5"/>
       <c r="E433" s="12"/>
       <c r="F433" s="5"/>
       <c r="G433" s="14"/>
     </row>
-    <row r="434" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="434" spans="2:7" ht="30" customHeight="1">
       <c r="B434" s="13"/>
       <c r="C434" s="15"/>
       <c r="G434" s="14"/>
     </row>
-    <row r="435" spans="2:7" hidden="1">
+    <row r="435" spans="2:7">
       <c r="C435" s="5"/>
       <c r="G435"/>
     </row>
-    <row r="436" spans="2:7" hidden="1">
+    <row r="436" spans="2:7">
       <c r="C436" s="5"/>
       <c r="G436"/>
     </row>
-    <row r="437" spans="2:7" hidden="1">
+    <row r="437" spans="2:7">
       <c r="C437" s="5"/>
       <c r="G437"/>
     </row>
-    <row r="438" spans="2:7" hidden="1">
+    <row r="438" spans="2:7">
       <c r="C438" s="5"/>
       <c r="G438"/>
     </row>
-    <row r="439" spans="2:7" hidden="1">
+    <row r="439" spans="2:7">
       <c r="C439" s="5"/>
       <c r="G439"/>
     </row>
-    <row r="440" spans="2:7" hidden="1">
+    <row r="440" spans="2:7">
       <c r="C440" s="5"/>
       <c r="G440"/>
     </row>
-    <row r="441" spans="2:7" hidden="1">
+    <row r="441" spans="2:7">
       <c r="C441" s="5"/>
       <c r="G441"/>
     </row>
-    <row r="442" spans="2:7" hidden="1">
+    <row r="442" spans="2:7">
       <c r="C442" s="5"/>
       <c r="G442"/>
     </row>
-    <row r="443" spans="2:7" hidden="1">
+    <row r="443" spans="2:7">
       <c r="C443" s="5"/>
       <c r="G443"/>
     </row>
-    <row r="444" spans="2:7" hidden="1">
+    <row r="444" spans="2:7">
       <c r="C444" s="5"/>
       <c r="G444"/>
     </row>
-    <row r="445" spans="2:7" hidden="1">
+    <row r="445" spans="2:7">
       <c r="C445" s="5"/>
       <c r="G445"/>
     </row>
-    <row r="446" spans="2:7" hidden="1">
+    <row r="446" spans="2:7">
       <c r="C446" s="5"/>
       <c r="G446"/>
     </row>
-    <row r="447" spans="2:7" hidden="1">
+    <row r="447" spans="2:7">
       <c r="C447" s="5"/>
       <c r="G447"/>
     </row>
-    <row r="448" spans="2:7" hidden="1">
+    <row r="448" spans="2:7">
       <c r="C448" s="5"/>
       <c r="G448"/>
     </row>
-    <row r="449" spans="2:7" hidden="1">
+    <row r="449" spans="2:7">
       <c r="C449" s="5"/>
       <c r="G449"/>
     </row>
-    <row r="450" spans="2:7" hidden="1">
+    <row r="450" spans="2:7">
       <c r="C450" s="5"/>
       <c r="G450"/>
     </row>
-    <row r="451" spans="2:7" hidden="1">
+    <row r="451" spans="2:7">
       <c r="C451" s="5"/>
       <c r="G451"/>
     </row>
-    <row r="452" spans="2:7" hidden="1">
+    <row r="452" spans="2:7">
       <c r="C452" s="5"/>
       <c r="G452"/>
     </row>
-    <row r="453" spans="2:7" hidden="1">
+    <row r="453" spans="2:7">
       <c r="C453" s="5"/>
       <c r="G453"/>
     </row>
-    <row r="454" spans="2:7" hidden="1">
+    <row r="454" spans="2:7">
       <c r="C454" s="5"/>
       <c r="G454"/>
     </row>
-    <row r="455" spans="2:7" hidden="1">
+    <row r="455" spans="2:7">
       <c r="C455" s="5"/>
       <c r="G455"/>
     </row>
-    <row r="456" spans="2:7" hidden="1">
+    <row r="456" spans="2:7">
       <c r="C456" s="5"/>
       <c r="G456"/>
     </row>
-    <row r="457" spans="2:7" hidden="1">
+    <row r="457" spans="2:7">
       <c r="C457" s="5"/>
       <c r="G457"/>
     </row>
-    <row r="458" spans="2:7" hidden="1">
+    <row r="458" spans="2:7">
       <c r="B458" s="13"/>
       <c r="C458" s="15"/>
       <c r="G458" s="14"/>
     </row>
-    <row r="459" spans="2:7" hidden="1">
+    <row r="459" spans="2:7">
       <c r="B459" s="13"/>
       <c r="C459" s="15"/>
       <c r="G459" s="13"/>
     </row>
-    <row r="460" spans="2:7" hidden="1">
+    <row r="460" spans="2:7">
       <c r="B460" s="13"/>
       <c r="C460" s="15"/>
       <c r="G460" s="13"/>
     </row>
-    <row r="461" spans="2:7" hidden="1">
+    <row r="461" spans="2:7">
       <c r="B461" s="13"/>
       <c r="C461" s="15"/>
       <c r="G461" s="13"/>
     </row>
-    <row r="462" spans="2:7" hidden="1">
+    <row r="462" spans="2:7">
       <c r="B462" s="13"/>
       <c r="C462" s="15"/>
       <c r="G462" s="13"/>
     </row>
-    <row r="463" spans="2:7" hidden="1">
+    <row r="463" spans="2:7">
       <c r="B463" s="13"/>
       <c r="C463" s="15"/>
       <c r="G463" s="13"/>
     </row>
-    <row r="464" spans="2:7" hidden="1">
+    <row r="464" spans="2:7">
       <c r="B464" s="13"/>
       <c r="C464" s="15"/>
       <c r="G464" s="13"/>
     </row>
-    <row r="465" spans="2:6" hidden="1">
+    <row r="465" spans="2:6">
       <c r="B465" s="13"/>
       <c r="C465" s="5"/>
       <c r="D465" s="5"/>
       <c r="E465" s="15"/>
       <c r="F465" s="5"/>
     </row>
-    <row r="466" spans="2:6" ht="30" hidden="1" customHeight="1">
+    <row r="466" spans="2:6" ht="30" customHeight="1">
       <c r="C466" s="5"/>
       <c r="D466" s="5"/>
       <c r="E466" s="15"/>
       <c r="F466" s="5"/>
     </row>
-    <row r="467" spans="2:6" hidden="1">
+    <row r="467" spans="2:6">
       <c r="C467" s="5"/>
       <c r="D467" s="5"/>
       <c r="E467" s="15"/>
       <c r="F467" s="5"/>
     </row>
-    <row r="468" spans="2:6" hidden="1">
+    <row r="468" spans="2:6">
       <c r="C468" s="5"/>
       <c r="D468" s="5"/>
       <c r="E468" s="15"/>
       <c r="F468" s="5"/>
     </row>
-    <row r="469" spans="2:6" hidden="1">
+    <row r="469" spans="2:6">
       <c r="C469" s="5"/>
       <c r="D469" s="5"/>
       <c r="E469" s="15"/>
       <c r="F469" s="5"/>
     </row>
-    <row r="470" spans="2:6" hidden="1">
+    <row r="470" spans="2:6">
       <c r="C470" s="5"/>
       <c r="D470" s="5"/>
       <c r="E470" s="15"/>
       <c r="F470" s="5"/>
     </row>
-    <row r="471" spans="2:6" hidden="1">
+    <row r="471" spans="2:6">
       <c r="C471" s="5"/>
       <c r="D471" s="5"/>
       <c r="E471" s="15"/>
       <c r="F471" s="5"/>
     </row>
-    <row r="472" spans="2:6" hidden="1">
+    <row r="472" spans="2:6">
       <c r="C472" s="5"/>
       <c r="D472" s="5"/>
       <c r="E472" s="15"/>
       <c r="F472" s="5"/>
     </row>
-    <row r="473" spans="2:6" hidden="1">
+    <row r="473" spans="2:6">
       <c r="C473" s="5"/>
       <c r="D473" s="5"/>
       <c r="E473" s="15"/>
       <c r="F473" s="5"/>
     </row>
-    <row r="474" spans="2:6" hidden="1">
+    <row r="474" spans="2:6">
       <c r="C474" s="5"/>
       <c r="D474" s="5"/>
       <c r="E474" s="15"/>
       <c r="F474" s="5"/>
     </row>
-    <row r="475" spans="2:6" hidden="1">
+    <row r="475" spans="2:6">
       <c r="C475" s="5"/>
       <c r="D475" s="5"/>
       <c r="E475" s="15"/>
       <c r="F475" s="5"/>
     </row>
-    <row r="476" spans="2:6" hidden="1">
+    <row r="476" spans="2:6">
       <c r="C476" s="5"/>
       <c r="D476" s="5"/>
       <c r="E476" s="15"/>
       <c r="F476" s="5"/>
     </row>
-    <row r="477" spans="2:6" hidden="1">
+    <row r="477" spans="2:6">
       <c r="C477" s="5"/>
       <c r="D477" s="5"/>
       <c r="E477" s="15"/>
       <c r="F477" s="5"/>
     </row>
-    <row r="478" spans="2:6" hidden="1">
+    <row r="478" spans="2:6">
       <c r="C478" s="5"/>
       <c r="D478" s="5"/>
       <c r="E478" s="15"/>
       <c r="F478" s="5"/>
     </row>
-    <row r="479" spans="2:6" hidden="1">
+    <row r="479" spans="2:6">
       <c r="C479" s="5"/>
       <c r="D479" s="5"/>
       <c r="E479" s="15"/>
       <c r="F479" s="5"/>
     </row>
-    <row r="480" spans="2:6" hidden="1">
+    <row r="480" spans="2:6">
       <c r="C480" s="5"/>
       <c r="D480" s="5"/>
       <c r="E480" s="15"/>
       <c r="F480" s="5"/>
     </row>
-    <row r="481" spans="3:6" hidden="1">
+    <row r="481" spans="3:6">
       <c r="C481" s="5"/>
       <c r="D481" s="5"/>
       <c r="E481" s="15"/>
       <c r="F481" s="5"/>
     </row>
-    <row r="482" spans="3:6" hidden="1">
+    <row r="482" spans="3:6">
       <c r="C482" s="5"/>
       <c r="D482" s="5"/>
       <c r="E482" s="15"/>
       <c r="F482" s="5"/>
     </row>
-    <row r="483" spans="3:6" hidden="1">
+    <row r="483" spans="3:6">
       <c r="C483" s="5"/>
       <c r="D483" s="5"/>
       <c r="E483" s="15"/>
       <c r="F483" s="5"/>
     </row>
-    <row r="484" spans="3:6" hidden="1">
+    <row r="484" spans="3:6">
       <c r="C484" s="5"/>
       <c r="D484" s="5"/>
       <c r="E484" s="15"/>
       <c r="F484" s="5"/>
     </row>
-    <row r="485" spans="3:6" hidden="1">
+    <row r="485" spans="3:6">
       <c r="C485" s="5"/>
       <c r="D485" s="5"/>
       <c r="E485" s="15"/>
       <c r="F485" s="5"/>
     </row>
-    <row r="486" spans="3:6" hidden="1">
+    <row r="486" spans="3:6">
       <c r="C486" s="5"/>
       <c r="D486" s="5"/>
       <c r="E486" s="15"/>
       <c r="F486" s="5"/>
     </row>
-    <row r="487" spans="3:6" hidden="1">
+    <row r="487" spans="3:6">
       <c r="C487" s="5"/>
       <c r="D487" s="5"/>
       <c r="E487" s="15"/>
       <c r="F487" s="5"/>
     </row>
-    <row r="488" spans="3:6" hidden="1">
+    <row r="488" spans="3:6">
       <c r="C488" s="5"/>
       <c r="D488" s="5"/>
       <c r="E488" s="15"/>
       <c r="F488" s="5"/>
     </row>
-    <row r="489" spans="3:6" hidden="1">
+    <row r="489" spans="3:6">
       <c r="C489" s="5"/>
       <c r="D489" s="5"/>
       <c r="E489" s="15"/>
       <c r="F489" s="5"/>
     </row>
-    <row r="490" spans="3:6" hidden="1">
+    <row r="490" spans="3:6">
       <c r="C490" s="5"/>
       <c r="D490" s="5"/>
       <c r="E490" s="15"/>
       <c r="F490" s="5"/>
     </row>
-    <row r="491" spans="3:6" hidden="1">
+    <row r="491" spans="3:6">
       <c r="C491" s="5"/>
       <c r="D491" s="5"/>
       <c r="E491" s="15"/>
       <c r="F491" s="5"/>
     </row>
-    <row r="492" spans="3:6" hidden="1">
+    <row r="492" spans="3:6">
       <c r="C492" s="5"/>
       <c r="D492" s="5"/>
       <c r="E492" s="15"/>
       <c r="F492" s="5"/>
     </row>
-    <row r="493" spans="3:6" hidden="1">
+    <row r="493" spans="3:6">
       <c r="C493" s="5"/>
       <c r="D493" s="5"/>
       <c r="E493" s="15"/>
       <c r="F493" s="5"/>
     </row>
-    <row r="494" spans="3:6" hidden="1">
+    <row r="494" spans="3:6">
       <c r="C494" s="5"/>
       <c r="D494" s="5"/>
       <c r="E494" s="15"/>
       <c r="F494" s="5"/>
     </row>
-    <row r="495" spans="3:6" hidden="1">
+    <row r="495" spans="3:6">
       <c r="C495" s="5"/>
       <c r="D495" s="5"/>
       <c r="E495" s="15"/>
       <c r="F495" s="5"/>
     </row>
-    <row r="496" spans="3:6" hidden="1">
+    <row r="496" spans="3:6">
       <c r="C496" s="5"/>
       <c r="D496" s="5"/>
       <c r="E496" s="15"/>
       <c r="F496" s="5"/>
     </row>
-    <row r="497" spans="3:6" hidden="1">
+    <row r="497" spans="3:6">
       <c r="C497" s="5"/>
       <c r="D497" s="5"/>
       <c r="E497" s="15"/>
       <c r="F497" s="5"/>
     </row>
-    <row r="498" spans="3:6" hidden="1">
+    <row r="498" spans="3:6">
       <c r="C498" s="5"/>
       <c r="D498" s="5"/>
       <c r="E498" s="15"/>
       <c r="F498" s="5"/>
     </row>
-    <row r="499" spans="3:6" hidden="1">
+    <row r="499" spans="3:6">
       <c r="C499" s="5"/>
       <c r="D499" s="5"/>
       <c r="E499" s="15"/>
       <c r="F499" s="5"/>
     </row>
-    <row r="500" spans="3:6" hidden="1">
+    <row r="500" spans="3:6">
       <c r="C500" s="5"/>
       <c r="D500" s="5"/>
       <c r="E500" s="15"/>
       <c r="F500" s="5"/>
     </row>
-    <row r="501" spans="3:6" hidden="1">
+    <row r="501" spans="3:6">
       <c r="C501" s="5"/>
       <c r="D501" s="5"/>
       <c r="E501" s="15"/>
       <c r="F501" s="5"/>
     </row>
-    <row r="502" spans="3:6" hidden="1">
+    <row r="502" spans="3:6">
       <c r="C502" s="5"/>
       <c r="D502" s="5"/>
       <c r="E502" s="15"/>
       <c r="F502" s="5"/>
     </row>
-    <row r="503" spans="3:6" hidden="1">
+    <row r="503" spans="3:6">
       <c r="C503" s="5"/>
       <c r="D503" s="5"/>
       <c r="E503" s="15"/>
       <c r="F503" s="5"/>
     </row>
-    <row r="504" spans="3:6" hidden="1">
+    <row r="504" spans="3:6">
       <c r="C504" s="5"/>
       <c r="D504" s="5"/>
       <c r="E504" s="15"/>
       <c r="F504" s="5"/>
     </row>
-    <row r="505" spans="3:6" hidden="1">
+    <row r="505" spans="3:6">
       <c r="C505" s="5"/>
       <c r="D505" s="5"/>
       <c r="E505" s="15"/>
       <c r="F505" s="5"/>
     </row>
-    <row r="506" spans="3:6" hidden="1">
+    <row r="506" spans="3:6">
       <c r="C506" s="5"/>
       <c r="D506" s="5"/>
       <c r="E506" s="15"/>
       <c r="F506" s="5"/>
     </row>
-    <row r="507" spans="3:6" hidden="1">
+    <row r="507" spans="3:6">
       <c r="C507" s="5"/>
       <c r="D507" s="5"/>
       <c r="E507" s="15"/>
       <c r="F507" s="5"/>
     </row>
-    <row r="508" spans="3:6" hidden="1">
+    <row r="508" spans="3:6">
       <c r="C508" s="5"/>
       <c r="D508" s="5"/>
       <c r="E508" s="15"/>
       <c r="F508" s="5"/>
     </row>
-    <row r="509" spans="3:6" hidden="1">
+    <row r="509" spans="3:6">
       <c r="C509" s="5"/>
       <c r="D509" s="5"/>
       <c r="E509" s="15"/>
       <c r="F509" s="5"/>
     </row>
-    <row r="510" spans="3:6" hidden="1">
+    <row r="510" spans="3:6">
       <c r="C510" s="5"/>
       <c r="D510" s="5"/>
       <c r="E510" s="15"/>
       <c r="F510" s="5"/>
     </row>
-    <row r="511" spans="3:6" ht="30" hidden="1" customHeight="1">
+    <row r="511" spans="3:6" ht="30" customHeight="1">
       <c r="C511" s="5"/>
       <c r="D511" s="5"/>
       <c r="E511" s="15"/>
       <c r="F511" s="5"/>
     </row>
-    <row r="512" spans="3:6" hidden="1">
+    <row r="512" spans="3:6">
       <c r="C512" s="5"/>
       <c r="D512" s="5"/>
       <c r="E512" s="15"/>
       <c r="F512" s="5"/>
     </row>
-    <row r="513" spans="3:6" hidden="1">
+    <row r="513" spans="3:6">
       <c r="C513" s="5"/>
       <c r="D513" s="5"/>
       <c r="E513" s="15"/>
       <c r="F513" s="5"/>
     </row>
-    <row r="514" spans="3:6" hidden="1">
+    <row r="514" spans="3:6">
       <c r="C514" s="5"/>
       <c r="D514" s="5"/>
       <c r="E514" s="15"/>
       <c r="F514" s="5"/>
     </row>
-    <row r="515" spans="3:6" hidden="1">
+    <row r="515" spans="3:6">
       <c r="C515" s="5"/>
       <c r="D515" s="5"/>
       <c r="E515" s="15"/>
       <c r="F515" s="5"/>
     </row>
-    <row r="516" spans="3:6" hidden="1">
+    <row r="516" spans="3:6">
       <c r="C516" s="5"/>
       <c r="D516" s="5"/>
       <c r="E516" s="15"/>
       <c r="F516" s="5"/>
     </row>
-    <row r="517" spans="3:6" hidden="1">
+    <row r="517" spans="3:6">
       <c r="C517" s="5"/>
       <c r="D517" s="5"/>
       <c r="E517" s="15"/>
       <c r="F517" s="5"/>
     </row>
-    <row r="518" spans="3:6" hidden="1">
+    <row r="518" spans="3:6">
       <c r="C518" s="5"/>
       <c r="D518" s="5"/>
       <c r="E518" s="15"/>
       <c r="F518" s="5"/>
     </row>
-    <row r="519" spans="3:6" hidden="1">
+    <row r="519" spans="3:6">
       <c r="C519" s="5"/>
       <c r="D519" s="5"/>
       <c r="E519" s="15"/>
       <c r="F519" s="5"/>
     </row>
-    <row r="520" spans="3:6" hidden="1">
+    <row r="520" spans="3:6">
       <c r="C520" s="5"/>
       <c r="D520" s="5"/>
       <c r="E520" s="15"/>
       <c r="F520" s="5"/>
     </row>
-    <row r="521" spans="3:6" hidden="1">
+    <row r="521" spans="3:6">
       <c r="C521" s="5"/>
       <c r="D521" s="5"/>
       <c r="E521" s="15"/>
       <c r="F521" s="5"/>
     </row>
-    <row r="522" spans="3:6" hidden="1">
+    <row r="522" spans="3:6">
       <c r="C522" s="5"/>
       <c r="D522" s="5"/>
       <c r="E522" s="15"/>
       <c r="F522" s="5"/>
     </row>
-    <row r="523" spans="3:6" hidden="1">
+    <row r="523" spans="3:6">
       <c r="C523" s="5"/>
       <c r="D523" s="5"/>
       <c r="E523" s="15"/>
       <c r="F523" s="5"/>
     </row>
-    <row r="524" spans="3:6" hidden="1">
+    <row r="524" spans="3:6">
       <c r="C524" s="5"/>
       <c r="D524" s="5"/>
       <c r="E524" s="15"/>
       <c r="F524" s="5"/>
     </row>
-    <row r="525" spans="3:6" hidden="1">
+    <row r="525" spans="3:6">
       <c r="C525" s="5"/>
       <c r="D525" s="5"/>
       <c r="E525" s="15"/>
       <c r="F525" s="5"/>
     </row>
-    <row r="526" spans="3:6" ht="30" hidden="1" customHeight="1">
+    <row r="526" spans="3:6" ht="30" customHeight="1">
       <c r="C526" s="5"/>
       <c r="D526" s="5"/>
       <c r="E526" s="15"/>
       <c r="F526" s="5"/>
     </row>
-    <row r="527" spans="3:6" ht="30" hidden="1" customHeight="1">
+    <row r="527" spans="3:6" ht="30" customHeight="1">
       <c r="C527" s="5"/>
       <c r="D527" s="5"/>
       <c r="E527" s="15"/>
       <c r="F527" s="5"/>
     </row>
-    <row r="528" spans="3:6" ht="30" hidden="1" customHeight="1">
+    <row r="528" spans="3:6" ht="30" customHeight="1">
       <c r="C528" s="5"/>
       <c r="D528" s="5"/>
       <c r="E528" s="15"/>
       <c r="F528" s="5"/>
     </row>
-    <row r="529" spans="3:7" ht="30" hidden="1" customHeight="1">
+    <row r="529" spans="3:7" ht="30" customHeight="1">
       <c r="C529" s="5"/>
       <c r="D529" s="5"/>
       <c r="E529" s="15"/>
       <c r="F529" s="5"/>
       <c r="G529" s="14"/>
     </row>
-    <row r="530" spans="3:7" hidden="1">
+    <row r="530" spans="3:7">
       <c r="C530" s="5"/>
       <c r="D530" s="5"/>
       <c r="E530" s="15"/>
       <c r="F530" s="5"/>
     </row>
-    <row r="531" spans="3:7" ht="30" hidden="1" customHeight="1">
+    <row r="531" spans="3:7" ht="30" customHeight="1">
       <c r="C531" s="5"/>
       <c r="D531" s="5"/>
       <c r="E531" s="15"/>
       <c r="F531" s="5"/>
       <c r="G531" s="14"/>
     </row>
-    <row r="532" spans="3:7" hidden="1">
+    <row r="532" spans="3:7">
       <c r="C532" s="5"/>
       <c r="D532" s="5"/>
       <c r="E532" s="15"/>
       <c r="F532" s="5"/>
     </row>
-    <row r="533" spans="3:7" hidden="1">
+    <row r="533" spans="3:7">
       <c r="C533" s="5"/>
       <c r="D533" s="5"/>
       <c r="E533" s="15"/>
       <c r="F533" s="5"/>
     </row>
-    <row r="534" spans="3:7" hidden="1">
+    <row r="534" spans="3:7">
       <c r="C534" s="5"/>
       <c r="D534" s="5"/>
       <c r="E534" s="15"/>
       <c r="F534" s="5"/>
     </row>
-    <row r="535" spans="3:7" hidden="1">
+    <row r="535" spans="3:7">
       <c r="C535" s="5"/>
       <c r="D535" s="5"/>
       <c r="E535" s="15"/>
       <c r="F535" s="5"/>
     </row>
-    <row r="536" spans="3:7" hidden="1">
+    <row r="536" spans="3:7">
       <c r="C536" s="5"/>
       <c r="D536" s="5"/>
       <c r="E536" s="15"/>
       <c r="F536" s="5"/>
     </row>
-    <row r="537" spans="3:7" hidden="1">
+    <row r="537" spans="3:7">
       <c r="C537" s="5"/>
       <c r="D537" s="5"/>
       <c r="E537" s="15"/>
       <c r="F537" s="5"/>
     </row>
-    <row r="538" spans="3:7" hidden="1">
+    <row r="538" spans="3:7">
       <c r="C538" s="5"/>
       <c r="D538" s="5"/>
       <c r="E538" s="15"/>
       <c r="F538" s="5"/>
     </row>
-    <row r="539" spans="3:7" hidden="1">
+    <row r="539" spans="3:7">
       <c r="C539" s="5"/>
       <c r="D539" s="5"/>
       <c r="E539" s="15"/>
       <c r="F539" s="5"/>
     </row>
-    <row r="540" spans="3:7" hidden="1">
+    <row r="540" spans="3:7">
       <c r="C540" s="5"/>
       <c r="D540" s="5"/>
       <c r="E540" s="15"/>
       <c r="F540" s="5"/>
     </row>
-    <row r="541" spans="3:7" hidden="1">
+    <row r="541" spans="3:7">
       <c r="C541" s="5"/>
       <c r="D541" s="5"/>
       <c r="E541" s="15"/>
       <c r="F541" s="5"/>
     </row>
-    <row r="542" spans="3:7" hidden="1">
+    <row r="542" spans="3:7">
       <c r="C542" s="5"/>
       <c r="D542" s="5"/>
       <c r="E542" s="15"/>
       <c r="F542" s="5"/>
     </row>
-    <row r="543" spans="3:7" hidden="1">
+    <row r="543" spans="3:7">
       <c r="C543" s="5"/>
       <c r="D543" s="5"/>
       <c r="E543" s="15"/>
       <c r="F543" s="5"/>
     </row>
-    <row r="544" spans="3:7" hidden="1">
+    <row r="544" spans="3:7">
       <c r="C544" s="5"/>
       <c r="D544" s="5"/>
       <c r="E544" s="15"/>
       <c r="F544" s="5"/>
     </row>
-    <row r="545" spans="1:7" hidden="1">
+    <row r="545" spans="1:7">
       <c r="C545" s="5"/>
       <c r="D545" s="5"/>
       <c r="E545" s="15"/>
       <c r="F545" s="5"/>
     </row>
-    <row r="546" spans="1:7" hidden="1">
+    <row r="546" spans="1:7">
       <c r="C546" s="5"/>
       <c r="D546" s="5"/>
       <c r="E546" s="15"/>
       <c r="F546" s="5"/>
     </row>
-    <row r="547" spans="1:7" hidden="1">
+    <row r="547" spans="1:7">
       <c r="C547" s="5"/>
       <c r="D547" s="5"/>
       <c r="E547" s="15"/>
       <c r="F547" s="5"/>
     </row>
-    <row r="548" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="548" spans="1:7" ht="30" customHeight="1">
       <c r="C548" s="5"/>
       <c r="D548" s="5"/>
       <c r="E548" s="15"/>
       <c r="F548" s="5"/>
       <c r="G548" s="14"/>
     </row>
-    <row r="549" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="549" spans="1:7" ht="30" customHeight="1">
       <c r="C549" s="5"/>
       <c r="D549" s="5"/>
       <c r="E549" s="15"/>
       <c r="F549" s="5"/>
     </row>
-    <row r="550" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="550" spans="1:7" ht="30" customHeight="1">
       <c r="C550" s="5"/>
       <c r="D550" s="5"/>
       <c r="E550" s="15"/>
       <c r="F550" s="5"/>
       <c r="G550" s="14"/>
     </row>
-    <row r="551" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="551" spans="1:7" ht="30" customHeight="1">
       <c r="C551" s="5"/>
       <c r="D551" s="5"/>
       <c r="E551" s="15"/>
       <c r="F551" s="5"/>
     </row>
-    <row r="552" spans="1:7" hidden="1">
+    <row r="552" spans="1:7">
       <c r="C552" s="5"/>
       <c r="D552" s="5"/>
       <c r="E552" s="15"/>
       <c r="F552" s="5"/>
       <c r="G552" s="3"/>
     </row>
-    <row r="553" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="553" spans="1:7" ht="30" customHeight="1">
       <c r="C553" s="5"/>
       <c r="D553" s="5"/>
       <c r="E553" s="15"/>
       <c r="F553" s="5"/>
     </row>
-    <row r="554" spans="1:7" hidden="1">
+    <row r="554" spans="1:7">
       <c r="C554" s="5"/>
       <c r="D554" s="5"/>
       <c r="E554" s="15"/>
       <c r="F554" s="5"/>
     </row>
-    <row r="555" spans="1:7" hidden="1">
+    <row r="555" spans="1:7">
       <c r="C555" s="5"/>
       <c r="D555" s="5"/>
       <c r="E555" s="15"/>
       <c r="F555" s="5"/>
     </row>
-    <row r="556" spans="1:7" hidden="1">
+    <row r="556" spans="1:7">
       <c r="C556" s="5"/>
       <c r="D556" s="5"/>
       <c r="E556" s="15"/>
       <c r="F556" s="5"/>
     </row>
-    <row r="557" spans="1:7" ht="12.75" hidden="1" customHeight="1">
+    <row r="557" spans="1:7" ht="12.75" customHeight="1">
       <c r="A557" s="7"/>
       <c r="B557" s="7"/>
       <c r="C557" s="8"/>
@@ -10112,14 +10111,14 @@
       <c r="F557" s="8"/>
       <c r="G557" s="9"/>
     </row>
-    <row r="558" spans="1:7" hidden="1">
+    <row r="558" spans="1:7">
       <c r="C558" s="5"/>
       <c r="D558" s="5"/>
       <c r="E558" s="15"/>
       <c r="F558" s="5"/>
       <c r="G558" s="3"/>
     </row>
-    <row r="559" spans="1:7" hidden="1">
+    <row r="559" spans="1:7">
       <c r="A559" s="13"/>
       <c r="B559" s="13"/>
       <c r="C559" s="5"/>
@@ -10128,700 +10127,700 @@
       <c r="F559" s="5"/>
       <c r="G559" s="14"/>
     </row>
-    <row r="560" spans="1:7" hidden="1">
+    <row r="560" spans="1:7">
       <c r="C560" s="5"/>
       <c r="D560" s="5"/>
       <c r="E560" s="15"/>
       <c r="F560" s="5"/>
       <c r="G560"/>
     </row>
-    <row r="561" spans="3:7" hidden="1">
+    <row r="561" spans="3:7">
       <c r="C561" s="5"/>
       <c r="D561" s="5"/>
       <c r="E561" s="15"/>
       <c r="F561" s="5"/>
       <c r="G561"/>
     </row>
-    <row r="562" spans="3:7" ht="30" hidden="1" customHeight="1">
+    <row r="562" spans="3:7" ht="30" customHeight="1">
       <c r="C562" s="5"/>
       <c r="D562" s="5"/>
       <c r="E562" s="15"/>
       <c r="F562" s="5"/>
       <c r="G562" s="14"/>
     </row>
-    <row r="563" spans="3:7" hidden="1">
+    <row r="563" spans="3:7">
       <c r="C563" s="5"/>
       <c r="D563" s="5"/>
       <c r="E563" s="15"/>
       <c r="F563" s="5"/>
       <c r="G563"/>
     </row>
-    <row r="564" spans="3:7" ht="30" hidden="1" customHeight="1">
+    <row r="564" spans="3:7" ht="30" customHeight="1">
       <c r="C564" s="5"/>
       <c r="D564" s="5"/>
       <c r="E564" s="12"/>
       <c r="F564" s="5"/>
       <c r="G564" s="14"/>
     </row>
-    <row r="565" spans="3:7" hidden="1">
+    <row r="565" spans="3:7">
       <c r="C565" s="5"/>
       <c r="D565" s="5"/>
       <c r="E565" s="15"/>
       <c r="F565" s="5"/>
       <c r="G565"/>
     </row>
-    <row r="566" spans="3:7" hidden="1">
+    <row r="566" spans="3:7">
       <c r="C566" s="5"/>
       <c r="D566" s="5"/>
       <c r="E566" s="15"/>
       <c r="F566" s="5"/>
       <c r="G566"/>
     </row>
-    <row r="567" spans="3:7" hidden="1">
+    <row r="567" spans="3:7">
       <c r="C567" s="5"/>
       <c r="D567" s="5"/>
       <c r="E567" s="15"/>
       <c r="F567" s="5"/>
       <c r="G567"/>
     </row>
-    <row r="568" spans="3:7" hidden="1">
+    <row r="568" spans="3:7">
       <c r="C568" s="5"/>
       <c r="D568" s="5"/>
       <c r="E568" s="15"/>
       <c r="F568" s="5"/>
       <c r="G568"/>
     </row>
-    <row r="569" spans="3:7" hidden="1">
+    <row r="569" spans="3:7">
       <c r="C569" s="5"/>
       <c r="D569" s="5"/>
       <c r="E569" s="15"/>
       <c r="F569" s="5"/>
       <c r="G569"/>
     </row>
-    <row r="570" spans="3:7" hidden="1">
+    <row r="570" spans="3:7">
       <c r="C570" s="5"/>
       <c r="D570" s="5"/>
       <c r="E570" s="15"/>
       <c r="F570" s="5"/>
       <c r="G570"/>
     </row>
-    <row r="571" spans="3:7" hidden="1">
+    <row r="571" spans="3:7">
       <c r="C571" s="5"/>
       <c r="D571" s="5"/>
       <c r="E571" s="15"/>
       <c r="F571" s="5"/>
       <c r="G571"/>
     </row>
-    <row r="572" spans="3:7" hidden="1">
+    <row r="572" spans="3:7">
       <c r="C572" s="5"/>
       <c r="D572" s="5"/>
       <c r="E572" s="15"/>
       <c r="F572" s="5"/>
       <c r="G572"/>
     </row>
-    <row r="573" spans="3:7" hidden="1">
+    <row r="573" spans="3:7">
       <c r="C573" s="5"/>
       <c r="D573" s="5"/>
       <c r="E573" s="15"/>
       <c r="F573" s="5"/>
       <c r="G573"/>
     </row>
-    <row r="574" spans="3:7" hidden="1">
+    <row r="574" spans="3:7">
       <c r="C574" s="5"/>
       <c r="D574" s="5"/>
       <c r="E574" s="15"/>
       <c r="F574" s="5"/>
       <c r="G574"/>
     </row>
-    <row r="575" spans="3:7" hidden="1">
+    <row r="575" spans="3:7">
       <c r="C575" s="5"/>
       <c r="D575" s="5"/>
       <c r="E575" s="15"/>
       <c r="F575" s="5"/>
       <c r="G575"/>
     </row>
-    <row r="576" spans="3:7" hidden="1">
+    <row r="576" spans="3:7">
       <c r="C576" s="5"/>
       <c r="D576" s="5"/>
       <c r="E576" s="15"/>
       <c r="F576" s="5"/>
       <c r="G576"/>
     </row>
-    <row r="577" spans="3:7" hidden="1">
+    <row r="577" spans="3:7">
       <c r="C577" s="5"/>
       <c r="D577" s="5"/>
       <c r="E577" s="15"/>
       <c r="F577" s="5"/>
       <c r="G577"/>
     </row>
-    <row r="578" spans="3:7" hidden="1">
+    <row r="578" spans="3:7">
       <c r="C578" s="5"/>
       <c r="D578" s="5"/>
       <c r="E578" s="15"/>
       <c r="F578" s="5"/>
       <c r="G578"/>
     </row>
-    <row r="579" spans="3:7" hidden="1">
+    <row r="579" spans="3:7">
       <c r="C579" s="5"/>
       <c r="D579" s="5"/>
       <c r="E579" s="15"/>
       <c r="F579" s="5"/>
       <c r="G579"/>
     </row>
-    <row r="580" spans="3:7" hidden="1">
+    <row r="580" spans="3:7">
       <c r="C580" s="5"/>
       <c r="D580" s="5"/>
       <c r="E580" s="15"/>
       <c r="F580" s="5"/>
       <c r="G580"/>
     </row>
-    <row r="581" spans="3:7" hidden="1">
+    <row r="581" spans="3:7">
       <c r="C581" s="5"/>
       <c r="D581" s="5"/>
       <c r="E581" s="15"/>
       <c r="F581" s="5"/>
       <c r="G581"/>
     </row>
-    <row r="582" spans="3:7" hidden="1">
+    <row r="582" spans="3:7">
       <c r="C582" s="5"/>
       <c r="D582" s="5"/>
       <c r="E582" s="15"/>
       <c r="F582" s="5"/>
       <c r="G582"/>
     </row>
-    <row r="583" spans="3:7" hidden="1">
+    <row r="583" spans="3:7">
       <c r="C583" s="5"/>
       <c r="D583" s="5"/>
       <c r="E583" s="15"/>
       <c r="F583" s="5"/>
       <c r="G583"/>
     </row>
-    <row r="584" spans="3:7" hidden="1">
+    <row r="584" spans="3:7">
       <c r="C584" s="5"/>
       <c r="D584" s="5"/>
       <c r="E584" s="15"/>
       <c r="F584" s="5"/>
       <c r="G584"/>
     </row>
-    <row r="585" spans="3:7" hidden="1">
+    <row r="585" spans="3:7">
       <c r="C585" s="5"/>
       <c r="D585" s="5"/>
       <c r="E585" s="15"/>
       <c r="F585" s="5"/>
       <c r="G585"/>
     </row>
-    <row r="586" spans="3:7" hidden="1">
+    <row r="586" spans="3:7">
       <c r="C586" s="5"/>
       <c r="D586" s="5"/>
       <c r="E586" s="15"/>
       <c r="F586" s="5"/>
       <c r="G586"/>
     </row>
-    <row r="587" spans="3:7" hidden="1">
+    <row r="587" spans="3:7">
       <c r="C587" s="5"/>
       <c r="D587" s="5"/>
       <c r="E587" s="15"/>
       <c r="F587" s="5"/>
       <c r="G587"/>
     </row>
-    <row r="588" spans="3:7" hidden="1">
+    <row r="588" spans="3:7">
       <c r="C588" s="5"/>
       <c r="D588" s="5"/>
       <c r="E588" s="15"/>
       <c r="F588" s="5"/>
       <c r="G588"/>
     </row>
-    <row r="589" spans="3:7" hidden="1">
+    <row r="589" spans="3:7">
       <c r="C589" s="5"/>
       <c r="D589" s="5"/>
       <c r="E589" s="15"/>
       <c r="F589" s="5"/>
       <c r="G589"/>
     </row>
-    <row r="590" spans="3:7" hidden="1">
+    <row r="590" spans="3:7">
       <c r="C590" s="5"/>
       <c r="D590" s="5"/>
       <c r="E590" s="15"/>
       <c r="F590" s="5"/>
       <c r="G590"/>
     </row>
-    <row r="591" spans="3:7" hidden="1">
+    <row r="591" spans="3:7">
       <c r="C591" s="5"/>
       <c r="D591" s="5"/>
       <c r="E591" s="15"/>
       <c r="F591" s="5"/>
       <c r="G591"/>
     </row>
-    <row r="592" spans="3:7" hidden="1">
+    <row r="592" spans="3:7">
       <c r="C592" s="5"/>
       <c r="D592" s="5"/>
       <c r="E592" s="15"/>
       <c r="F592" s="5"/>
       <c r="G592"/>
     </row>
-    <row r="593" spans="3:7" hidden="1">
+    <row r="593" spans="3:7">
       <c r="C593" s="5"/>
       <c r="D593" s="5"/>
       <c r="E593" s="15"/>
       <c r="F593" s="5"/>
       <c r="G593"/>
     </row>
-    <row r="594" spans="3:7" hidden="1">
+    <row r="594" spans="3:7">
       <c r="C594" s="5"/>
       <c r="D594" s="5"/>
       <c r="E594" s="15"/>
       <c r="F594" s="5"/>
       <c r="G594"/>
     </row>
-    <row r="595" spans="3:7" hidden="1">
+    <row r="595" spans="3:7">
       <c r="C595" s="5"/>
       <c r="D595" s="5"/>
       <c r="E595" s="15"/>
       <c r="F595" s="5"/>
       <c r="G595"/>
     </row>
-    <row r="596" spans="3:7" hidden="1">
+    <row r="596" spans="3:7">
       <c r="C596" s="5"/>
       <c r="D596" s="5"/>
       <c r="E596" s="15"/>
       <c r="F596" s="5"/>
       <c r="G596"/>
     </row>
-    <row r="597" spans="3:7" hidden="1">
+    <row r="597" spans="3:7">
       <c r="C597" s="5"/>
       <c r="D597" s="5"/>
       <c r="E597" s="15"/>
       <c r="F597" s="5"/>
       <c r="G597"/>
     </row>
-    <row r="598" spans="3:7" hidden="1">
+    <row r="598" spans="3:7">
       <c r="C598" s="5"/>
       <c r="D598" s="5"/>
       <c r="E598" s="15"/>
       <c r="F598" s="5"/>
       <c r="G598"/>
     </row>
-    <row r="599" spans="3:7" hidden="1">
+    <row r="599" spans="3:7">
       <c r="C599" s="5"/>
       <c r="D599" s="5"/>
       <c r="E599" s="15"/>
       <c r="F599" s="5"/>
       <c r="G599"/>
     </row>
-    <row r="600" spans="3:7" hidden="1">
+    <row r="600" spans="3:7">
       <c r="C600" s="5"/>
       <c r="D600" s="5"/>
       <c r="E600" s="15"/>
       <c r="F600" s="5"/>
       <c r="G600"/>
     </row>
-    <row r="601" spans="3:7" hidden="1">
+    <row r="601" spans="3:7">
       <c r="C601" s="5"/>
       <c r="D601" s="5"/>
       <c r="E601" s="15"/>
       <c r="F601" s="5"/>
       <c r="G601"/>
     </row>
-    <row r="602" spans="3:7" hidden="1">
+    <row r="602" spans="3:7">
       <c r="C602" s="5"/>
       <c r="D602" s="5"/>
       <c r="E602" s="15"/>
       <c r="F602" s="5"/>
       <c r="G602"/>
     </row>
-    <row r="603" spans="3:7" hidden="1">
+    <row r="603" spans="3:7">
       <c r="C603" s="5"/>
       <c r="D603" s="5"/>
       <c r="E603" s="15"/>
       <c r="F603" s="5"/>
       <c r="G603"/>
     </row>
-    <row r="604" spans="3:7" hidden="1">
+    <row r="604" spans="3:7">
       <c r="C604" s="5"/>
       <c r="D604" s="5"/>
       <c r="E604" s="15"/>
       <c r="F604" s="5"/>
       <c r="G604"/>
     </row>
-    <row r="605" spans="3:7" hidden="1">
+    <row r="605" spans="3:7">
       <c r="C605" s="5"/>
       <c r="D605" s="5"/>
       <c r="E605" s="15"/>
       <c r="F605" s="5"/>
       <c r="G605"/>
     </row>
-    <row r="606" spans="3:7" hidden="1">
+    <row r="606" spans="3:7">
       <c r="C606" s="5"/>
       <c r="D606" s="5"/>
       <c r="E606" s="15"/>
       <c r="F606" s="5"/>
       <c r="G606"/>
     </row>
-    <row r="607" spans="3:7" hidden="1">
+    <row r="607" spans="3:7">
       <c r="C607" s="5"/>
       <c r="D607" s="5"/>
       <c r="E607" s="15"/>
       <c r="F607" s="5"/>
       <c r="G607"/>
     </row>
-    <row r="608" spans="3:7" hidden="1">
+    <row r="608" spans="3:7">
       <c r="C608" s="5"/>
       <c r="D608" s="5"/>
       <c r="E608" s="15"/>
       <c r="F608" s="5"/>
       <c r="G608"/>
     </row>
-    <row r="609" spans="3:7" hidden="1">
+    <row r="609" spans="3:7">
       <c r="C609" s="5"/>
       <c r="D609" s="5"/>
       <c r="E609" s="15"/>
       <c r="F609" s="5"/>
       <c r="G609"/>
     </row>
-    <row r="610" spans="3:7" hidden="1">
+    <row r="610" spans="3:7">
       <c r="C610" s="5"/>
       <c r="D610" s="5"/>
       <c r="E610" s="15"/>
       <c r="F610" s="5"/>
       <c r="G610"/>
     </row>
-    <row r="611" spans="3:7" hidden="1">
+    <row r="611" spans="3:7">
       <c r="C611" s="5"/>
       <c r="D611" s="5"/>
       <c r="E611" s="15"/>
       <c r="F611" s="5"/>
       <c r="G611"/>
     </row>
-    <row r="612" spans="3:7" hidden="1">
+    <row r="612" spans="3:7">
       <c r="C612" s="5"/>
       <c r="D612" s="5"/>
       <c r="E612" s="15"/>
       <c r="F612" s="5"/>
       <c r="G612"/>
     </row>
-    <row r="613" spans="3:7" hidden="1">
+    <row r="613" spans="3:7">
       <c r="C613" s="5"/>
       <c r="D613" s="5"/>
       <c r="E613" s="15"/>
       <c r="F613" s="5"/>
       <c r="G613"/>
     </row>
-    <row r="614" spans="3:7" hidden="1">
+    <row r="614" spans="3:7">
       <c r="C614" s="5"/>
       <c r="D614" s="5"/>
       <c r="E614" s="15"/>
       <c r="F614" s="5"/>
       <c r="G614"/>
     </row>
-    <row r="615" spans="3:7" hidden="1">
+    <row r="615" spans="3:7">
       <c r="C615" s="5"/>
       <c r="D615" s="5"/>
       <c r="E615" s="15"/>
       <c r="F615" s="5"/>
       <c r="G615"/>
     </row>
-    <row r="616" spans="3:7" hidden="1">
+    <row r="616" spans="3:7">
       <c r="C616" s="5"/>
       <c r="D616" s="5"/>
       <c r="E616" s="15"/>
       <c r="F616" s="5"/>
       <c r="G616"/>
     </row>
-    <row r="617" spans="3:7" hidden="1">
+    <row r="617" spans="3:7">
       <c r="C617" s="5"/>
       <c r="D617" s="5"/>
       <c r="E617" s="15"/>
       <c r="F617" s="5"/>
       <c r="G617"/>
     </row>
-    <row r="618" spans="3:7" hidden="1">
+    <row r="618" spans="3:7">
       <c r="C618" s="5"/>
       <c r="D618" s="5"/>
       <c r="E618" s="15"/>
       <c r="F618" s="5"/>
       <c r="G618"/>
     </row>
-    <row r="619" spans="3:7" hidden="1">
+    <row r="619" spans="3:7">
       <c r="C619" s="5"/>
       <c r="D619" s="5"/>
       <c r="E619" s="15"/>
       <c r="F619" s="5"/>
       <c r="G619"/>
     </row>
-    <row r="620" spans="3:7" hidden="1">
+    <row r="620" spans="3:7">
       <c r="C620" s="5"/>
       <c r="D620" s="5"/>
       <c r="E620" s="15"/>
       <c r="F620" s="5"/>
       <c r="G620"/>
     </row>
-    <row r="621" spans="3:7" hidden="1">
+    <row r="621" spans="3:7">
       <c r="C621" s="5"/>
       <c r="D621" s="5"/>
       <c r="E621" s="15"/>
       <c r="F621" s="5"/>
       <c r="G621"/>
     </row>
-    <row r="622" spans="3:7" hidden="1">
+    <row r="622" spans="3:7">
       <c r="C622" s="5"/>
       <c r="D622" s="5"/>
       <c r="E622" s="15"/>
       <c r="F622" s="5"/>
       <c r="G622"/>
     </row>
-    <row r="623" spans="3:7" hidden="1">
+    <row r="623" spans="3:7">
       <c r="C623" s="5"/>
       <c r="D623" s="5"/>
       <c r="E623" s="15"/>
       <c r="F623" s="5"/>
       <c r="G623"/>
     </row>
-    <row r="624" spans="3:7" hidden="1">
+    <row r="624" spans="3:7">
       <c r="C624" s="5"/>
       <c r="D624" s="5"/>
       <c r="E624" s="15"/>
       <c r="F624" s="5"/>
       <c r="G624"/>
     </row>
-    <row r="625" spans="3:7" hidden="1">
+    <row r="625" spans="3:7">
       <c r="C625" s="5"/>
       <c r="D625" s="5"/>
       <c r="E625" s="15"/>
       <c r="F625" s="5"/>
       <c r="G625"/>
     </row>
-    <row r="626" spans="3:7" hidden="1">
+    <row r="626" spans="3:7">
       <c r="C626" s="5"/>
       <c r="D626" s="5"/>
       <c r="E626" s="15"/>
       <c r="F626" s="5"/>
       <c r="G626"/>
     </row>
-    <row r="627" spans="3:7" hidden="1">
+    <row r="627" spans="3:7">
       <c r="C627" s="5"/>
       <c r="D627" s="5"/>
       <c r="E627" s="15"/>
       <c r="F627" s="5"/>
       <c r="G627"/>
     </row>
-    <row r="628" spans="3:7" hidden="1">
+    <row r="628" spans="3:7">
       <c r="C628" s="5"/>
       <c r="D628" s="5"/>
       <c r="E628" s="15"/>
       <c r="F628" s="5"/>
       <c r="G628"/>
     </row>
-    <row r="629" spans="3:7" hidden="1">
+    <row r="629" spans="3:7">
       <c r="C629" s="5"/>
       <c r="D629" s="5"/>
       <c r="E629" s="15"/>
       <c r="F629" s="5"/>
       <c r="G629"/>
     </row>
-    <row r="630" spans="3:7" hidden="1">
+    <row r="630" spans="3:7">
       <c r="C630" s="5"/>
       <c r="D630" s="5"/>
       <c r="E630" s="15"/>
       <c r="F630" s="5"/>
       <c r="G630"/>
     </row>
-    <row r="631" spans="3:7" hidden="1">
+    <row r="631" spans="3:7">
       <c r="C631" s="5"/>
       <c r="D631" s="5"/>
       <c r="E631" s="15"/>
       <c r="F631" s="5"/>
       <c r="G631"/>
     </row>
-    <row r="632" spans="3:7" hidden="1">
+    <row r="632" spans="3:7">
       <c r="C632" s="5"/>
       <c r="D632" s="5"/>
       <c r="E632" s="15"/>
       <c r="F632" s="5"/>
       <c r="G632"/>
     </row>
-    <row r="633" spans="3:7" hidden="1">
+    <row r="633" spans="3:7">
       <c r="C633" s="5"/>
       <c r="D633" s="5"/>
       <c r="E633" s="15"/>
       <c r="F633" s="5"/>
       <c r="G633"/>
     </row>
-    <row r="634" spans="3:7" hidden="1">
+    <row r="634" spans="3:7">
       <c r="C634" s="5"/>
       <c r="D634" s="5"/>
       <c r="E634" s="15"/>
       <c r="F634" s="5"/>
       <c r="G634"/>
     </row>
-    <row r="635" spans="3:7" hidden="1">
+    <row r="635" spans="3:7">
       <c r="C635" s="5"/>
       <c r="D635" s="5"/>
       <c r="E635" s="15"/>
       <c r="F635" s="5"/>
       <c r="G635"/>
     </row>
-    <row r="636" spans="3:7" hidden="1">
+    <row r="636" spans="3:7">
       <c r="C636" s="5"/>
       <c r="D636" s="5"/>
       <c r="E636" s="15"/>
       <c r="F636" s="5"/>
       <c r="G636"/>
     </row>
-    <row r="637" spans="3:7" hidden="1">
+    <row r="637" spans="3:7">
       <c r="C637" s="5"/>
       <c r="D637" s="5"/>
       <c r="E637" s="15"/>
       <c r="F637" s="5"/>
       <c r="G637"/>
     </row>
-    <row r="638" spans="3:7" hidden="1">
+    <row r="638" spans="3:7">
       <c r="C638" s="5"/>
       <c r="D638" s="5"/>
       <c r="E638" s="15"/>
       <c r="F638" s="5"/>
       <c r="G638"/>
     </row>
-    <row r="639" spans="3:7" hidden="1">
+    <row r="639" spans="3:7">
       <c r="C639" s="5"/>
       <c r="D639" s="5"/>
       <c r="E639" s="15"/>
       <c r="F639" s="5"/>
       <c r="G639"/>
     </row>
-    <row r="640" spans="3:7" hidden="1">
+    <row r="640" spans="3:7">
       <c r="C640" s="5"/>
       <c r="D640" s="5"/>
       <c r="E640" s="15"/>
       <c r="F640" s="5"/>
       <c r="G640"/>
     </row>
-    <row r="641" spans="3:7" hidden="1">
+    <row r="641" spans="3:7">
       <c r="C641" s="5"/>
       <c r="D641" s="5"/>
       <c r="E641" s="15"/>
       <c r="F641" s="5"/>
       <c r="G641"/>
     </row>
-    <row r="642" spans="3:7" hidden="1">
+    <row r="642" spans="3:7">
       <c r="C642" s="5"/>
       <c r="D642" s="5"/>
       <c r="E642" s="15"/>
       <c r="F642" s="5"/>
       <c r="G642"/>
     </row>
-    <row r="643" spans="3:7" hidden="1">
+    <row r="643" spans="3:7">
       <c r="C643" s="5"/>
       <c r="D643" s="5"/>
       <c r="E643" s="15"/>
       <c r="F643" s="5"/>
       <c r="G643"/>
     </row>
-    <row r="644" spans="3:7" hidden="1">
+    <row r="644" spans="3:7">
       <c r="C644" s="5"/>
       <c r="D644" s="5"/>
       <c r="E644" s="15"/>
       <c r="F644" s="5"/>
       <c r="G644"/>
     </row>
-    <row r="645" spans="3:7" hidden="1">
+    <row r="645" spans="3:7">
       <c r="C645" s="5"/>
       <c r="D645" s="5"/>
       <c r="E645" s="15"/>
       <c r="F645" s="5"/>
       <c r="G645"/>
     </row>
-    <row r="646" spans="3:7" hidden="1">
+    <row r="646" spans="3:7">
       <c r="C646" s="5"/>
       <c r="D646" s="5"/>
       <c r="E646" s="15"/>
       <c r="F646" s="5"/>
       <c r="G646"/>
     </row>
-    <row r="647" spans="3:7" hidden="1">
+    <row r="647" spans="3:7">
       <c r="C647" s="5"/>
       <c r="D647" s="5"/>
       <c r="E647" s="15"/>
       <c r="F647" s="5"/>
       <c r="G647"/>
     </row>
-    <row r="648" spans="3:7" hidden="1">
+    <row r="648" spans="3:7">
       <c r="C648" s="5"/>
       <c r="D648" s="5"/>
       <c r="E648" s="15"/>
       <c r="F648" s="5"/>
       <c r="G648"/>
     </row>
-    <row r="649" spans="3:7" hidden="1">
+    <row r="649" spans="3:7">
       <c r="C649" s="5"/>
       <c r="D649" s="5"/>
       <c r="E649" s="15"/>
       <c r="F649" s="5"/>
       <c r="G649"/>
     </row>
-    <row r="650" spans="3:7" hidden="1">
+    <row r="650" spans="3:7">
       <c r="C650" s="5"/>
       <c r="D650" s="5"/>
       <c r="E650" s="15"/>
       <c r="F650" s="5"/>
       <c r="G650"/>
     </row>
-    <row r="651" spans="3:7" hidden="1">
+    <row r="651" spans="3:7">
       <c r="C651" s="5"/>
       <c r="D651" s="5"/>
       <c r="E651" s="15"/>
       <c r="F651" s="5"/>
       <c r="G651"/>
     </row>
-    <row r="652" spans="3:7" hidden="1">
+    <row r="652" spans="3:7">
       <c r="C652" s="5"/>
       <c r="D652" s="5"/>
       <c r="E652" s="15"/>
       <c r="F652" s="5"/>
       <c r="G652"/>
     </row>
-    <row r="653" spans="3:7" hidden="1">
+    <row r="653" spans="3:7">
       <c r="C653" s="5"/>
       <c r="D653" s="5"/>
       <c r="E653" s="15"/>
       <c r="F653" s="5"/>
       <c r="G653"/>
     </row>
-    <row r="654" spans="3:7" hidden="1">
+    <row r="654" spans="3:7">
       <c r="C654" s="5"/>
       <c r="D654" s="5"/>
       <c r="E654" s="15"/>
       <c r="F654" s="5"/>
       <c r="G654"/>
     </row>
-    <row r="655" spans="3:7" hidden="1">
+    <row r="655" spans="3:7">
       <c r="C655" s="5"/>
       <c r="D655" s="5"/>
       <c r="E655" s="15"/>
       <c r="F655" s="5"/>
       <c r="G655"/>
     </row>
-    <row r="656" spans="3:7" hidden="1">
+    <row r="656" spans="3:7">
       <c r="C656" s="5"/>
       <c r="D656" s="5"/>
       <c r="E656" s="15"/>
       <c r="F656" s="5"/>
       <c r="G656"/>
     </row>
-    <row r="657" spans="1:7" hidden="1">
+    <row r="657" spans="1:7">
       <c r="C657" s="5"/>
       <c r="D657" s="5"/>
       <c r="E657" s="15"/>
       <c r="F657" s="5"/>
       <c r="G657"/>
     </row>
-    <row r="658" spans="1:7" hidden="1">
+    <row r="658" spans="1:7">
       <c r="C658" s="5"/>
       <c r="D658" s="5"/>
       <c r="E658" s="15"/>
       <c r="F658" s="5"/>
       <c r="G658"/>
     </row>
-    <row r="659" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="659" spans="1:7" ht="30" customHeight="1">
       <c r="A659" s="13"/>
       <c r="C659" s="5"/>
       <c r="D659" s="5"/>
@@ -10829,7 +10828,7 @@
       <c r="F659" s="12"/>
       <c r="G659" s="14"/>
     </row>
-    <row r="660" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="660" spans="1:7" ht="30" customHeight="1">
       <c r="A660" s="13"/>
       <c r="C660" s="5"/>
       <c r="D660" s="5"/>
@@ -10837,7 +10836,7 @@
       <c r="F660" s="5"/>
       <c r="G660" s="14"/>
     </row>
-    <row r="661" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="661" spans="1:7" ht="30" customHeight="1">
       <c r="A661" s="13"/>
       <c r="C661" s="5"/>
       <c r="D661" s="5"/>
@@ -10845,7 +10844,7 @@
       <c r="F661" s="5"/>
       <c r="G661" s="14"/>
     </row>
-    <row r="662" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="662" spans="1:7" ht="30" customHeight="1">
       <c r="A662" s="13"/>
       <c r="C662" s="5"/>
       <c r="D662" s="5"/>
@@ -10853,7 +10852,7 @@
       <c r="F662" s="5"/>
       <c r="G662" s="14"/>
     </row>
-    <row r="663" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="663" spans="1:7" ht="30" customHeight="1">
       <c r="A663" s="13"/>
       <c r="C663" s="5"/>
       <c r="D663" s="5"/>
@@ -10861,7 +10860,7 @@
       <c r="F663" s="5"/>
       <c r="G663" s="14"/>
     </row>
-    <row r="664" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="664" spans="1:7" ht="30" customHeight="1">
       <c r="A664" s="13"/>
       <c r="C664" s="5"/>
       <c r="D664" s="5"/>
@@ -10869,14 +10868,14 @@
       <c r="F664" s="5"/>
       <c r="G664" s="14"/>
     </row>
-    <row r="665" spans="1:7" hidden="1">
+    <row r="665" spans="1:7">
       <c r="C665" s="5"/>
       <c r="D665" s="5"/>
       <c r="E665" s="15"/>
       <c r="F665" s="5"/>
       <c r="G665"/>
     </row>
-    <row r="666" spans="1:7" hidden="1">
+    <row r="666" spans="1:7">
       <c r="A666" s="7"/>
       <c r="B666" s="7"/>
       <c r="C666" s="11"/>
@@ -10885,28 +10884,28 @@
       <c r="F666" s="11"/>
       <c r="G666" s="10"/>
     </row>
-    <row r="667" spans="1:7" hidden="1">
+    <row r="667" spans="1:7">
       <c r="C667" s="5"/>
       <c r="D667" s="5"/>
       <c r="E667" s="15"/>
       <c r="F667" s="5"/>
       <c r="G667" s="3"/>
     </row>
-    <row r="668" spans="1:7" hidden="1">
+    <row r="668" spans="1:7">
       <c r="C668" s="5"/>
       <c r="D668" s="5"/>
       <c r="E668" s="15"/>
       <c r="F668" s="5"/>
       <c r="G668" s="3"/>
     </row>
-    <row r="669" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="669" spans="1:7" ht="30" customHeight="1">
       <c r="C669" s="5"/>
       <c r="D669" s="5"/>
       <c r="E669" s="15"/>
       <c r="F669" s="5"/>
       <c r="G669" s="14"/>
     </row>
-    <row r="670" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="670" spans="1:7" ht="30" customHeight="1">
       <c r="A670" s="13"/>
       <c r="B670" s="13"/>
       <c r="C670" s="5"/>
@@ -10915,21 +10914,21 @@
       <c r="F670" s="5"/>
       <c r="G670" s="14"/>
     </row>
-    <row r="671" spans="1:7" hidden="1">
+    <row r="671" spans="1:7">
       <c r="C671" s="5"/>
       <c r="D671" s="5"/>
       <c r="E671" s="15"/>
       <c r="F671" s="5"/>
       <c r="G671" s="3"/>
     </row>
-    <row r="672" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="672" spans="1:7" ht="30" customHeight="1">
       <c r="C672" s="5"/>
       <c r="D672" s="5"/>
       <c r="E672" s="12"/>
       <c r="F672" s="5"/>
       <c r="G672" s="14"/>
     </row>
-    <row r="673" spans="1:7" hidden="1">
+    <row r="673" spans="1:7">
       <c r="A673" s="7"/>
       <c r="B673" s="7"/>
       <c r="C673" s="8"/>
@@ -10938,84 +10937,84 @@
       <c r="F673" s="8"/>
       <c r="G673" s="10"/>
     </row>
-    <row r="674" spans="1:7" hidden="1">
+    <row r="674" spans="1:7">
       <c r="C674" s="5"/>
       <c r="D674" s="5"/>
       <c r="E674" s="15"/>
       <c r="F674" s="5"/>
       <c r="G674" s="3"/>
     </row>
-    <row r="675" spans="1:7" hidden="1">
+    <row r="675" spans="1:7">
       <c r="C675" s="5"/>
       <c r="D675" s="5"/>
       <c r="E675" s="15"/>
       <c r="F675" s="5"/>
       <c r="G675" s="3"/>
     </row>
-    <row r="676" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="676" spans="1:7" ht="30" customHeight="1">
       <c r="C676" s="5"/>
       <c r="D676" s="5"/>
       <c r="E676" s="15"/>
       <c r="F676" s="5"/>
       <c r="G676" s="14"/>
     </row>
-    <row r="677" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="677" spans="1:7" ht="30" customHeight="1">
       <c r="C677" s="5"/>
       <c r="D677" s="5"/>
       <c r="E677" s="15"/>
       <c r="F677" s="5"/>
       <c r="G677" s="14"/>
     </row>
-    <row r="678" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="678" spans="1:7" ht="30" customHeight="1">
       <c r="C678" s="5"/>
       <c r="D678" s="5"/>
       <c r="E678" s="15"/>
       <c r="F678" s="5"/>
       <c r="G678" s="14"/>
     </row>
-    <row r="679" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="679" spans="1:7" ht="30" customHeight="1">
       <c r="C679" s="5"/>
       <c r="D679" s="5"/>
       <c r="E679" s="15"/>
       <c r="F679" s="5"/>
       <c r="G679" s="14"/>
     </row>
-    <row r="680" spans="1:7" hidden="1">
+    <row r="680" spans="1:7">
       <c r="C680" s="5"/>
       <c r="D680" s="5"/>
       <c r="E680" s="15"/>
       <c r="F680" s="5"/>
       <c r="G680" s="3"/>
     </row>
-    <row r="681" spans="1:7" hidden="1">
+    <row r="681" spans="1:7">
       <c r="C681" s="5"/>
       <c r="D681" s="5"/>
       <c r="E681" s="15"/>
       <c r="F681" s="5"/>
       <c r="G681" s="3"/>
     </row>
-    <row r="682" spans="1:7" hidden="1">
+    <row r="682" spans="1:7">
       <c r="C682" s="5"/>
       <c r="D682" s="5"/>
       <c r="E682" s="15"/>
       <c r="F682" s="5"/>
       <c r="G682" s="3"/>
     </row>
-    <row r="683" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="683" spans="1:7" ht="30" customHeight="1">
       <c r="C683" s="5"/>
       <c r="D683" s="5"/>
       <c r="E683" s="15"/>
       <c r="F683" s="5"/>
       <c r="G683" s="14"/>
     </row>
-    <row r="684" spans="1:7" hidden="1">
+    <row r="684" spans="1:7">
       <c r="C684" s="5"/>
       <c r="D684" s="5"/>
       <c r="E684" s="15"/>
       <c r="F684" s="5"/>
       <c r="G684" s="3"/>
     </row>
-    <row r="685" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="685" spans="1:7" ht="30" customHeight="1">
       <c r="A685" s="13"/>
       <c r="C685" s="5"/>
       <c r="D685" s="5"/>
@@ -11023,7 +11022,7 @@
       <c r="F685" s="5"/>
       <c r="G685" s="14"/>
     </row>
-    <row r="686" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="686" spans="1:7" ht="30" customHeight="1">
       <c r="A686" s="13"/>
       <c r="C686" s="5"/>
       <c r="D686" s="5"/>
@@ -11031,7 +11030,7 @@
       <c r="F686" s="5"/>
       <c r="G686" s="14"/>
     </row>
-    <row r="687" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="687" spans="1:7" ht="30" customHeight="1">
       <c r="A687" s="13"/>
       <c r="C687" s="5"/>
       <c r="D687" s="5"/>
@@ -11039,21 +11038,21 @@
       <c r="F687" s="5"/>
       <c r="G687" s="14"/>
     </row>
-    <row r="688" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="688" spans="1:7" ht="30" customHeight="1">
       <c r="C688" s="5"/>
       <c r="D688" s="5"/>
       <c r="E688" s="12"/>
       <c r="F688" s="5"/>
       <c r="G688" s="14"/>
     </row>
-    <row r="689" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="689" spans="1:7" ht="30" customHeight="1">
       <c r="C689" s="5"/>
       <c r="D689" s="5"/>
       <c r="E689" s="12"/>
       <c r="F689" s="5"/>
       <c r="G689" s="14"/>
     </row>
-    <row r="690" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="690" spans="1:7" ht="30" customHeight="1">
       <c r="A690" s="13"/>
       <c r="C690" s="5"/>
       <c r="D690" s="5"/>
@@ -11061,7 +11060,7 @@
       <c r="F690" s="5"/>
       <c r="G690" s="14"/>
     </row>
-    <row r="691" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="691" spans="1:7" ht="30" customHeight="1">
       <c r="A691" s="13"/>
       <c r="C691" s="5"/>
       <c r="D691" s="5"/>
@@ -11069,7 +11068,7 @@
       <c r="F691" s="5"/>
       <c r="G691" s="14"/>
     </row>
-    <row r="692" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="692" spans="1:7" ht="30" customHeight="1">
       <c r="A692" s="13"/>
       <c r="C692" s="5"/>
       <c r="D692" s="5"/>
@@ -11077,7 +11076,7 @@
       <c r="F692" s="5"/>
       <c r="G692" s="14"/>
     </row>
-    <row r="693" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="693" spans="1:7" ht="30" customHeight="1">
       <c r="A693" s="13"/>
       <c r="C693" s="5"/>
       <c r="D693" s="5"/>
@@ -11085,7 +11084,7 @@
       <c r="F693" s="5"/>
       <c r="G693" s="14"/>
     </row>
-    <row r="694" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="694" spans="1:7" ht="30" customHeight="1">
       <c r="A694" s="13"/>
       <c r="C694" s="5"/>
       <c r="D694" s="5"/>
@@ -11093,7 +11092,7 @@
       <c r="F694" s="5"/>
       <c r="G694" s="14"/>
     </row>
-    <row r="695" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="695" spans="1:7" ht="30" customHeight="1">
       <c r="A695" s="13"/>
       <c r="C695" s="5"/>
       <c r="D695" s="5"/>
@@ -11101,210 +11100,210 @@
       <c r="F695" s="5"/>
       <c r="G695" s="14"/>
     </row>
-    <row r="696" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="696" spans="1:7" ht="30" customHeight="1">
       <c r="C696" s="5"/>
       <c r="D696" s="5"/>
       <c r="E696" s="15"/>
       <c r="F696" s="5"/>
       <c r="G696" s="14"/>
     </row>
-    <row r="697" spans="1:7" hidden="1">
+    <row r="697" spans="1:7">
       <c r="C697" s="5"/>
       <c r="D697" s="5"/>
       <c r="E697" s="15"/>
       <c r="F697" s="5"/>
       <c r="G697" s="3"/>
     </row>
-    <row r="698" spans="1:7" hidden="1">
+    <row r="698" spans="1:7">
       <c r="C698" s="5"/>
       <c r="D698" s="5"/>
       <c r="E698" s="15"/>
       <c r="F698" s="5"/>
       <c r="G698" s="3"/>
     </row>
-    <row r="699" spans="1:7" hidden="1">
+    <row r="699" spans="1:7">
       <c r="C699" s="5"/>
       <c r="D699" s="5"/>
       <c r="E699" s="15"/>
       <c r="F699" s="5"/>
       <c r="G699" s="3"/>
     </row>
-    <row r="700" spans="1:7" hidden="1">
+    <row r="700" spans="1:7">
       <c r="C700" s="5"/>
       <c r="D700" s="5"/>
       <c r="E700" s="15"/>
       <c r="F700" s="5"/>
       <c r="G700" s="3"/>
     </row>
-    <row r="701" spans="1:7" hidden="1">
+    <row r="701" spans="1:7">
       <c r="C701" s="5"/>
       <c r="D701" s="5"/>
       <c r="E701" s="15"/>
       <c r="F701" s="5"/>
       <c r="G701" s="3"/>
     </row>
-    <row r="702" spans="1:7" hidden="1">
+    <row r="702" spans="1:7">
       <c r="C702" s="5"/>
       <c r="D702" s="5"/>
       <c r="E702" s="15"/>
       <c r="F702" s="5"/>
       <c r="G702" s="3"/>
     </row>
-    <row r="703" spans="1:7" hidden="1">
+    <row r="703" spans="1:7">
       <c r="C703" s="5"/>
       <c r="D703" s="5"/>
       <c r="E703" s="15"/>
       <c r="F703" s="5"/>
       <c r="G703" s="3"/>
     </row>
-    <row r="704" spans="1:7" hidden="1">
+    <row r="704" spans="1:7">
       <c r="C704" s="5"/>
       <c r="D704" s="5"/>
       <c r="E704" s="15"/>
       <c r="F704" s="5"/>
       <c r="G704" s="3"/>
     </row>
-    <row r="705" spans="3:7" hidden="1">
+    <row r="705" spans="3:7">
       <c r="C705" s="5"/>
       <c r="D705" s="5"/>
       <c r="E705" s="15"/>
       <c r="F705" s="5"/>
       <c r="G705" s="3"/>
     </row>
-    <row r="706" spans="3:7" hidden="1">
+    <row r="706" spans="3:7">
       <c r="C706" s="5"/>
       <c r="D706" s="5"/>
       <c r="E706" s="15"/>
       <c r="F706" s="5"/>
       <c r="G706" s="3"/>
     </row>
-    <row r="707" spans="3:7" hidden="1">
+    <row r="707" spans="3:7">
       <c r="C707" s="5"/>
       <c r="D707" s="5"/>
       <c r="E707" s="15"/>
       <c r="F707" s="5"/>
       <c r="G707" s="3"/>
     </row>
-    <row r="708" spans="3:7" hidden="1">
+    <row r="708" spans="3:7">
       <c r="C708" s="5"/>
       <c r="D708" s="5"/>
       <c r="E708" s="15"/>
       <c r="F708" s="5"/>
       <c r="G708" s="3"/>
     </row>
-    <row r="709" spans="3:7" hidden="1">
+    <row r="709" spans="3:7">
       <c r="C709" s="5"/>
       <c r="D709" s="5"/>
       <c r="E709" s="15"/>
       <c r="F709" s="5"/>
       <c r="G709" s="3"/>
     </row>
-    <row r="710" spans="3:7" hidden="1">
+    <row r="710" spans="3:7">
       <c r="C710" s="5"/>
       <c r="D710" s="5"/>
       <c r="E710" s="15"/>
       <c r="F710" s="5"/>
       <c r="G710" s="3"/>
     </row>
-    <row r="711" spans="3:7" hidden="1">
+    <row r="711" spans="3:7">
       <c r="C711" s="5"/>
       <c r="D711" s="5"/>
       <c r="E711" s="15"/>
       <c r="F711" s="5"/>
       <c r="G711" s="3"/>
     </row>
-    <row r="712" spans="3:7" hidden="1">
+    <row r="712" spans="3:7">
       <c r="C712" s="5"/>
       <c r="D712" s="5"/>
       <c r="E712" s="15"/>
       <c r="F712" s="5"/>
       <c r="G712" s="3"/>
     </row>
-    <row r="713" spans="3:7" hidden="1">
+    <row r="713" spans="3:7">
       <c r="C713" s="5"/>
       <c r="D713" s="5"/>
       <c r="E713" s="15"/>
       <c r="F713" s="5"/>
       <c r="G713" s="3"/>
     </row>
-    <row r="714" spans="3:7" hidden="1">
+    <row r="714" spans="3:7">
       <c r="C714" s="5"/>
       <c r="D714" s="5"/>
       <c r="E714" s="15"/>
       <c r="F714" s="5"/>
       <c r="G714" s="3"/>
     </row>
-    <row r="715" spans="3:7" hidden="1">
+    <row r="715" spans="3:7">
       <c r="C715" s="5"/>
       <c r="D715" s="5"/>
       <c r="E715" s="15"/>
       <c r="F715" s="5"/>
       <c r="G715" s="3"/>
     </row>
-    <row r="716" spans="3:7" hidden="1">
+    <row r="716" spans="3:7">
       <c r="C716" s="5"/>
       <c r="D716" s="5"/>
       <c r="E716" s="15"/>
       <c r="F716" s="5"/>
       <c r="G716" s="3"/>
     </row>
-    <row r="717" spans="3:7" hidden="1">
+    <row r="717" spans="3:7">
       <c r="C717" s="5"/>
       <c r="D717" s="5"/>
       <c r="E717" s="15"/>
       <c r="F717" s="5"/>
       <c r="G717" s="3"/>
     </row>
-    <row r="718" spans="3:7" hidden="1">
+    <row r="718" spans="3:7">
       <c r="C718" s="5"/>
       <c r="D718" s="5"/>
       <c r="E718" s="15"/>
       <c r="F718" s="5"/>
       <c r="G718" s="3"/>
     </row>
-    <row r="719" spans="3:7" hidden="1">
+    <row r="719" spans="3:7">
       <c r="C719" s="5"/>
       <c r="D719" s="5"/>
       <c r="E719" s="15"/>
       <c r="F719" s="5"/>
       <c r="G719" s="3"/>
     </row>
-    <row r="720" spans="3:7" hidden="1">
+    <row r="720" spans="3:7">
       <c r="C720" s="5"/>
       <c r="D720" s="5"/>
       <c r="E720" s="15"/>
       <c r="F720" s="5"/>
       <c r="G720" s="3"/>
     </row>
-    <row r="721" spans="1:7" hidden="1">
+    <row r="721" spans="1:7">
       <c r="C721" s="5"/>
       <c r="D721" s="5"/>
       <c r="E721" s="15"/>
       <c r="F721" s="5"/>
       <c r="G721" s="3"/>
     </row>
-    <row r="722" spans="1:7" hidden="1">
+    <row r="722" spans="1:7">
       <c r="C722" s="5"/>
       <c r="D722" s="5"/>
       <c r="E722" s="15"/>
       <c r="F722" s="5"/>
       <c r="G722" s="3"/>
     </row>
-    <row r="723" spans="1:7" hidden="1">
+    <row r="723" spans="1:7">
       <c r="C723" s="5"/>
       <c r="D723" s="5"/>
       <c r="E723" s="15"/>
       <c r="F723" s="5"/>
       <c r="G723" s="3"/>
     </row>
-    <row r="724" spans="1:7" hidden="1">
+    <row r="724" spans="1:7">
       <c r="C724" s="5"/>
       <c r="D724" s="5"/>
       <c r="E724" s="15"/>
       <c r="F724" s="5"/>
       <c r="G724" s="3"/>
     </row>
-    <row r="725" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="725" spans="1:7" ht="30" customHeight="1">
       <c r="B725" s="13"/>
       <c r="C725" s="5"/>
       <c r="D725" s="5"/>
@@ -11312,7 +11311,7 @@
       <c r="F725" s="5"/>
       <c r="G725" s="14"/>
     </row>
-    <row r="726" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="726" spans="1:7" ht="30" customHeight="1">
       <c r="B726" s="13"/>
       <c r="C726" s="15"/>
       <c r="D726" s="5"/>
@@ -11320,21 +11319,21 @@
       <c r="F726" s="5"/>
       <c r="G726" s="14"/>
     </row>
-    <row r="727" spans="1:7" hidden="1">
+    <row r="727" spans="1:7">
       <c r="C727" s="15"/>
       <c r="D727" s="5"/>
       <c r="E727" s="15"/>
       <c r="F727" s="5"/>
       <c r="G727" s="14"/>
     </row>
-    <row r="728" spans="1:7" hidden="1">
+    <row r="728" spans="1:7">
       <c r="C728" s="15"/>
       <c r="D728" s="5"/>
       <c r="E728" s="15"/>
       <c r="F728" s="5"/>
       <c r="G728" s="14"/>
     </row>
-    <row r="729" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="729" spans="1:7" ht="30" customHeight="1">
       <c r="B729" s="13"/>
       <c r="C729" s="15"/>
       <c r="D729" s="5"/>
@@ -11342,7 +11341,7 @@
       <c r="F729" s="5"/>
       <c r="G729" s="14"/>
     </row>
-    <row r="730" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="730" spans="1:7" ht="30" customHeight="1">
       <c r="B730" s="13"/>
       <c r="C730" s="15"/>
       <c r="D730" s="5"/>
@@ -11350,7 +11349,7 @@
       <c r="F730" s="5"/>
       <c r="G730" s="14"/>
     </row>
-    <row r="731" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="731" spans="1:7" ht="30" customHeight="1">
       <c r="B731" s="13"/>
       <c r="C731" s="15"/>
       <c r="D731" s="5"/>
@@ -11358,7 +11357,7 @@
       <c r="F731" s="5"/>
       <c r="G731" s="14"/>
     </row>
-    <row r="732" spans="1:7" hidden="1">
+    <row r="732" spans="1:7">
       <c r="B732" s="13"/>
       <c r="C732" s="15"/>
       <c r="D732" s="5"/>
@@ -11366,21 +11365,21 @@
       <c r="F732" s="5"/>
       <c r="G732" s="14"/>
     </row>
-    <row r="733" spans="1:7" hidden="1">
+    <row r="733" spans="1:7">
       <c r="C733" s="15"/>
       <c r="D733" s="5"/>
       <c r="E733" s="15"/>
       <c r="F733" s="5"/>
       <c r="G733" s="14"/>
     </row>
-    <row r="734" spans="1:7" hidden="1">
+    <row r="734" spans="1:7">
       <c r="C734" s="15"/>
       <c r="D734" s="5"/>
       <c r="E734" s="15"/>
       <c r="F734" s="5"/>
       <c r="G734" s="14"/>
     </row>
-    <row r="735" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="735" spans="1:7" ht="30" customHeight="1">
       <c r="B735" s="13"/>
       <c r="C735" s="15"/>
       <c r="D735" s="5"/>
@@ -11388,7 +11387,7 @@
       <c r="F735" s="5"/>
       <c r="G735" s="14"/>
     </row>
-    <row r="736" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="736" spans="1:7" ht="30" customHeight="1">
       <c r="A736" s="13"/>
       <c r="B736" s="13"/>
       <c r="C736" s="15"/>
@@ -11397,14 +11396,14 @@
       <c r="F736" s="5"/>
       <c r="G736" s="14"/>
     </row>
-    <row r="737" spans="1:7" hidden="1">
+    <row r="737" spans="1:7">
       <c r="C737" s="15"/>
       <c r="D737" s="5"/>
       <c r="E737" s="15"/>
       <c r="F737" s="5"/>
       <c r="G737" s="14"/>
     </row>
-    <row r="738" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="738" spans="1:7" ht="30" customHeight="1">
       <c r="B738" s="13"/>
       <c r="C738" s="15"/>
       <c r="D738" s="5"/>
@@ -11412,14 +11411,14 @@
       <c r="F738" s="5"/>
       <c r="G738" s="14"/>
     </row>
-    <row r="739" spans="1:7" hidden="1">
+    <row r="739" spans="1:7">
       <c r="C739" s="15"/>
       <c r="D739" s="5"/>
       <c r="E739" s="15"/>
       <c r="F739" s="5"/>
       <c r="G739" s="14"/>
     </row>
-    <row r="740" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="740" spans="1:7" ht="30" customHeight="1">
       <c r="B740" s="13"/>
       <c r="C740" s="15"/>
       <c r="D740" s="5"/>
@@ -11427,7 +11426,7 @@
       <c r="F740" s="5"/>
       <c r="G740" s="14"/>
     </row>
-    <row r="741" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="741" spans="1:7" ht="30" customHeight="1">
       <c r="B741" s="13"/>
       <c r="C741" s="15"/>
       <c r="D741" s="5"/>
@@ -11435,7 +11434,7 @@
       <c r="F741" s="5"/>
       <c r="G741" s="14"/>
     </row>
-    <row r="742" spans="1:7" hidden="1">
+    <row r="742" spans="1:7">
       <c r="A742" s="13"/>
       <c r="C742" s="15"/>
       <c r="D742" s="5"/>
@@ -11443,7 +11442,7 @@
       <c r="F742" s="5"/>
       <c r="G742" s="14"/>
     </row>
-    <row r="743" spans="1:7" hidden="1">
+    <row r="743" spans="1:7">
       <c r="A743" s="13"/>
       <c r="C743" s="15"/>
       <c r="D743" s="5"/>
@@ -11451,7 +11450,7 @@
       <c r="F743" s="5"/>
       <c r="G743" s="14"/>
     </row>
-    <row r="744" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="744" spans="1:7" ht="30" customHeight="1">
       <c r="B744" s="13"/>
       <c r="C744" s="15"/>
       <c r="D744" s="5"/>
@@ -11459,14 +11458,14 @@
       <c r="F744" s="5"/>
       <c r="G744" s="14"/>
     </row>
-    <row r="745" spans="1:7" hidden="1">
+    <row r="745" spans="1:7">
       <c r="C745" s="15"/>
       <c r="D745" s="5"/>
       <c r="E745" s="15"/>
       <c r="F745" s="5"/>
       <c r="G745" s="14"/>
     </row>
-    <row r="746" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="746" spans="1:7" ht="30" customHeight="1">
       <c r="B746" s="13"/>
       <c r="C746" s="15"/>
       <c r="D746" s="5"/>
@@ -11474,208 +11473,208 @@
       <c r="F746" s="5"/>
       <c r="G746" s="14"/>
     </row>
-    <row r="747" spans="1:7" hidden="1">
+    <row r="747" spans="1:7">
       <c r="C747" s="15"/>
       <c r="D747" s="5"/>
       <c r="E747" s="15"/>
       <c r="F747" s="5"/>
       <c r="G747" s="14"/>
     </row>
-    <row r="748" spans="1:7" hidden="1">
+    <row r="748" spans="1:7">
       <c r="C748" s="15"/>
       <c r="D748" s="5"/>
       <c r="E748" s="15"/>
       <c r="F748" s="5"/>
       <c r="G748" s="14"/>
     </row>
-    <row r="749" spans="1:7" hidden="1">
+    <row r="749" spans="1:7">
       <c r="C749" s="15"/>
       <c r="D749" s="5"/>
       <c r="E749" s="15"/>
       <c r="F749" s="5"/>
       <c r="G749" s="14"/>
     </row>
-    <row r="750" spans="1:7" hidden="1">
+    <row r="750" spans="1:7">
       <c r="C750" s="15"/>
       <c r="D750" s="5"/>
       <c r="E750" s="15"/>
       <c r="F750" s="5"/>
       <c r="G750" s="14"/>
     </row>
-    <row r="751" spans="1:7" hidden="1">
+    <row r="751" spans="1:7">
       <c r="C751" s="15"/>
       <c r="D751" s="5"/>
       <c r="E751" s="15"/>
       <c r="F751" s="5"/>
       <c r="G751" s="14"/>
     </row>
-    <row r="752" spans="1:7" hidden="1">
+    <row r="752" spans="1:7">
       <c r="C752" s="15"/>
       <c r="D752" s="5"/>
       <c r="E752" s="15"/>
       <c r="F752" s="5"/>
       <c r="G752" s="14"/>
     </row>
-    <row r="753" spans="3:7" hidden="1">
+    <row r="753" spans="3:7">
       <c r="C753" s="15"/>
       <c r="D753" s="5"/>
       <c r="E753" s="15"/>
       <c r="F753" s="5"/>
       <c r="G753" s="14"/>
     </row>
-    <row r="754" spans="3:7" hidden="1">
+    <row r="754" spans="3:7">
       <c r="C754" s="15"/>
       <c r="D754" s="5"/>
       <c r="E754" s="15"/>
       <c r="F754" s="5"/>
       <c r="G754" s="14"/>
     </row>
-    <row r="755" spans="3:7" hidden="1">
+    <row r="755" spans="3:7">
       <c r="C755" s="15"/>
       <c r="D755" s="5"/>
       <c r="E755" s="15"/>
       <c r="F755" s="5"/>
       <c r="G755" s="14"/>
     </row>
-    <row r="756" spans="3:7" hidden="1">
+    <row r="756" spans="3:7">
       <c r="C756" s="15"/>
       <c r="D756" s="5"/>
       <c r="E756" s="15"/>
       <c r="F756" s="5"/>
       <c r="G756" s="14"/>
     </row>
-    <row r="757" spans="3:7" hidden="1">
+    <row r="757" spans="3:7">
       <c r="C757" s="15"/>
       <c r="D757" s="5"/>
       <c r="E757" s="15"/>
       <c r="F757" s="5"/>
       <c r="G757" s="14"/>
     </row>
-    <row r="758" spans="3:7" hidden="1">
+    <row r="758" spans="3:7">
       <c r="C758" s="15"/>
       <c r="D758" s="5"/>
       <c r="E758" s="15"/>
       <c r="F758" s="5"/>
       <c r="G758" s="14"/>
     </row>
-    <row r="759" spans="3:7" hidden="1">
+    <row r="759" spans="3:7">
       <c r="C759" s="15"/>
       <c r="D759" s="5"/>
       <c r="E759" s="15"/>
       <c r="F759" s="5"/>
       <c r="G759" s="14"/>
     </row>
-    <row r="760" spans="3:7" hidden="1">
+    <row r="760" spans="3:7">
       <c r="C760" s="15"/>
       <c r="D760" s="5"/>
       <c r="E760" s="15"/>
       <c r="F760" s="5"/>
       <c r="G760" s="14"/>
     </row>
-    <row r="761" spans="3:7" hidden="1">
+    <row r="761" spans="3:7">
       <c r="C761" s="15"/>
       <c r="D761" s="5"/>
       <c r="E761" s="15"/>
       <c r="F761" s="5"/>
       <c r="G761" s="14"/>
     </row>
-    <row r="762" spans="3:7" hidden="1">
+    <row r="762" spans="3:7">
       <c r="C762" s="5"/>
       <c r="D762" s="5"/>
       <c r="E762" s="15"/>
       <c r="F762" s="5"/>
       <c r="G762" s="3"/>
     </row>
-    <row r="763" spans="3:7" hidden="1">
+    <row r="763" spans="3:7">
       <c r="C763" s="5"/>
       <c r="D763" s="5"/>
       <c r="E763" s="15"/>
       <c r="F763" s="5"/>
       <c r="G763" s="3"/>
     </row>
-    <row r="764" spans="3:7" hidden="1">
+    <row r="764" spans="3:7">
       <c r="C764" s="5"/>
       <c r="D764" s="5"/>
       <c r="E764" s="15"/>
       <c r="F764" s="5"/>
       <c r="G764" s="3"/>
     </row>
-    <row r="765" spans="3:7" hidden="1">
+    <row r="765" spans="3:7">
       <c r="C765" s="5"/>
       <c r="D765" s="5"/>
       <c r="E765" s="15"/>
       <c r="F765" s="5"/>
       <c r="G765" s="3"/>
     </row>
-    <row r="766" spans="3:7" hidden="1">
+    <row r="766" spans="3:7">
       <c r="C766" s="5"/>
       <c r="D766" s="5"/>
       <c r="E766" s="15"/>
       <c r="F766" s="5"/>
       <c r="G766" s="3"/>
     </row>
-    <row r="767" spans="3:7" hidden="1">
+    <row r="767" spans="3:7">
       <c r="C767" s="5"/>
       <c r="D767" s="5"/>
       <c r="E767" s="15"/>
       <c r="F767" s="5"/>
       <c r="G767" s="3"/>
     </row>
-    <row r="768" spans="3:7" hidden="1">
+    <row r="768" spans="3:7">
       <c r="C768" s="5"/>
       <c r="D768" s="5"/>
       <c r="E768" s="15"/>
       <c r="F768" s="5"/>
       <c r="G768" s="3"/>
     </row>
-    <row r="769" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="769" spans="1:7" ht="30" customHeight="1">
       <c r="C769" s="5"/>
       <c r="D769" s="5"/>
       <c r="E769" s="12"/>
       <c r="F769" s="5"/>
       <c r="G769" s="14"/>
     </row>
-    <row r="770" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="770" spans="1:7" ht="30" customHeight="1">
       <c r="C770" s="5"/>
       <c r="D770" s="5"/>
       <c r="E770" s="15"/>
       <c r="F770" s="5"/>
       <c r="G770" s="14"/>
     </row>
-    <row r="771" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="771" spans="1:7" ht="30" customHeight="1">
       <c r="C771" s="5"/>
       <c r="D771" s="5"/>
       <c r="E771" s="15"/>
       <c r="F771" s="5"/>
       <c r="G771" s="14"/>
     </row>
-    <row r="772" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="772" spans="1:7" ht="30" customHeight="1">
       <c r="C772" s="5"/>
       <c r="D772" s="5"/>
       <c r="E772" s="12"/>
       <c r="F772" s="5"/>
       <c r="G772" s="14"/>
     </row>
-    <row r="773" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="773" spans="1:7" ht="30" customHeight="1">
       <c r="A773" s="13"/>
       <c r="B773" s="13"/>
       <c r="C773" s="15"/>
       <c r="G773" s="14"/>
     </row>
-    <row r="774" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="774" spans="1:7" ht="30" customHeight="1">
       <c r="A774" s="13"/>
       <c r="B774" s="13"/>
       <c r="C774" s="15"/>
       <c r="G774" s="14"/>
     </row>
-    <row r="775" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="775" spans="1:7" ht="30" customHeight="1">
       <c r="C775" s="5"/>
       <c r="D775" s="5"/>
       <c r="E775" s="15"/>
       <c r="F775" s="5"/>
       <c r="G775" s="14"/>
     </row>
-    <row r="776" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="776" spans="1:7" ht="30" customHeight="1">
       <c r="A776" s="13"/>
       <c r="B776" s="13"/>
       <c r="C776" s="15"/>
@@ -11684,7 +11683,7 @@
       <c r="F776" s="5"/>
       <c r="G776" s="14"/>
     </row>
-    <row r="777" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="777" spans="1:7" ht="30" customHeight="1">
       <c r="B777" s="13"/>
       <c r="C777" s="15"/>
       <c r="D777" s="5"/>
@@ -11692,7 +11691,7 @@
       <c r="F777" s="5"/>
       <c r="G777" s="14"/>
     </row>
-    <row r="778" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="778" spans="1:7" ht="30" customHeight="1">
       <c r="B778" s="13"/>
       <c r="C778" s="15"/>
       <c r="D778" s="5"/>
@@ -11700,7 +11699,7 @@
       <c r="F778" s="5"/>
       <c r="G778" s="14"/>
     </row>
-    <row r="779" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="779" spans="1:7" ht="30" customHeight="1">
       <c r="B779" s="13"/>
       <c r="C779" s="15"/>
       <c r="D779" s="5"/>
@@ -11708,7 +11707,7 @@
       <c r="F779" s="5"/>
       <c r="G779" s="14"/>
     </row>
-    <row r="780" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="780" spans="1:7" ht="30" customHeight="1">
       <c r="B780" s="13"/>
       <c r="C780" s="15"/>
       <c r="D780" s="5"/>
@@ -11716,7 +11715,7 @@
       <c r="F780" s="5"/>
       <c r="G780" s="14"/>
     </row>
-    <row r="781" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="781" spans="1:7" ht="30" customHeight="1">
       <c r="B781" s="13"/>
       <c r="C781" s="15"/>
       <c r="D781" s="5"/>
@@ -11724,7 +11723,7 @@
       <c r="F781" s="5"/>
       <c r="G781" s="14"/>
     </row>
-    <row r="782" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="782" spans="1:7" ht="30" customHeight="1">
       <c r="B782" s="13"/>
       <c r="C782" s="15"/>
       <c r="D782" s="5"/>
@@ -11732,21 +11731,21 @@
       <c r="F782" s="5"/>
       <c r="G782" s="14"/>
     </row>
-    <row r="783" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="783" spans="1:7" ht="30" customHeight="1">
       <c r="C783" s="5"/>
       <c r="D783" s="5"/>
       <c r="E783" s="15"/>
       <c r="F783" s="5"/>
       <c r="G783" s="14"/>
     </row>
-    <row r="784" spans="1:7" hidden="1">
+    <row r="784" spans="1:7">
       <c r="C784" s="5"/>
       <c r="D784" s="5"/>
       <c r="E784" s="15"/>
       <c r="F784" s="5"/>
       <c r="G784" s="3"/>
     </row>
-    <row r="785" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="785" spans="1:7" ht="30" customHeight="1">
       <c r="A785" s="13"/>
       <c r="C785" s="5"/>
       <c r="D785" s="5"/>
@@ -11754,42 +11753,42 @@
       <c r="F785" s="5"/>
       <c r="G785" s="14"/>
     </row>
-    <row r="786" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="786" spans="1:7" ht="30" customHeight="1">
       <c r="B786" s="13"/>
       <c r="C786" s="15"/>
       <c r="D786" s="13"/>
       <c r="F786" s="13"/>
       <c r="G786" s="14"/>
     </row>
-    <row r="787" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="787" spans="1:7" ht="30" customHeight="1">
       <c r="B787" s="13"/>
       <c r="C787" s="15"/>
       <c r="D787" s="13"/>
       <c r="F787" s="13"/>
       <c r="G787" s="14"/>
     </row>
-    <row r="788" spans="1:7" hidden="1">
+    <row r="788" spans="1:7">
       <c r="B788" s="13"/>
       <c r="C788" s="15"/>
       <c r="D788" s="13"/>
       <c r="F788" s="13"/>
       <c r="G788" s="14"/>
     </row>
-    <row r="789" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="789" spans="1:7" ht="30" customHeight="1">
       <c r="B789" s="13"/>
       <c r="C789" s="15"/>
       <c r="D789" s="13"/>
       <c r="F789" s="13"/>
       <c r="G789" s="14"/>
     </row>
-    <row r="790" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="790" spans="1:7" ht="30" customHeight="1">
       <c r="B790" s="13"/>
       <c r="C790" s="15"/>
       <c r="D790" s="13"/>
       <c r="F790" s="13"/>
       <c r="G790" s="14"/>
     </row>
-    <row r="791" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="791" spans="1:7" ht="30" customHeight="1">
       <c r="A791" s="13"/>
       <c r="B791" s="13"/>
       <c r="C791" s="15"/>
@@ -11797,419 +11796,419 @@
       <c r="F791" s="13"/>
       <c r="G791" s="14"/>
     </row>
-    <row r="792" spans="1:7" hidden="1">
+    <row r="792" spans="1:7">
       <c r="B792" s="13"/>
       <c r="C792" s="15"/>
       <c r="D792" s="13"/>
       <c r="F792" s="13"/>
       <c r="G792" s="14"/>
     </row>
-    <row r="793" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="793" spans="1:7" ht="30" customHeight="1">
       <c r="B793" s="13"/>
       <c r="C793" s="15"/>
       <c r="D793" s="13"/>
       <c r="F793" s="13"/>
       <c r="G793" s="14"/>
     </row>
-    <row r="794" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="794" spans="1:7" ht="30" customHeight="1">
       <c r="B794" s="13"/>
       <c r="C794" s="15"/>
       <c r="G794" s="14"/>
     </row>
-    <row r="795" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="795" spans="1:7" ht="30" customHeight="1">
       <c r="B795" s="13"/>
       <c r="C795" s="15"/>
       <c r="G795" s="14"/>
     </row>
-    <row r="796" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="796" spans="1:7" ht="30" customHeight="1">
       <c r="B796" s="13"/>
       <c r="C796" s="15"/>
       <c r="G796" s="14"/>
     </row>
-    <row r="797" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="797" spans="1:7" ht="30" customHeight="1">
       <c r="A797" s="13"/>
       <c r="B797" s="13"/>
       <c r="C797" s="15"/>
       <c r="G797" s="14"/>
     </row>
-    <row r="798" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="798" spans="1:7" ht="30" customHeight="1">
       <c r="B798" s="13"/>
       <c r="C798" s="15"/>
       <c r="G798" s="14"/>
     </row>
-    <row r="799" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="799" spans="1:7" ht="30" customHeight="1">
       <c r="B799" s="13"/>
       <c r="C799" s="15"/>
       <c r="G799" s="14"/>
     </row>
-    <row r="800" spans="1:7" hidden="1">
+    <row r="800" spans="1:7">
       <c r="B800" s="13"/>
       <c r="C800" s="15"/>
       <c r="G800" s="14"/>
     </row>
-    <row r="801" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="801" spans="2:7" ht="30" customHeight="1">
       <c r="B801" s="13"/>
       <c r="C801" s="15"/>
       <c r="G801" s="14"/>
     </row>
-    <row r="802" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="802" spans="2:7" ht="30" customHeight="1">
       <c r="B802" s="13"/>
       <c r="C802" s="15"/>
       <c r="G802" s="14"/>
     </row>
-    <row r="803" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="803" spans="2:7" ht="30" customHeight="1">
       <c r="B803" s="13"/>
       <c r="C803" s="15"/>
       <c r="G803" s="14"/>
     </row>
-    <row r="804" spans="2:7" hidden="1">
+    <row r="804" spans="2:7">
       <c r="B804" s="13"/>
       <c r="C804" s="15"/>
       <c r="G804" s="14"/>
     </row>
-    <row r="805" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="805" spans="2:7" ht="30" customHeight="1">
       <c r="B805" s="13"/>
       <c r="C805" s="15"/>
       <c r="G805" s="14"/>
     </row>
-    <row r="806" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="806" spans="2:7" ht="30" customHeight="1">
       <c r="B806" s="13"/>
       <c r="C806" s="15"/>
       <c r="G806" s="14"/>
     </row>
-    <row r="807" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="807" spans="2:7" ht="30" customHeight="1">
       <c r="B807" s="13"/>
       <c r="C807" s="15"/>
       <c r="G807" s="14"/>
     </row>
-    <row r="808" spans="2:7" hidden="1">
+    <row r="808" spans="2:7">
       <c r="B808" s="13"/>
       <c r="C808" s="15"/>
       <c r="G808" s="14"/>
     </row>
-    <row r="809" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="809" spans="2:7" ht="30" customHeight="1">
       <c r="B809" s="13"/>
       <c r="C809" s="15"/>
       <c r="G809" s="14"/>
     </row>
-    <row r="810" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="810" spans="2:7" ht="30" customHeight="1">
       <c r="B810" s="13"/>
       <c r="C810" s="15"/>
       <c r="G810" s="14"/>
     </row>
-    <row r="811" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="811" spans="2:7" ht="30" customHeight="1">
       <c r="B811" s="13"/>
       <c r="C811" s="15"/>
       <c r="G811" s="14"/>
     </row>
-    <row r="812" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="812" spans="2:7" ht="30" customHeight="1">
       <c r="B812" s="13"/>
       <c r="C812" s="15"/>
       <c r="G812" s="14"/>
     </row>
-    <row r="813" spans="2:7" hidden="1">
+    <row r="813" spans="2:7">
       <c r="B813" s="13"/>
       <c r="C813" s="15"/>
       <c r="G813" s="14"/>
     </row>
-    <row r="814" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="814" spans="2:7" ht="30" customHeight="1">
       <c r="B814" s="13"/>
       <c r="C814" s="15"/>
       <c r="G814" s="14"/>
     </row>
-    <row r="815" spans="2:7" hidden="1">
+    <row r="815" spans="2:7">
       <c r="B815" s="13"/>
       <c r="C815" s="15"/>
       <c r="G815" s="14"/>
     </row>
-    <row r="816" spans="2:7" hidden="1">
+    <row r="816" spans="2:7">
       <c r="B816" s="13"/>
       <c r="C816" s="15"/>
       <c r="G816" s="14"/>
     </row>
-    <row r="817" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="817" spans="2:7" ht="30" customHeight="1">
       <c r="B817" s="13"/>
       <c r="C817" s="15"/>
       <c r="G817" s="14"/>
     </row>
-    <row r="818" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="818" spans="2:7" ht="30" customHeight="1">
       <c r="B818" s="13"/>
       <c r="C818" s="15"/>
       <c r="E818" s="14"/>
       <c r="G818" s="14"/>
     </row>
-    <row r="819" spans="2:7" hidden="1">
+    <row r="819" spans="2:7">
       <c r="B819" s="13"/>
       <c r="C819" s="15"/>
       <c r="G819" s="14"/>
     </row>
-    <row r="820" spans="2:7" hidden="1">
+    <row r="820" spans="2:7">
       <c r="B820" s="13"/>
       <c r="C820" s="15"/>
       <c r="G820" s="14"/>
     </row>
-    <row r="821" spans="2:7" hidden="1">
+    <row r="821" spans="2:7">
       <c r="B821" s="13"/>
       <c r="C821" s="15"/>
       <c r="G821" s="14"/>
     </row>
-    <row r="822" spans="2:7" hidden="1">
+    <row r="822" spans="2:7">
       <c r="B822" s="13"/>
       <c r="C822" s="15"/>
       <c r="G822" s="14"/>
     </row>
-    <row r="823" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="823" spans="2:7" ht="30" customHeight="1">
       <c r="B823" s="13"/>
       <c r="C823" s="15"/>
       <c r="G823" s="14"/>
     </row>
-    <row r="824" spans="2:7" hidden="1">
+    <row r="824" spans="2:7">
       <c r="B824" s="13"/>
       <c r="C824" s="15"/>
       <c r="G824" s="14"/>
     </row>
-    <row r="825" spans="2:7" hidden="1">
+    <row r="825" spans="2:7">
       <c r="B825" s="13"/>
       <c r="C825" s="15"/>
       <c r="G825" s="14"/>
     </row>
-    <row r="826" spans="2:7" hidden="1">
+    <row r="826" spans="2:7">
       <c r="B826" s="13"/>
       <c r="C826" s="15"/>
       <c r="G826" s="14"/>
     </row>
-    <row r="827" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="827" spans="2:7" ht="30" customHeight="1">
       <c r="B827" s="13"/>
       <c r="C827" s="15"/>
       <c r="G827" s="14"/>
     </row>
-    <row r="828" spans="2:7" hidden="1">
+    <row r="828" spans="2:7">
       <c r="B828" s="13"/>
       <c r="C828" s="15"/>
       <c r="G828" s="14"/>
     </row>
-    <row r="829" spans="2:7" hidden="1">
+    <row r="829" spans="2:7">
       <c r="B829" s="13"/>
       <c r="C829" s="15"/>
       <c r="G829" s="14"/>
     </row>
-    <row r="830" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="830" spans="2:7" ht="30" customHeight="1">
       <c r="B830" s="13"/>
       <c r="C830" s="15"/>
       <c r="G830" s="14"/>
     </row>
-    <row r="831" spans="2:7" hidden="1">
+    <row r="831" spans="2:7">
       <c r="B831" s="13"/>
       <c r="C831" s="15"/>
       <c r="G831" s="14"/>
     </row>
-    <row r="832" spans="2:7" hidden="1">
+    <row r="832" spans="2:7">
       <c r="B832" s="13"/>
       <c r="C832" s="15"/>
       <c r="G832" s="14"/>
     </row>
-    <row r="833" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="833" spans="2:7" ht="30" customHeight="1">
       <c r="B833" s="13"/>
       <c r="C833" s="15"/>
       <c r="G833" s="14"/>
     </row>
-    <row r="834" spans="2:7" hidden="1">
+    <row r="834" spans="2:7">
       <c r="B834" s="13"/>
       <c r="C834" s="15"/>
       <c r="G834" s="14"/>
     </row>
-    <row r="835" spans="2:7" hidden="1">
+    <row r="835" spans="2:7">
       <c r="B835" s="13"/>
       <c r="C835" s="15"/>
       <c r="G835" s="14"/>
     </row>
-    <row r="836" spans="2:7" hidden="1">
+    <row r="836" spans="2:7">
       <c r="B836" s="13"/>
       <c r="C836" s="15"/>
       <c r="G836" s="14"/>
     </row>
-    <row r="837" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="837" spans="2:7" ht="30" customHeight="1">
       <c r="B837" s="13"/>
       <c r="C837" s="15"/>
       <c r="G837" s="14"/>
     </row>
-    <row r="838" spans="2:7" hidden="1">
+    <row r="838" spans="2:7">
       <c r="B838" s="13"/>
       <c r="C838" s="15"/>
       <c r="G838" s="14"/>
     </row>
-    <row r="839" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="839" spans="2:7" ht="30" customHeight="1">
       <c r="B839" s="13"/>
       <c r="C839" s="15"/>
       <c r="G839" s="14"/>
     </row>
-    <row r="840" spans="2:7" hidden="1">
+    <row r="840" spans="2:7">
       <c r="B840" s="13"/>
       <c r="C840" s="15"/>
       <c r="G840" s="14"/>
     </row>
-    <row r="841" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="841" spans="2:7" ht="30" customHeight="1">
       <c r="B841" s="13"/>
       <c r="C841" s="15"/>
       <c r="G841" s="14"/>
     </row>
-    <row r="842" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="842" spans="2:7" ht="30" customHeight="1">
       <c r="B842" s="13"/>
       <c r="C842" s="15"/>
       <c r="G842" s="14"/>
     </row>
-    <row r="843" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="843" spans="2:7" ht="30" customHeight="1">
       <c r="B843" s="13"/>
       <c r="C843" s="15"/>
       <c r="G843" s="14"/>
     </row>
-    <row r="844" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="844" spans="2:7" ht="30" customHeight="1">
       <c r="B844" s="13"/>
       <c r="C844" s="15"/>
       <c r="G844" s="14"/>
     </row>
-    <row r="845" spans="2:7" hidden="1">
+    <row r="845" spans="2:7">
       <c r="B845" s="13"/>
       <c r="C845" s="15"/>
       <c r="G845" s="14"/>
     </row>
-    <row r="846" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="846" spans="2:7" ht="30" customHeight="1">
       <c r="B846" s="13"/>
       <c r="C846" s="15"/>
       <c r="G846" s="14"/>
     </row>
-    <row r="847" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="847" spans="2:7" ht="30" customHeight="1">
       <c r="B847" s="13"/>
       <c r="C847" s="15"/>
       <c r="E847" s="14"/>
       <c r="G847" s="14"/>
     </row>
-    <row r="848" spans="2:7" hidden="1">
+    <row r="848" spans="2:7">
       <c r="B848" s="13"/>
       <c r="C848" s="15"/>
       <c r="G848" s="14"/>
     </row>
-    <row r="849" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="849" spans="2:7" ht="30" customHeight="1">
       <c r="B849" s="13"/>
       <c r="C849" s="15"/>
       <c r="E849" s="14"/>
       <c r="G849" s="14"/>
     </row>
-    <row r="850" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="850" spans="2:7" ht="30" customHeight="1">
       <c r="B850" s="13"/>
       <c r="C850" s="15"/>
       <c r="E850" s="14"/>
       <c r="G850" s="14"/>
     </row>
-    <row r="851" spans="2:7" hidden="1">
+    <row r="851" spans="2:7">
       <c r="B851" s="13"/>
       <c r="C851" s="15"/>
       <c r="G851" s="14"/>
     </row>
-    <row r="852" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="852" spans="2:7" ht="30" customHeight="1">
       <c r="C852" s="5"/>
       <c r="D852" s="5"/>
       <c r="E852" s="12"/>
       <c r="F852" s="5"/>
       <c r="G852" s="14"/>
     </row>
-    <row r="853" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="853" spans="2:7" ht="30" customHeight="1">
       <c r="C853" s="5"/>
       <c r="G853" s="14"/>
     </row>
-    <row r="854" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="854" spans="2:7" ht="30" customHeight="1">
       <c r="B854" s="13"/>
       <c r="C854" s="5"/>
       <c r="G854" s="14"/>
     </row>
-    <row r="855" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="855" spans="2:7" ht="30" customHeight="1">
       <c r="B855" s="13"/>
       <c r="C855" s="15"/>
       <c r="G855" s="14"/>
     </row>
-    <row r="856" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="856" spans="2:7" ht="30" customHeight="1">
       <c r="C856" s="5"/>
       <c r="D856" s="5"/>
       <c r="E856" s="12"/>
       <c r="F856" s="5"/>
       <c r="G856" s="14"/>
     </row>
-    <row r="857" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="857" spans="2:7" ht="30" customHeight="1">
       <c r="C857" s="5"/>
       <c r="D857" s="5"/>
       <c r="E857" s="15"/>
       <c r="F857" s="5"/>
       <c r="G857" s="14"/>
     </row>
-    <row r="858" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="858" spans="2:7" ht="30" customHeight="1">
       <c r="C858" s="5"/>
       <c r="D858" s="5"/>
       <c r="E858" s="15"/>
       <c r="F858" s="5"/>
       <c r="G858" s="14"/>
     </row>
-    <row r="859" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="859" spans="2:7" ht="30" customHeight="1">
       <c r="C859" s="5"/>
       <c r="G859" s="14"/>
     </row>
-    <row r="860" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="860" spans="2:7" ht="30" customHeight="1">
       <c r="B860" s="13"/>
       <c r="C860" s="5"/>
       <c r="G860" s="14"/>
     </row>
-    <row r="861" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="861" spans="2:7" ht="30" customHeight="1">
       <c r="C861" s="5"/>
       <c r="D861" s="5"/>
       <c r="E861" s="15"/>
       <c r="F861" s="5"/>
       <c r="G861" s="14"/>
     </row>
-    <row r="862" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="862" spans="2:7" ht="30" customHeight="1">
       <c r="C862" s="5"/>
       <c r="G862" s="14"/>
     </row>
-    <row r="863" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="863" spans="2:7" ht="30" customHeight="1">
       <c r="C863" s="5"/>
       <c r="G863" s="14"/>
     </row>
-    <row r="864" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="864" spans="2:7" ht="30" customHeight="1">
       <c r="C864" s="5"/>
       <c r="E864" s="14"/>
       <c r="G864" s="14"/>
     </row>
-    <row r="865" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="865" spans="1:7" ht="30" customHeight="1">
       <c r="C865" s="5"/>
       <c r="D865" s="5"/>
       <c r="E865" s="15"/>
       <c r="F865" s="5"/>
       <c r="G865" s="14"/>
     </row>
-    <row r="866" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="866" spans="1:7" ht="30" customHeight="1">
       <c r="B866" s="13"/>
       <c r="C866" s="5"/>
       <c r="G866" s="14"/>
     </row>
-    <row r="867" spans="1:7" hidden="1">
+    <row r="867" spans="1:7">
       <c r="C867" s="5"/>
       <c r="G867" s="14"/>
     </row>
-    <row r="868" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="868" spans="1:7" ht="30" customHeight="1">
       <c r="B868" s="13"/>
       <c r="C868" s="5"/>
       <c r="G868" s="14"/>
     </row>
-    <row r="869" spans="1:7" hidden="1">
+    <row r="869" spans="1:7">
       <c r="C869" s="5"/>
       <c r="G869" s="3"/>
     </row>
-    <row r="870" spans="1:7" hidden="1">
+    <row r="870" spans="1:7">
       <c r="B870" s="13"/>
       <c r="C870" s="15"/>
       <c r="D870" s="13"/>
       <c r="F870" s="13"/>
       <c r="G870" s="14"/>
     </row>
-    <row r="871" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="871" spans="1:7" ht="30" customHeight="1">
       <c r="A871" s="13"/>
       <c r="C871" s="5"/>
       <c r="D871" s="5"/>
@@ -12217,49 +12216,49 @@
       <c r="F871" s="5"/>
       <c r="G871" s="14"/>
     </row>
-    <row r="872" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="872" spans="1:7" ht="30" customHeight="1">
       <c r="B872" s="13"/>
       <c r="C872" s="5"/>
       <c r="G872" s="14"/>
     </row>
-    <row r="873" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="873" spans="1:7" ht="30" customHeight="1">
       <c r="C873" s="5"/>
       <c r="G873" s="14"/>
     </row>
-    <row r="874" spans="1:7" hidden="1">
+    <row r="874" spans="1:7">
       <c r="C874" s="5"/>
       <c r="D874" s="5"/>
       <c r="E874" s="15"/>
       <c r="F874" s="5"/>
       <c r="G874" s="14"/>
     </row>
-    <row r="875" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="875" spans="1:7" ht="30" customHeight="1">
       <c r="B875" s="13"/>
       <c r="C875" s="15"/>
       <c r="G875" s="14"/>
     </row>
-    <row r="876" spans="1:7" hidden="1">
+    <row r="876" spans="1:7">
       <c r="B876" s="13"/>
       <c r="C876" s="15"/>
       <c r="D876" s="13"/>
       <c r="F876" s="13"/>
       <c r="G876" s="14"/>
     </row>
-    <row r="877" spans="1:7" hidden="1">
+    <row r="877" spans="1:7">
       <c r="B877" s="13"/>
       <c r="C877" s="15"/>
       <c r="D877" s="13"/>
       <c r="F877" s="13"/>
       <c r="G877" s="14"/>
     </row>
-    <row r="878" spans="1:7" hidden="1">
+    <row r="878" spans="1:7">
       <c r="B878" s="13"/>
       <c r="C878" s="15"/>
       <c r="D878" s="13"/>
       <c r="F878" s="13"/>
       <c r="G878" s="14"/>
     </row>
-    <row r="879" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="879" spans="1:7" ht="30" customHeight="1">
       <c r="B879" s="13"/>
       <c r="C879" s="15"/>
       <c r="D879" s="13"/>
@@ -12267,111 +12266,111 @@
       <c r="F879" s="13"/>
       <c r="G879" s="14"/>
     </row>
-    <row r="880" spans="1:7" hidden="1">
+    <row r="880" spans="1:7">
       <c r="B880" s="13"/>
       <c r="C880" s="15"/>
       <c r="D880" s="13"/>
       <c r="F880" s="13"/>
       <c r="G880" s="14"/>
     </row>
-    <row r="881" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="881" spans="1:7" ht="30" customHeight="1">
       <c r="C881" s="5"/>
       <c r="E881" s="14"/>
       <c r="G881" s="14"/>
     </row>
-    <row r="882" spans="1:7" hidden="1">
+    <row r="882" spans="1:7">
       <c r="C882" s="5"/>
       <c r="G882" s="3"/>
     </row>
-    <row r="883" spans="1:7" hidden="1">
+    <row r="883" spans="1:7">
       <c r="B883" s="13"/>
       <c r="C883" s="15"/>
       <c r="G883" s="14"/>
     </row>
-    <row r="884" spans="1:7" hidden="1">
+    <row r="884" spans="1:7">
       <c r="B884" s="13"/>
       <c r="C884" s="15"/>
       <c r="G884" s="14"/>
     </row>
-    <row r="885" spans="1:7" hidden="1">
+    <row r="885" spans="1:7">
       <c r="B885" s="13"/>
       <c r="C885" s="15"/>
       <c r="G885" s="14"/>
     </row>
-    <row r="886" spans="1:7" hidden="1">
+    <row r="886" spans="1:7">
       <c r="B886" s="13"/>
       <c r="C886" s="15"/>
       <c r="G886" s="14"/>
     </row>
-    <row r="887" spans="1:7" hidden="1">
+    <row r="887" spans="1:7">
       <c r="B887" s="13"/>
       <c r="C887" s="15"/>
       <c r="G887" s="14"/>
     </row>
-    <row r="888" spans="1:7" hidden="1">
+    <row r="888" spans="1:7">
       <c r="B888" s="13"/>
       <c r="C888" s="15"/>
       <c r="G888" s="14"/>
     </row>
-    <row r="889" spans="1:7" hidden="1">
+    <row r="889" spans="1:7">
       <c r="B889" s="13"/>
       <c r="C889" s="15"/>
       <c r="G889" s="14"/>
     </row>
-    <row r="890" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="890" spans="1:7" ht="30" customHeight="1">
       <c r="B890" s="13"/>
       <c r="C890" s="15"/>
       <c r="D890" s="13"/>
       <c r="F890" s="13"/>
       <c r="G890" s="14"/>
     </row>
-    <row r="891" spans="1:7" hidden="1">
+    <row r="891" spans="1:7">
       <c r="A891" s="13"/>
       <c r="B891" s="13"/>
       <c r="C891" s="15"/>
       <c r="G891" s="14"/>
     </row>
-    <row r="892" spans="1:7" hidden="1">
+    <row r="892" spans="1:7">
       <c r="B892" s="13"/>
       <c r="C892" s="15"/>
       <c r="G892" s="14"/>
     </row>
-    <row r="893" spans="1:7" hidden="1">
+    <row r="893" spans="1:7">
       <c r="B893" s="13"/>
       <c r="C893" s="15"/>
       <c r="G893" s="14"/>
     </row>
-    <row r="894" spans="1:7" hidden="1">
+    <row r="894" spans="1:7">
       <c r="B894" s="13"/>
       <c r="C894" s="15"/>
       <c r="G894" s="14"/>
     </row>
-    <row r="895" spans="1:7" hidden="1">
+    <row r="895" spans="1:7">
       <c r="B895" s="13"/>
       <c r="C895" s="15"/>
       <c r="G895" s="14"/>
     </row>
-    <row r="896" spans="1:7" hidden="1">
+    <row r="896" spans="1:7">
       <c r="B896" s="13"/>
       <c r="C896" s="15"/>
       <c r="G896" s="14"/>
     </row>
-    <row r="897" spans="2:7" hidden="1">
+    <row r="897" spans="2:7">
       <c r="B897" s="13"/>
       <c r="C897" s="15"/>
       <c r="G897" s="14"/>
     </row>
-    <row r="898" spans="2:7" hidden="1">
+    <row r="898" spans="2:7">
       <c r="B898" s="13"/>
       <c r="C898" s="15"/>
       <c r="G898" s="14"/>
     </row>
-    <row r="899" spans="2:7" hidden="1">
+    <row r="899" spans="2:7">
       <c r="B899" s="13"/>
       <c r="C899" s="15"/>
       <c r="G899" s="14"/>
     </row>
-    <row r="900" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="900" spans="2:7" ht="30" customHeight="1">
       <c r="B900" s="13"/>
       <c r="C900" s="15"/>
       <c r="D900" s="13"/>
@@ -12379,21 +12378,21 @@
       <c r="F900" s="13"/>
       <c r="G900" s="14"/>
     </row>
-    <row r="901" spans="2:7" hidden="1">
+    <row r="901" spans="2:7">
       <c r="B901" s="13"/>
       <c r="C901" s="15"/>
       <c r="D901" s="13"/>
       <c r="F901" s="13"/>
       <c r="G901" s="14"/>
     </row>
-    <row r="902" spans="2:7" hidden="1">
+    <row r="902" spans="2:7">
       <c r="B902" s="13"/>
       <c r="C902" s="15"/>
       <c r="D902" s="13"/>
       <c r="F902" s="13"/>
       <c r="G902" s="14"/>
     </row>
-    <row r="903" spans="2:7" ht="30" hidden="1" customHeight="1">
+    <row r="903" spans="2:7" ht="30" customHeight="1">
       <c r="B903" s="13"/>
       <c r="C903" s="15"/>
       <c r="D903" s="13"/>
@@ -12401,148 +12400,142 @@
       <c r="F903" s="13"/>
       <c r="G903" s="14"/>
     </row>
-    <row r="904" spans="2:7" hidden="1">
+    <row r="904" spans="2:7">
       <c r="B904" s="13"/>
       <c r="C904" s="15"/>
       <c r="G904" s="14"/>
     </row>
-    <row r="905" spans="2:7" hidden="1">
+    <row r="905" spans="2:7">
       <c r="B905" s="13"/>
       <c r="C905" s="15"/>
       <c r="G905" s="14"/>
     </row>
-    <row r="906" spans="2:7" hidden="1">
+    <row r="906" spans="2:7">
       <c r="B906" s="13"/>
       <c r="C906" s="15"/>
       <c r="G906" s="14"/>
     </row>
-    <row r="907" spans="2:7" hidden="1">
+    <row r="907" spans="2:7">
       <c r="B907" s="13"/>
       <c r="C907" s="15"/>
       <c r="G907" s="14"/>
     </row>
-    <row r="908" spans="2:7" hidden="1">
+    <row r="908" spans="2:7">
       <c r="B908" s="13"/>
       <c r="C908" s="15"/>
       <c r="G908" s="14"/>
     </row>
-    <row r="909" spans="2:7" hidden="1">
+    <row r="909" spans="2:7">
       <c r="B909" s="13"/>
       <c r="C909" s="15"/>
       <c r="G909" s="14"/>
     </row>
-    <row r="910" spans="2:7" hidden="1">
+    <row r="910" spans="2:7">
       <c r="B910" s="13"/>
       <c r="C910" s="15"/>
       <c r="G910" s="14"/>
     </row>
-    <row r="911" spans="2:7" hidden="1">
+    <row r="911" spans="2:7">
       <c r="B911" s="13"/>
       <c r="C911" s="15"/>
       <c r="G911" s="14"/>
     </row>
-    <row r="912" spans="2:7" hidden="1">
+    <row r="912" spans="2:7">
       <c r="B912" s="13"/>
       <c r="C912" s="15"/>
       <c r="G912" s="14"/>
     </row>
-    <row r="913" spans="1:7" hidden="1">
+    <row r="913" spans="1:7">
       <c r="B913" s="13"/>
       <c r="C913" s="15"/>
       <c r="G913" s="14"/>
     </row>
-    <row r="914" spans="1:7" hidden="1">
+    <row r="914" spans="1:7">
       <c r="B914" s="13"/>
       <c r="C914" s="15"/>
       <c r="G914" s="14"/>
     </row>
-    <row r="915" spans="1:7" hidden="1">
+    <row r="915" spans="1:7">
       <c r="B915" s="13"/>
       <c r="C915" s="15"/>
       <c r="G915" s="14"/>
     </row>
-    <row r="916" spans="1:7" hidden="1">
+    <row r="916" spans="1:7">
       <c r="B916" s="13"/>
       <c r="C916" s="15"/>
       <c r="G916" s="14"/>
     </row>
-    <row r="917" spans="1:7" hidden="1">
+    <row r="917" spans="1:7">
       <c r="B917" s="13"/>
       <c r="C917" s="15"/>
       <c r="G917" s="14"/>
     </row>
-    <row r="918" spans="1:7" hidden="1">
+    <row r="918" spans="1:7">
       <c r="B918" s="13"/>
       <c r="C918" s="15"/>
       <c r="G918" s="14"/>
     </row>
-    <row r="919" spans="1:7" hidden="1">
+    <row r="919" spans="1:7">
       <c r="B919" s="13"/>
       <c r="C919" s="15"/>
       <c r="G919" s="14"/>
     </row>
-    <row r="920" spans="1:7" hidden="1">
+    <row r="920" spans="1:7">
       <c r="B920" s="13"/>
       <c r="C920" s="15"/>
       <c r="G920" s="14"/>
     </row>
-    <row r="921" spans="1:7" hidden="1">
+    <row r="921" spans="1:7">
       <c r="B921" s="13"/>
       <c r="C921" s="15"/>
       <c r="G921" s="14"/>
     </row>
-    <row r="922" spans="1:7" hidden="1">
+    <row r="922" spans="1:7">
       <c r="B922" s="13"/>
       <c r="C922" s="15"/>
       <c r="G922" s="14"/>
     </row>
-    <row r="923" spans="1:7" hidden="1">
+    <row r="923" spans="1:7">
       <c r="B923" s="13"/>
       <c r="C923" s="15"/>
       <c r="G923" s="14"/>
     </row>
-    <row r="924" spans="1:7" hidden="1">
+    <row r="924" spans="1:7">
       <c r="B924" s="13"/>
       <c r="C924" s="15"/>
       <c r="G924" s="14"/>
     </row>
-    <row r="925" spans="1:7" hidden="1">
+    <row r="925" spans="1:7">
       <c r="B925" s="13"/>
       <c r="C925" s="15"/>
       <c r="G925" s="14"/>
     </row>
-    <row r="926" spans="1:7" hidden="1">
+    <row r="926" spans="1:7">
       <c r="B926" s="13"/>
       <c r="C926" s="15"/>
       <c r="G926" s="14"/>
     </row>
-    <row r="927" spans="1:7" hidden="1">
+    <row r="927" spans="1:7">
       <c r="B927" s="13"/>
       <c r="C927" s="15"/>
       <c r="D927" s="13"/>
       <c r="F927" s="13"/>
       <c r="G927" s="14"/>
     </row>
-    <row r="928" spans="1:7" ht="30" hidden="1" customHeight="1">
+    <row r="928" spans="1:7" ht="30" customHeight="1">
       <c r="A928" s="16"/>
       <c r="B928" s="16"/>
       <c r="C928" s="16"/>
       <c r="D928" s="19"/>
     </row>
-    <row r="929" spans="1:4" ht="30" hidden="1" customHeight="1">
+    <row r="929" spans="1:4" ht="30" customHeight="1">
       <c r="A929" s="16"/>
       <c r="B929" s="16"/>
       <c r="C929" s="16"/>
       <c r="D929" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:C929">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="是"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="G1:G929"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B900:G903 B890:G890 B879:G880">
     <cfRule type="cellIs" dxfId="0" priority="5" stopIfTrue="1" operator="notEqual">
